--- a/D1_Fiches_Clubs_Joueurs_26_27.xlsx
+++ b/D1_Fiches_Clubs_Joueurs_26_27.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Mode emploi" sheetId="1" state="visible" r:id="rId3"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="474">
   <si>
     <t xml:space="preserve">FICHES CLUBS · D1 FUTSAL 2026-2027</t>
   </si>
@@ -115,7 +115,7 @@
     <t xml:space="preserve">logo</t>
   </si>
   <si>
-    <t xml:space="preserve">ACASA.png</t>
+    <t xml:space="preserve">8.png</t>
   </si>
   <si>
     <t xml:space="preserve">site_web</t>
@@ -331,7 +331,7 @@
     <t xml:space="preserve">Mousse</t>
   </si>
   <si>
-    <t xml:space="preserve">Wassim-si-chaib</t>
+    <t xml:space="preserve">wassim-si-chaib</t>
   </si>
   <si>
     <t xml:space="preserve">WASSIM SI CHAIB</t>
@@ -382,6 +382,9 @@
     <t xml:space="preserve">blanc/rouge</t>
   </si>
   <si>
+    <t xml:space="preserve">1.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">buts (info)</t>
   </si>
   <si>
@@ -394,7 +397,7 @@
     <t xml:space="preserve">HAKAN BULBUL</t>
   </si>
   <si>
-    <t xml:space="preserve">HAKAN </t>
+    <t xml:space="preserve">Hakan </t>
   </si>
   <si>
     <t xml:space="preserve">BULBUL</t>
@@ -406,9 +409,6 @@
     <t xml:space="preserve">MAMADOU SAKO</t>
   </si>
   <si>
-    <t xml:space="preserve">MAMADOU</t>
-  </si>
-  <si>
     <t xml:space="preserve">SACKO</t>
   </si>
   <si>
@@ -418,7 +418,7 @@
     <t xml:space="preserve">RAHIM MARIE SAINTE</t>
   </si>
   <si>
-    <t xml:space="preserve">RAHIM</t>
+    <t xml:space="preserve">Rahim</t>
   </si>
   <si>
     <t xml:space="preserve">MARIE SAINTE</t>
@@ -430,7 +430,7 @@
     <t xml:space="preserve">MOUSSA DOUCOURE</t>
   </si>
   <si>
-    <t xml:space="preserve">MOUSSA</t>
+    <t xml:space="preserve">Moussa</t>
   </si>
   <si>
     <t xml:space="preserve">DOUCOURE</t>
@@ -445,7 +445,7 @@
     <t xml:space="preserve">YANIS PUCH</t>
   </si>
   <si>
-    <t xml:space="preserve">YANIS</t>
+    <t xml:space="preserve">Yanis</t>
   </si>
   <si>
     <t xml:space="preserve">PUCH HERRANTZ</t>
@@ -457,9 +457,6 @@
     <t xml:space="preserve">ALI AGOURRAM</t>
   </si>
   <si>
-    <t xml:space="preserve">ALI</t>
-  </si>
-  <si>
     <t xml:space="preserve">AGOURRAM</t>
   </si>
   <si>
@@ -469,7 +466,7 @@
     <t xml:space="preserve">IBRAHIM KOITA</t>
   </si>
   <si>
-    <t xml:space="preserve">IBRAHIM</t>
+    <t xml:space="preserve">Ibrahim</t>
   </si>
   <si>
     <t xml:space="preserve">KOITA</t>
@@ -481,13 +478,13 @@
     <t xml:space="preserve">MARWAN IDAASSI</t>
   </si>
   <si>
-    <t xml:space="preserve">MARWAN</t>
+    <t xml:space="preserve">Marwan</t>
   </si>
   <si>
     <t xml:space="preserve">IDAASSI</t>
   </si>
   <si>
-    <t xml:space="preserve">IBRAHIM-MARTINS</t>
+    <t xml:space="preserve">ibrahim-martins</t>
   </si>
   <si>
     <t xml:space="preserve">IBRAHIM MARTINS</t>
@@ -496,31 +493,31 @@
     <t xml:space="preserve">MARTINS</t>
   </si>
   <si>
-    <t xml:space="preserve">ALPHA-SEY </t>
+    <t xml:space="preserve">alpha-sey </t>
   </si>
   <si>
     <t xml:space="preserve">ALPHA SEY</t>
   </si>
   <si>
-    <t xml:space="preserve">ALPHA </t>
+    <t xml:space="preserve">Alpha </t>
   </si>
   <si>
     <t xml:space="preserve">SEY</t>
   </si>
   <si>
-    <t xml:space="preserve">MATHIEU-HAMMAD </t>
+    <t xml:space="preserve">mathieu-hammad </t>
   </si>
   <si>
     <t xml:space="preserve">MATHIEU HAMMAD </t>
   </si>
   <si>
-    <t xml:space="preserve">MATHIEU</t>
+    <t xml:space="preserve">Mathieu</t>
   </si>
   <si>
     <t xml:space="preserve"> HAMMAD </t>
   </si>
   <si>
-    <t xml:space="preserve">IBRAHIM-ABDOU-SAIDOU</t>
+    <t xml:space="preserve">ibrahim-abdou-saidou</t>
   </si>
   <si>
     <t xml:space="preserve">IBRAHIM ABDOU SAIDOU</t>
@@ -550,6 +547,9 @@
     <t xml:space="preserve">gris</t>
   </si>
   <si>
+    <t xml:space="preserve">11.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://avionfutsal.com/</t>
   </si>
   <si>
@@ -613,6 +613,9 @@
     <t xml:space="preserve">DUBOIS</t>
   </si>
   <si>
+    <t xml:space="preserve">geoffroey-dubois</t>
+  </si>
+  <si>
     <t xml:space="preserve">YACINE-KASMI </t>
   </si>
   <si>
@@ -625,6 +628,9 @@
     <t xml:space="preserve">KASMI </t>
   </si>
   <si>
+    <t xml:space="preserve">yacine-kasmi </t>
+  </si>
+  <si>
     <t xml:space="preserve">ISLEM BERRADA </t>
   </si>
   <si>
@@ -634,6 +640,9 @@
     <t xml:space="preserve">BERRADA </t>
   </si>
   <si>
+    <t xml:space="preserve">islem berrada </t>
+  </si>
+  <si>
     <t xml:space="preserve">TAO-FARINE </t>
   </si>
   <si>
@@ -646,6 +655,9 @@
     <t xml:space="preserve">FARINE </t>
   </si>
   <si>
+    <t xml:space="preserve">tao-farine </t>
+  </si>
+  <si>
     <t xml:space="preserve">RASLENE-BEN-AMMAR </t>
   </si>
   <si>
@@ -658,6 +670,9 @@
     <t xml:space="preserve">BEN AMMAR </t>
   </si>
   <si>
+    <t xml:space="preserve">raslene-ben-ammar </t>
+  </si>
+  <si>
     <t xml:space="preserve">AHMAD-AIT-AMY </t>
   </si>
   <si>
@@ -667,6 +682,9 @@
     <t xml:space="preserve">AIT AMY </t>
   </si>
   <si>
+    <t xml:space="preserve">ahmad-ait-amy </t>
+  </si>
+  <si>
     <t xml:space="preserve">HAMZA-ABOUYA </t>
   </si>
   <si>
@@ -679,6 +697,9 @@
     <t xml:space="preserve">ABOUYA </t>
   </si>
   <si>
+    <t xml:space="preserve">hamza-abouya </t>
+  </si>
+  <si>
     <t xml:space="preserve">MATHEUS-LINCOLN-SANDOVAL-FERREIRA </t>
   </si>
   <si>
@@ -691,6 +712,9 @@
     <t xml:space="preserve">FERREIRA </t>
   </si>
   <si>
+    <t xml:space="preserve">matheus-lincoln-sandoval-ferreira </t>
+  </si>
+  <si>
     <t xml:space="preserve">MATTEO-MARIEN </t>
   </si>
   <si>
@@ -700,13 +724,19 @@
     <t xml:space="preserve">MARIEN </t>
   </si>
   <si>
+    <t xml:space="preserve">matteo-marien </t>
+  </si>
+  <si>
     <t xml:space="preserve">FICHE CLUB · GARGES</t>
   </si>
   <si>
     <t xml:space="preserve">GARGES DJIBSON</t>
   </si>
   <si>
-    <t xml:space="preserve">GARGES.png</t>
+    <t xml:space="preserve">GARGES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.png</t>
   </si>
   <si>
     <t xml:space="preserve">halim-hadji-ali</t>
@@ -778,7 +808,10 @@
     <t xml:space="preserve">GOAL FUTSAL CLUB</t>
   </si>
   <si>
-    <t xml:space="preserve">GOAL.png</t>
+    <t xml:space="preserve">GOAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.png</t>
   </si>
   <si>
     <t xml:space="preserve">marouane-rezzoug</t>
@@ -886,7 +919,10 @@
     <t xml:space="preserve">ETOILE LAVALLOISE FC</t>
   </si>
   <si>
-    <t xml:space="preserve">LAVAL.png</t>
+    <t xml:space="preserve">LAVAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.png</t>
   </si>
   <si>
     <t xml:space="preserve">bilal-bakkali</t>
@@ -976,7 +1012,10 @@
     <t xml:space="preserve">MONTPELLIER MED. F.</t>
   </si>
   <si>
-    <t xml:space="preserve">MTP.png</t>
+    <t xml:space="preserve">Montpellier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.png</t>
   </si>
   <si>
     <t xml:space="preserve">david-mesquita-rodrigues</t>
@@ -1048,7 +1087,10 @@
     <t xml:space="preserve">NANTES METROPOLE F.</t>
   </si>
   <si>
-    <t xml:space="preserve">NANTES.png</t>
+    <t xml:space="preserve">NANTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.png</t>
   </si>
   <si>
     <t xml:space="preserve">francisco-valdelvira-jimenez</t>
@@ -1138,7 +1180,10 @@
     <t xml:space="preserve">NICE FUTSAL CLUB</t>
   </si>
   <si>
-    <t xml:space="preserve">NICE.png</t>
+    <t xml:space="preserve">NICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.png</t>
   </si>
   <si>
     <t xml:space="preserve">lucas-nahuel-paroldo-ferreri</t>
@@ -1183,7 +1228,10 @@
     <t xml:space="preserve">SPORTING CLUB PARIS</t>
   </si>
   <si>
-    <t xml:space="preserve">SPORTING.png</t>
+    <t xml:space="preserve">SPORTING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.png</t>
   </si>
   <si>
     <t xml:space="preserve">francisco-martinez-villalba</t>
@@ -1255,7 +1303,10 @@
     <t xml:space="preserve">TOULON METROPOLE F.</t>
   </si>
   <si>
-    <t xml:space="preserve">TOULON.png</t>
+    <t xml:space="preserve">TOOULON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.png</t>
   </si>
   <si>
     <t xml:space="preserve">alexis-dubois</t>
@@ -1327,7 +1378,10 @@
     <t xml:space="preserve">UJS TOULOUSE</t>
   </si>
   <si>
-    <t xml:space="preserve">TOULOUSE.png</t>
+    <t xml:space="preserve">TOULOUSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.png</t>
   </si>
   <si>
     <t xml:space="preserve">ayoub-bouita</t>
@@ -1756,249 +1810,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>453600</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>87480</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Image 1"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2114640" y="2430720"/>
-          <a:ext cx="453600" cy="468720"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>501480</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>137520</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2114640" y="1935000"/>
-          <a:ext cx="501480" cy="518400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>286560</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>105840</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Image 3"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2114640" y="1935000"/>
-          <a:ext cx="286560" cy="296280"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>692280</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>112320</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Image 4"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11912040" y="3839760"/>
-          <a:ext cx="692280" cy="684000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>604800</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>55440</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Image 5"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11912040" y="5173200"/>
-          <a:ext cx="604800" cy="572400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>687600</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>149040</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Image 6"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11912040" y="3268440"/>
-          <a:ext cx="687600" cy="529920"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
@@ -2278,7 +2089,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2292,14 +2103,16 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="12"/>
+      <c r="B5" s="12" t="s">
+        <v>382</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
@@ -2336,7 +2149,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2400,18 +2213,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -2424,7 +2237,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -2440,10 +2253,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -2456,7 +2269,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -2472,10 +2285,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -2488,7 +2301,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -2504,10 +2317,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -2520,7 +2333,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -2853,7 +2666,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2867,14 +2680,16 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="12"/>
+      <c r="B5" s="12" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
@@ -2911,7 +2726,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2975,18 +2790,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -2999,7 +2814,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -3015,10 +2830,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -3031,7 +2846,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -3047,10 +2862,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -3063,7 +2878,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -3079,10 +2894,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -3095,7 +2910,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -3111,10 +2926,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -3127,7 +2942,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -3143,10 +2958,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -3159,7 +2974,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -3175,10 +2990,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -3191,7 +3006,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -3470,7 +3285,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3484,14 +3299,16 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="12"/>
+      <c r="B5" s="12" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
@@ -3528,7 +3345,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3592,18 +3409,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -3616,7 +3433,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -3632,10 +3449,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -3648,7 +3465,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -3664,10 +3481,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -3680,7 +3497,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -3696,10 +3513,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -3712,7 +3529,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -3728,10 +3545,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -3744,7 +3561,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -3760,10 +3577,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -3776,7 +3593,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -3792,10 +3609,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>426</v>
+        <v>443</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -3808,7 +3625,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -4087,7 +3904,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4101,14 +3918,16 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="12"/>
+      <c r="B5" s="12" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
@@ -4145,7 +3964,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4209,18 +4028,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -4233,7 +4052,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -4249,10 +4068,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -4265,7 +4084,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -4281,10 +4100,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -4297,7 +4116,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -4313,10 +4132,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -4329,7 +4148,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -4345,10 +4164,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -4361,7 +4180,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -4377,10 +4196,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -4393,7 +4212,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -4409,10 +4228,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -4425,7 +4244,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -4441,10 +4260,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -4457,7 +4276,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -5467,7 +5286,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5565,7 +5383,9 @@
       <c r="A11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="12"/>
+      <c r="B11" s="12" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
@@ -5628,25 +5448,25 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
@@ -5672,14 +5492,14 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>125</v>
@@ -5825,10 +5645,10 @@
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="12" t="s">
         <v>141</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>142</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>16</v>
@@ -5854,17 +5674,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="C23" s="12"/>
+      <c r="D23" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12" t="s">
+      <c r="E23" s="20" t="s">
         <v>145</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>146</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>17</v>
@@ -5890,17 +5710,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>147</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>148</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="E24" s="12" t="s">
         <v>149</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>150</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>21</v>
@@ -5926,17 +5746,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B25" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="C25" s="12"/>
+      <c r="D25" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="E25" s="12" t="s">
         <v>152</v>
-      </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>153</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>1</v>
@@ -5956,17 +5776,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" s="19" t="s">
         <v>154</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>155</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E26" s="21" t="s">
         <v>156</v>
-      </c>
-      <c r="E26" s="21" t="s">
-        <v>157</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>25</v>
@@ -5986,17 +5806,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="B27" s="19" t="s">
         <v>158</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>159</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E27" s="21" t="s">
         <v>160</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>161</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>24</v>
@@ -6018,17 +5838,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="B28" s="19" t="s">
         <v>162</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>163</v>
       </c>
       <c r="C28" s="22"/>
       <c r="D28" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>14</v>
@@ -6191,7 +6011,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6222,7 +6041,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6236,7 +6055,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6244,7 +6063,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6252,7 +6071,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6260,7 +6079,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6274,7 +6093,7 @@
         <v>22</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6282,14 +6101,16 @@
         <v>24</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="12"/>
+      <c r="B11" s="12" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
@@ -6354,10 +6175,10 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6383,7 +6204,9 @@
       </c>
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
+      <c r="K17" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
         <v>54</v>
@@ -6419,7 +6242,9 @@
       </c>
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
+      <c r="K18" s="12" t="s">
+        <v>177</v>
+      </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
         <v>54</v>
@@ -6455,7 +6280,9 @@
       </c>
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
+      <c r="K19" s="12" t="s">
+        <v>181</v>
+      </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
         <v>54</v>
@@ -6491,7 +6318,9 @@
       </c>
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
+      <c r="K20" s="12" t="s">
+        <v>185</v>
+      </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
         <v>54</v>
@@ -6527,7 +6356,9 @@
       </c>
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
+      <c r="K21" s="15" t="s">
+        <v>193</v>
+      </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12"/>
       <c r="N21" s="12"/>
@@ -6536,17 +6367,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="19" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>7</v>
@@ -6557,7 +6388,9 @@
       </c>
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
+      <c r="K22" s="19" t="s">
+        <v>198</v>
+      </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12"/>
       <c r="N22" s="12"/>
@@ -6566,17 +6399,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="19" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>10</v>
@@ -6587,7 +6420,9 @@
       </c>
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
+      <c r="K23" s="19" t="s">
+        <v>202</v>
+      </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12"/>
       <c r="N23" s="12"/>
@@ -6596,17 +6431,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="25" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>17</v>
@@ -6617,7 +6452,9 @@
       </c>
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
+      <c r="K24" s="19" t="s">
+        <v>207</v>
+      </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12"/>
       <c r="N24" s="12"/>
@@ -6626,17 +6463,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="19" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>21</v>
@@ -6647,7 +6484,9 @@
       </c>
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
+      <c r="K25" s="19" t="s">
+        <v>212</v>
+      </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12"/>
       <c r="N25" s="12"/>
@@ -6656,17 +6495,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="19" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>23</v>
@@ -6677,7 +6516,9 @@
       </c>
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
+      <c r="K26" s="19" t="s">
+        <v>216</v>
+      </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12"/>
       <c r="N26" s="12"/>
@@ -6686,17 +6527,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="19" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>24</v>
@@ -6707,28 +6548,30 @@
       </c>
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
+      <c r="K27" s="19" t="s">
+        <v>221</v>
+      </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12"/>
       <c r="N27" s="12"/>
       <c r="O27" s="12"/>
       <c r="P27" s="12"/>
     </row>
-    <row r="28" customFormat="false" ht="25.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>18</v>
@@ -6741,7 +6584,9 @@
       </c>
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
+      <c r="K28" s="19" t="s">
+        <v>226</v>
+      </c>
       <c r="L28" s="12"/>
       <c r="M28" s="12"/>
       <c r="N28" s="12"/>
@@ -6750,17 +6595,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="19" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>20</v>
@@ -6771,7 +6616,9 @@
       </c>
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
+      <c r="K29" s="19" t="s">
+        <v>230</v>
+      </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12"/>
       <c r="N29" s="12"/>
@@ -6905,7 +6752,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6936,7 +6782,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6950,14 +6796,16 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="12"/>
+      <c r="B5" s="10" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
@@ -6994,7 +6842,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7058,18 +6906,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -7082,7 +6930,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -7098,10 +6946,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -7114,7 +6962,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -7130,10 +6978,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -7146,7 +6994,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -7162,10 +7010,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -7178,7 +7026,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -7194,10 +7042,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -7210,7 +7058,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -7226,10 +7074,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -7242,7 +7090,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -7258,10 +7106,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -7274,7 +7122,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -7553,7 +7401,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7567,14 +7415,16 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="12"/>
+      <c r="B5" s="12" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
@@ -7611,7 +7461,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7675,18 +7525,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -7699,7 +7549,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -7715,10 +7565,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -7731,7 +7581,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -7747,10 +7597,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -7763,7 +7613,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -7779,10 +7629,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -7795,7 +7645,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -7811,10 +7661,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -7827,7 +7677,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -7843,10 +7693,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -7859,7 +7709,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -7875,10 +7725,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -7891,7 +7741,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -7907,10 +7757,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -7923,7 +7773,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -7939,10 +7789,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -7955,7 +7805,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -7971,10 +7821,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
@@ -7987,7 +7837,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
       <c r="K26" s="12" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12" t="s">
@@ -8003,10 +7853,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
@@ -8019,7 +7869,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12" t="s">
@@ -8226,7 +8076,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8240,14 +8090,16 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="12"/>
+      <c r="B5" s="12" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
@@ -8284,7 +8136,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8348,18 +8200,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -8372,7 +8224,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -8388,10 +8240,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -8404,7 +8256,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -8420,10 +8272,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -8436,7 +8288,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -8452,10 +8304,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -8468,7 +8320,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -8484,10 +8336,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -8500,7 +8352,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -8516,10 +8368,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -8532,7 +8384,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -8548,10 +8400,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -8564,7 +8416,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -8580,10 +8432,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -8596,7 +8448,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -8612,10 +8464,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -8628,7 +8480,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -8871,7 +8723,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8885,14 +8737,16 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="12"/>
+      <c r="B5" s="12" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
@@ -8929,7 +8783,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8993,18 +8847,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -9017,7 +8871,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -9033,10 +8887,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -9049,7 +8903,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -9065,10 +8919,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -9081,7 +8935,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -9097,10 +8951,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -9113,7 +8967,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -9129,10 +8983,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -9145,7 +8999,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -9161,10 +9015,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -9177,7 +9031,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -9193,10 +9047,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -9209,7 +9063,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -9488,7 +9342,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9502,14 +9356,16 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="12"/>
+      <c r="B5" s="12" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
@@ -9546,7 +9402,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9610,18 +9466,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -9634,7 +9490,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -9650,10 +9506,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -9666,7 +9522,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -9682,10 +9538,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -9698,7 +9554,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -9714,10 +9570,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -9730,7 +9586,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -9746,10 +9602,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -9762,7 +9618,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -9778,10 +9634,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -9794,7 +9650,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -9810,10 +9666,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -9826,7 +9682,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -9842,10 +9698,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -9858,7 +9714,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -9874,10 +9730,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -9890,7 +9746,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">

--- a/D1_Fiches_Clubs_Joueurs_26_27.xlsx
+++ b/D1_Fiches_Clubs_Joueurs_26_27.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="Mode emploi" sheetId="1" state="visible" r:id="rId3"/>
@@ -1303,7 +1303,7 @@
     <t xml:space="preserve">TOULON METROPOLE F.</t>
   </si>
   <si>
-    <t xml:space="preserve">TOOULON</t>
+    <t xml:space="preserve">TOULON</t>
   </si>
   <si>
     <t xml:space="preserve">7.png</t>

--- a/D1_Fiches_Clubs_Joueurs_26_27.xlsx
+++ b/D1_Fiches_Clubs_Joueurs_26_27.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="11"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Mode emploi" sheetId="1" state="visible" r:id="rId3"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="469">
   <si>
     <t xml:space="preserve">FICHES CLUBS · D1 FUTSAL 2026-2027</t>
   </si>
@@ -601,7 +601,7 @@
     <t xml:space="preserve">ZAHRY</t>
   </si>
   <si>
-    <t xml:space="preserve">Geoffroey-dubois</t>
+    <t xml:space="preserve">geoffroey-dubois</t>
   </si>
   <si>
     <t xml:space="preserve">GEOFFREY DUBOIS</t>
@@ -613,10 +613,10 @@
     <t xml:space="preserve">DUBOIS</t>
   </si>
   <si>
-    <t xml:space="preserve">geoffroey-dubois</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YACINE-KASMI </t>
+    <t xml:space="preserve">geoffroey-dubois.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yacine-kasmi </t>
   </si>
   <si>
     <t xml:space="preserve">YACINE KASMI </t>
@@ -628,7 +628,7 @@
     <t xml:space="preserve">KASMI </t>
   </si>
   <si>
-    <t xml:space="preserve">yacine-kasmi </t>
+    <t xml:space="preserve">islem berrada </t>
   </si>
   <si>
     <t xml:space="preserve">ISLEM BERRADA </t>
@@ -640,10 +640,7 @@
     <t xml:space="preserve">BERRADA </t>
   </si>
   <si>
-    <t xml:space="preserve">islem berrada </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAO-FARINE </t>
+    <t xml:space="preserve">tao-farine </t>
   </si>
   <si>
     <t xml:space="preserve">TAO FARINE </t>
@@ -655,10 +652,7 @@
     <t xml:space="preserve">FARINE </t>
   </si>
   <si>
-    <t xml:space="preserve">tao-farine </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RASLENE-BEN-AMMAR </t>
+    <t xml:space="preserve">raslene-ben-ammar </t>
   </si>
   <si>
     <t xml:space="preserve">RASLENE BEN AMMAR </t>
@@ -670,10 +664,7 @@
     <t xml:space="preserve">BEN AMMAR </t>
   </si>
   <si>
-    <t xml:space="preserve">raslene-ben-ammar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHMAD-AIT-AMY </t>
+    <t xml:space="preserve">ahmad-ait-amy </t>
   </si>
   <si>
     <t xml:space="preserve">AHMAD AIT AMY </t>
@@ -682,10 +673,7 @@
     <t xml:space="preserve">AIT AMY </t>
   </si>
   <si>
-    <t xml:space="preserve">ahmad-ait-amy </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HAMZA-ABOUYA </t>
+    <t xml:space="preserve">hamza-abouya </t>
   </si>
   <si>
     <t xml:space="preserve">HAMZA ABOUYA </t>
@@ -697,7 +685,7 @@
     <t xml:space="preserve">ABOUYA </t>
   </si>
   <si>
-    <t xml:space="preserve">hamza-abouya </t>
+    <t xml:space="preserve">matheus-lincoln-sandoval-ferreira </t>
   </si>
   <si>
     <t xml:space="preserve">MATHEUS-LINCOLN-SANDOVAL-FERREIRA </t>
@@ -712,7 +700,7 @@
     <t xml:space="preserve">FERREIRA </t>
   </si>
   <si>
-    <t xml:space="preserve">matheus-lincoln-sandoval-ferreira </t>
+    <t xml:space="preserve">matteo-marien </t>
   </si>
   <si>
     <t xml:space="preserve">MATTEO-MARIEN </t>
@@ -724,9 +712,6 @@
     <t xml:space="preserve">MARIEN </t>
   </si>
   <si>
-    <t xml:space="preserve">matteo-marien </t>
-  </si>
-  <si>
     <t xml:space="preserve">FICHE CLUB · GARGES</t>
   </si>
   <si>
@@ -1012,7 +997,7 @@
     <t xml:space="preserve">MONTPELLIER MED. F.</t>
   </si>
   <si>
-    <t xml:space="preserve">Montpellier</t>
+    <t xml:space="preserve">MONTPELLIER</t>
   </si>
   <si>
     <t xml:space="preserve">6.png</t>
@@ -2089,7 +2074,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2103,7 +2088,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2111,7 +2096,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2149,7 +2134,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2221,10 +2206,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -2237,7 +2222,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -2253,10 +2238,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -2269,7 +2254,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -2285,10 +2270,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -2301,7 +2286,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -2317,10 +2302,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -2333,7 +2318,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -2666,7 +2651,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2680,7 +2665,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2688,7 +2673,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2726,7 +2711,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2798,10 +2783,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -2814,7 +2799,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -2830,10 +2815,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -2846,7 +2831,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -2862,10 +2847,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -2878,7 +2863,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -2894,10 +2879,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -2910,7 +2895,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -2926,10 +2911,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -2942,7 +2927,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -2958,10 +2943,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -2974,7 +2959,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -2990,10 +2975,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -3006,7 +2991,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -3285,7 +3270,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3299,7 +3284,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3307,7 +3292,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3345,7 +3330,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3417,10 +3402,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -3433,7 +3418,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -3449,10 +3434,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -3465,7 +3450,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -3481,10 +3466,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -3497,7 +3482,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -3513,10 +3498,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -3529,7 +3514,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -3545,10 +3530,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -3561,7 +3546,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -3577,10 +3562,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -3593,7 +3578,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -3609,10 +3594,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -3625,7 +3610,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -3904,7 +3889,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3918,7 +3903,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3926,7 +3911,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3964,7 +3949,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4036,10 +4021,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -4052,7 +4037,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -4068,10 +4053,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -4084,7 +4069,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -4100,10 +4085,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -4116,7 +4101,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -4132,10 +4117,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -4148,7 +4133,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -4164,10 +4149,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -4180,7 +4165,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -4196,10 +4181,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -4212,7 +4197,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -4228,10 +4213,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -4244,7 +4229,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -4260,10 +4245,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -4276,7 +4261,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -6389,7 +6374,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="19" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12"/>
@@ -6399,7 +6384,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>199</v>
@@ -6421,7 +6406,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="19" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12"/>
@@ -6431,17 +6416,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="B24" s="19" t="s">
         <v>203</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>204</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="E24" s="21" t="s">
         <v>205</v>
-      </c>
-      <c r="E24" s="21" t="s">
-        <v>206</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>17</v>
@@ -6453,7 +6438,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="19" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12"/>
@@ -6463,17 +6448,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>21</v>
@@ -6485,7 +6470,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="19" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12"/>
@@ -6495,17 +6480,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>23</v>
@@ -6517,7 +6502,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
       <c r="K26" s="19" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12"/>
@@ -6527,17 +6512,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="19" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>24</v>
@@ -6549,7 +6534,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="19" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12"/>
@@ -6559,19 +6544,19 @@
     </row>
     <row r="28" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>18</v>
@@ -6585,7 +6570,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
       <c r="K28" s="19" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="12"/>
@@ -6595,17 +6580,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="19" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>20</v>
@@ -6617,7 +6602,7 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="19" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12"/>
@@ -6782,7 +6767,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6796,7 +6781,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6804,7 +6789,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6842,7 +6827,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6914,10 +6899,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -6930,7 +6915,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -6946,10 +6931,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -6962,7 +6947,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -6978,10 +6963,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -6994,7 +6979,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -7010,10 +6995,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -7026,7 +7011,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -7042,10 +7027,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -7058,7 +7043,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -7074,10 +7059,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -7090,7 +7075,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -7106,10 +7091,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -7122,7 +7107,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -7401,7 +7386,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7415,7 +7400,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7423,7 +7408,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7461,7 +7446,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7533,10 +7518,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -7549,7 +7534,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -7565,10 +7550,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -7581,7 +7566,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -7597,10 +7582,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -7613,7 +7598,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -7629,10 +7614,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -7645,7 +7630,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -7661,10 +7646,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -7677,7 +7662,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -7693,10 +7678,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -7709,7 +7694,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -7725,10 +7710,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -7741,7 +7726,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -7757,10 +7742,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -7773,7 +7758,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -7789,10 +7774,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -7805,7 +7790,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -7821,10 +7806,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
@@ -7837,7 +7822,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
       <c r="K26" s="12" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12" t="s">
@@ -7853,10 +7838,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
@@ -7869,7 +7854,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12" t="s">
@@ -8076,7 +8061,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8090,7 +8075,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8098,7 +8083,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8136,7 +8121,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8208,10 +8193,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -8224,7 +8209,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -8240,10 +8225,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -8256,7 +8241,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -8272,10 +8257,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -8288,7 +8273,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -8304,10 +8289,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -8320,7 +8305,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -8336,10 +8321,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -8352,7 +8337,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -8368,10 +8353,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -8384,7 +8369,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -8400,10 +8385,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -8416,7 +8401,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -8432,10 +8417,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -8448,7 +8433,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -8464,10 +8449,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -8480,7 +8465,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -8723,7 +8708,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8737,7 +8722,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8745,7 +8730,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8783,7 +8768,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8855,10 +8840,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -8871,7 +8856,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -8887,10 +8872,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -8903,7 +8888,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -8919,10 +8904,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -8935,7 +8920,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -8951,10 +8936,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -8967,7 +8952,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -8983,10 +8968,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -8999,7 +8984,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -9015,10 +9000,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -9031,7 +9016,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -9047,10 +9032,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -9063,7 +9048,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -9342,7 +9327,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9356,7 +9341,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9364,7 +9349,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9402,7 +9387,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9474,10 +9459,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -9490,7 +9475,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -9506,10 +9491,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -9522,7 +9507,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -9538,10 +9523,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -9554,7 +9539,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -9570,10 +9555,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -9586,7 +9571,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -9602,10 +9587,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -9618,7 +9603,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -9634,10 +9619,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -9650,7 +9635,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -9666,10 +9651,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -9682,7 +9667,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -9698,10 +9683,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -9714,7 +9699,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -9730,10 +9715,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -9746,7 +9731,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">

--- a/D1_Fiches_Clubs_Joueurs_26_27.xlsx
+++ b/D1_Fiches_Clubs_Joueurs_26_27.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Mode emploi" sheetId="1" state="visible" r:id="rId3"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="486">
   <si>
     <t xml:space="preserve">FICHES CLUBS · D1 FUTSAL 2026-2027</t>
   </si>
@@ -344,6 +344,57 @@
   </si>
   <si>
     <t xml:space="preserve">Gauche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anas-dlimsi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANAS DLIMSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLIMSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yassine-alaoui-m’hammedi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YASSINE ALAOUI M’HAMMEDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yassine ALAOUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yassine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALAOUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marocain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soumaila-soumare </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOUMAILA SOUMARE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soumaila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOUMARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sirou-soumare </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sirou SOUMARE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sirou</t>
   </si>
   <si>
     <t xml:space="preserve">COMPO TYPE</t>
@@ -1448,7 +1499,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1537,17 +1588,6 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1618,7 +1658,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1691,36 +1731,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2074,7 +2094,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2088,7 +2108,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2096,7 +2116,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2134,7 +2154,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2198,18 +2218,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -2222,7 +2242,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -2238,10 +2258,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -2254,7 +2274,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -2270,10 +2290,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -2286,7 +2306,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>387</v>
+        <v>404</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -2302,10 +2322,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>389</v>
+        <v>406</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -2318,7 +2338,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>390</v>
+        <v>407</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -2531,31 +2551,31 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -2563,33 +2583,33 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" s="24"/>
+        <v>123</v>
+      </c>
+      <c r="B36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="24"/>
+      <c r="B37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" s="24"/>
+        <v>124</v>
+      </c>
+      <c r="B38" s="20"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="24"/>
+        <v>125</v>
+      </c>
+      <c r="B39" s="20"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="24"/>
+      <c r="B40" s="20"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -2651,7 +2671,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>391</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2665,7 +2685,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2673,7 +2693,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2711,7 +2731,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2775,18 +2795,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>396</v>
+        <v>413</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -2799,7 +2819,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -2815,10 +2835,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -2831,7 +2851,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -2847,10 +2867,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -2863,7 +2883,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -2879,10 +2899,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -2895,7 +2915,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -2911,10 +2931,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -2927,7 +2947,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -2943,10 +2963,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -2959,7 +2979,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -2975,10 +2995,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -2991,7 +3011,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -3150,31 +3170,31 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -3182,33 +3202,33 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" s="24"/>
+        <v>123</v>
+      </c>
+      <c r="B36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="24"/>
+      <c r="B37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" s="24"/>
+        <v>124</v>
+      </c>
+      <c r="B38" s="20"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="24"/>
+        <v>125</v>
+      </c>
+      <c r="B39" s="20"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="24"/>
+      <c r="B40" s="20"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -3270,7 +3290,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3284,7 +3304,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3292,7 +3312,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3330,7 +3350,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3394,18 +3414,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -3418,7 +3438,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -3434,10 +3454,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -3450,7 +3470,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -3466,10 +3486,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>426</v>
+        <v>443</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -3482,7 +3502,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -3498,10 +3518,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -3514,7 +3534,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -3530,10 +3550,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -3546,7 +3566,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -3562,10 +3582,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>436</v>
+        <v>453</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -3578,7 +3598,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -3594,10 +3614,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -3610,7 +3630,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -3769,31 +3789,31 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -3801,33 +3821,33 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" s="24"/>
+        <v>123</v>
+      </c>
+      <c r="B36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="24"/>
+      <c r="B37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" s="24"/>
+        <v>124</v>
+      </c>
+      <c r="B38" s="20"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="24"/>
+        <v>125</v>
+      </c>
+      <c r="B39" s="20"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="24"/>
+      <c r="B40" s="20"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -3889,7 +3909,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3903,7 +3923,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>442</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3911,7 +3931,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3949,7 +3969,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4013,18 +4033,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -4037,7 +4057,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -4053,10 +4073,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -4069,7 +4089,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>450</v>
+        <v>467</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -4085,10 +4105,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -4101,7 +4121,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -4117,10 +4137,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>455</v>
+        <v>472</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -4133,7 +4153,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>456</v>
+        <v>473</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -4149,10 +4169,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -4165,7 +4185,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>459</v>
+        <v>476</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -4181,10 +4201,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>461</v>
+        <v>478</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -4197,7 +4217,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>462</v>
+        <v>479</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -4213,10 +4233,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -4229,7 +4249,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -4245,10 +4265,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -4261,7 +4281,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>468</v>
+        <v>485</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -4402,31 +4422,31 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -4434,33 +4454,33 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" s="24"/>
+        <v>123</v>
+      </c>
+      <c r="B36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="24"/>
+      <c r="B37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" s="24"/>
+        <v>124</v>
+      </c>
+      <c r="B38" s="20"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="24"/>
+        <v>125</v>
+      </c>
+      <c r="B39" s="20"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="24"/>
+      <c r="B40" s="20"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -4501,7 +4521,7 @@
     <tabColor rgb="FF111111"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -5117,149 +5137,249 @@
       <c r="P28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15"/>
-      <c r="B29" s="12"/>
+      <c r="A29" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>105</v>
+      </c>
       <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
+      <c r="D29" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="K29" s="12"/>
       <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
+      <c r="M29" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="N29" s="12"/>
       <c r="O29" s="12"/>
       <c r="P29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
+      <c r="A30" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>113</v>
+      </c>
       <c r="K30" s="12"/>
       <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
+      <c r="M30" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="N30" s="12"/>
       <c r="O30" s="12"/>
       <c r="P30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15"/>
-      <c r="B31" s="12"/>
+      <c r="A31" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>115</v>
+      </c>
       <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
+      <c r="D31" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="K31" s="12"/>
       <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
+      <c r="M31" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="N31" s="12"/>
       <c r="O31" s="12"/>
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
-        <v>104</v>
-      </c>
+      <c r="A32" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="N32" s="12"/>
+      <c r="O32" s="12"/>
+      <c r="P32" s="12"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="19"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="B35" s="7" t="s">
+      <c r="A35" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>46</v>
+        <v>124</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B41" s="17" t="s">
         <v>61</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G17:G31" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G17:G32" type="list">
       <formula1>"Gardien,Fixo,Ailier,Pivot,Universel"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H17:H31" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H17:H32" type="list">
       <formula1>"oui,non"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I17:I31" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I17:I32" type="list">
       <formula1>"Droit,Gauche,Les deux"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M17:M31" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M17:M32" type="list">
       <formula1>"oui,non"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B36:B38 B40" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B37:B39 B41" type="list">
       <formula1>$A$17:$A$31</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5301,7 +5421,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5315,7 +5435,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5323,23 +5443,23 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="19" t="s">
-        <v>112</v>
+      <c r="B6" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>113</v>
+      <c r="B7" s="11" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5353,7 +5473,7 @@
         <v>22</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5361,7 +5481,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5369,7 +5489,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5433,25 +5553,25 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>122</v>
+        <v>138</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>139</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
@@ -5477,17 +5597,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
         <v>77</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>7</v>
@@ -5513,17 +5633,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>13</v>
@@ -5549,17 +5669,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>8</v>
@@ -5585,19 +5705,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>4</v>
@@ -5623,17 +5743,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
         <v>94</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>16</v>
@@ -5659,17 +5779,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="C23" s="12"/>
-      <c r="D23" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>145</v>
+      <c r="D23" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>162</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>17</v>
@@ -5695,17 +5815,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>21</v>
@@ -5730,18 +5850,18 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>151</v>
+      <c r="A25" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>168</v>
       </c>
       <c r="C25" s="12"/>
-      <c r="D25" s="19" t="s">
-        <v>144</v>
+      <c r="D25" s="11" t="s">
+        <v>161</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>1</v>
@@ -5760,18 +5880,18 @@
       <c r="P25" s="14"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>154</v>
+      <c r="A26" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>171</v>
       </c>
       <c r="C26" s="12"/>
-      <c r="D26" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E26" s="21" t="s">
-        <v>156</v>
+      <c r="D26" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>173</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>25</v>
@@ -5790,18 +5910,18 @@
       <c r="P26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>158</v>
+      <c r="A27" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>175</v>
       </c>
       <c r="C27" s="12"/>
-      <c r="D27" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>160</v>
+      <c r="D27" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>177</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>24</v>
@@ -5822,18 +5942,18 @@
       <c r="P27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="D28" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>163</v>
+      <c r="E28" s="16" t="s">
+        <v>180</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>14</v>
@@ -5906,31 +6026,31 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -5938,33 +6058,33 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" s="24"/>
+        <v>123</v>
+      </c>
+      <c r="B36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="24"/>
+      <c r="B37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" s="24"/>
+        <v>124</v>
+      </c>
+      <c r="B38" s="20"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="24"/>
+        <v>125</v>
+      </c>
+      <c r="B39" s="20"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="24"/>
+      <c r="B40" s="20"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -6026,7 +6146,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6040,7 +6160,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6048,7 +6168,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6056,15 +6176,15 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>168</v>
+      <c r="B7" s="11" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6078,7 +6198,7 @@
         <v>22</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6086,7 +6206,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6094,7 +6214,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6102,7 +6222,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6160,25 +6280,25 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="C17" s="12"/>
-      <c r="D17" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>176</v>
+      <c r="D17" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>193</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>8</v>
@@ -6190,7 +6310,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -6206,17 +6326,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="C18" s="12"/>
-      <c r="D18" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>180</v>
+      <c r="D18" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>197</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>6</v>
@@ -6228,7 +6348,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -6244,17 +6364,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="C19" s="12"/>
-      <c r="D19" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>184</v>
+      <c r="D19" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>201</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>22</v>
@@ -6266,7 +6386,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -6282,17 +6402,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="C20" s="12"/>
-      <c r="D20" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>188</v>
+      <c r="D20" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>5</v>
@@ -6304,7 +6424,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -6320,17 +6440,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="C21" s="12"/>
-      <c r="D21" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>192</v>
+      <c r="D21" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>209</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>1</v>
@@ -6342,7 +6462,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="15" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12"/>
@@ -6351,18 +6471,18 @@
       <c r="P21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>195</v>
+      <c r="A22" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>212</v>
       </c>
       <c r="C22" s="12"/>
-      <c r="D22" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="E22" s="21" t="s">
-        <v>197</v>
+      <c r="D22" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>214</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>7</v>
@@ -6373,8 +6493,8 @@
       </c>
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
-      <c r="K22" s="19" t="s">
-        <v>194</v>
+      <c r="K22" s="11" t="s">
+        <v>211</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12"/>
@@ -6383,18 +6503,18 @@
       <c r="P22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>199</v>
+      <c r="A23" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>216</v>
       </c>
       <c r="C23" s="12"/>
-      <c r="D23" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>201</v>
+      <c r="D23" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>218</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>10</v>
@@ -6405,8 +6525,8 @@
       </c>
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
-      <c r="K23" s="19" t="s">
-        <v>198</v>
+      <c r="K23" s="11" t="s">
+        <v>215</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12"/>
@@ -6415,18 +6535,18 @@
       <c r="P23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>203</v>
+      <c r="A24" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>220</v>
       </c>
       <c r="C24" s="12"/>
-      <c r="D24" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="E24" s="21" t="s">
-        <v>205</v>
+      <c r="D24" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>222</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>17</v>
@@ -6437,8 +6557,8 @@
       </c>
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
-      <c r="K24" s="19" t="s">
-        <v>202</v>
+      <c r="K24" s="11" t="s">
+        <v>219</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12"/>
@@ -6447,18 +6567,18 @@
       <c r="P24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>207</v>
+      <c r="A25" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>224</v>
       </c>
       <c r="C25" s="12"/>
-      <c r="D25" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="E25" s="21" t="s">
-        <v>209</v>
+      <c r="D25" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>226</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>21</v>
@@ -6469,8 +6589,8 @@
       </c>
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
-      <c r="K25" s="19" t="s">
-        <v>206</v>
+      <c r="K25" s="11" t="s">
+        <v>223</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12"/>
@@ -6479,18 +6599,18 @@
       <c r="P25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>211</v>
+      <c r="A26" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>228</v>
       </c>
       <c r="C26" s="12"/>
-      <c r="D26" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>212</v>
+      <c r="D26" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>229</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>23</v>
@@ -6501,8 +6621,8 @@
       </c>
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
-      <c r="K26" s="19" t="s">
-        <v>210</v>
+      <c r="K26" s="11" t="s">
+        <v>227</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12"/>
@@ -6511,18 +6631,18 @@
       <c r="P26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>214</v>
+      <c r="A27" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>231</v>
       </c>
       <c r="C27" s="12"/>
-      <c r="D27" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>216</v>
+      <c r="D27" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>233</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>24</v>
@@ -6533,8 +6653,8 @@
       </c>
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
-      <c r="K27" s="19" t="s">
-        <v>213</v>
+      <c r="K27" s="11" t="s">
+        <v>230</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12"/>
@@ -6543,20 +6663,20 @@
       <c r="P27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="D28" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="E28" s="21" t="s">
-        <v>221</v>
+      <c r="A28" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>238</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>18</v>
@@ -6569,8 +6689,8 @@
       </c>
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
-      <c r="K28" s="19" t="s">
-        <v>217</v>
+      <c r="K28" s="11" t="s">
+        <v>234</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="12"/>
@@ -6579,18 +6699,18 @@
       <c r="P28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>223</v>
+      <c r="A29" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>240</v>
       </c>
       <c r="C29" s="12"/>
-      <c r="D29" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>225</v>
+      <c r="D29" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>242</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>20</v>
@@ -6601,8 +6721,8 @@
       </c>
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
-      <c r="K29" s="19" t="s">
-        <v>222</v>
+      <c r="K29" s="11" t="s">
+        <v>239</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12"/>
@@ -6647,31 +6767,31 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -6679,33 +6799,33 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" s="24"/>
+        <v>123</v>
+      </c>
+      <c r="B36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="24"/>
+      <c r="B37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" s="24"/>
+        <v>124</v>
+      </c>
+      <c r="B38" s="20"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="24"/>
+        <v>125</v>
+      </c>
+      <c r="B39" s="20"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="24"/>
+      <c r="B40" s="20"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -6767,7 +6887,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6781,7 +6901,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6789,7 +6909,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6827,7 +6947,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6891,18 +7011,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -6915,7 +7035,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -6931,10 +7051,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -6947,7 +7067,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -6963,10 +7083,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -6979,7 +7099,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -6995,10 +7115,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -7011,7 +7131,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -7027,10 +7147,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -7043,7 +7163,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -7059,10 +7179,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -7075,7 +7195,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -7091,10 +7211,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -7107,7 +7227,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -7266,31 +7386,31 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -7298,33 +7418,33 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" s="24"/>
+        <v>123</v>
+      </c>
+      <c r="B36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="24"/>
+      <c r="B37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" s="24"/>
+        <v>124</v>
+      </c>
+      <c r="B38" s="20"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="24"/>
+        <v>125</v>
+      </c>
+      <c r="B39" s="20"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="24"/>
+      <c r="B40" s="20"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -7386,7 +7506,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7400,7 +7520,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7408,7 +7528,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7446,7 +7566,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7510,18 +7630,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -7534,7 +7654,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -7550,10 +7670,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -7566,7 +7686,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -7582,10 +7702,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -7598,7 +7718,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -7614,10 +7734,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -7630,7 +7750,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -7646,10 +7766,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -7662,7 +7782,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -7678,10 +7798,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -7694,7 +7814,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -7710,10 +7830,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -7726,7 +7846,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -7742,10 +7862,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -7758,7 +7878,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -7774,10 +7894,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -7790,7 +7910,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -7806,10 +7926,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
@@ -7822,7 +7942,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
       <c r="K26" s="12" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12" t="s">
@@ -7838,10 +7958,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
@@ -7854,7 +7974,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12" t="s">
@@ -7941,31 +8061,31 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -7973,33 +8093,33 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" s="24"/>
+        <v>123</v>
+      </c>
+      <c r="B36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="24"/>
+      <c r="B37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" s="24"/>
+        <v>124</v>
+      </c>
+      <c r="B38" s="20"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="24"/>
+        <v>125</v>
+      </c>
+      <c r="B39" s="20"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="24"/>
+      <c r="B40" s="20"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -8061,7 +8181,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8075,7 +8195,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8083,7 +8203,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8121,7 +8241,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8185,18 +8305,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -8209,7 +8329,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -8225,10 +8345,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -8241,7 +8361,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -8257,10 +8377,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -8273,7 +8393,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -8289,10 +8409,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -8305,7 +8425,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -8321,10 +8441,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -8337,7 +8457,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -8353,10 +8473,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -8369,7 +8489,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -8385,10 +8505,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -8401,7 +8521,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -8417,10 +8537,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -8433,7 +8553,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -8449,10 +8569,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -8465,7 +8585,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -8588,31 +8708,31 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -8620,33 +8740,33 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" s="24"/>
+        <v>123</v>
+      </c>
+      <c r="B36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="24"/>
+      <c r="B37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" s="24"/>
+        <v>124</v>
+      </c>
+      <c r="B38" s="20"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="24"/>
+        <v>125</v>
+      </c>
+      <c r="B39" s="20"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="24"/>
+      <c r="B40" s="20"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -8708,7 +8828,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8722,7 +8842,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8730,7 +8850,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8768,7 +8888,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8832,18 +8952,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -8856,7 +8976,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -8872,10 +8992,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -8888,7 +9008,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -8904,10 +9024,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -8920,7 +9040,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -8936,10 +9056,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -8952,7 +9072,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -8968,10 +9088,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -8984,7 +9104,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -9000,10 +9120,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -9016,7 +9136,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -9032,10 +9152,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -9048,7 +9168,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -9207,31 +9327,31 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -9239,33 +9359,33 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" s="24"/>
+        <v>123</v>
+      </c>
+      <c r="B36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="24"/>
+      <c r="B37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" s="24"/>
+        <v>124</v>
+      </c>
+      <c r="B38" s="20"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="24"/>
+        <v>125</v>
+      </c>
+      <c r="B39" s="20"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="24"/>
+      <c r="B40" s="20"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -9327,7 +9447,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9341,7 +9461,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9349,7 +9469,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9387,7 +9507,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>347</v>
+        <v>364</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9451,18 +9571,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -9475,7 +9595,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -9491,10 +9611,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -9507,7 +9627,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -9523,10 +9643,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -9539,7 +9659,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -9555,10 +9675,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -9571,7 +9691,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -9587,10 +9707,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -9603,7 +9723,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -9619,10 +9739,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -9635,7 +9755,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -9651,10 +9771,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -9667,7 +9787,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -9683,10 +9803,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -9699,7 +9819,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -9715,10 +9835,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -9731,7 +9851,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -9854,31 +9974,31 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
-      <c r="P32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -9886,33 +10006,33 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" s="24"/>
+        <v>123</v>
+      </c>
+      <c r="B36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="24"/>
+      <c r="B37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" s="24"/>
+        <v>124</v>
+      </c>
+      <c r="B38" s="20"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="24"/>
+        <v>125</v>
+      </c>
+      <c r="B39" s="20"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="24"/>
+      <c r="B40" s="20"/>
     </row>
   </sheetData>
   <dataValidations count="5">

--- a/D1_Fiches_Clubs_Joueurs_26_27.xlsx
+++ b/D1_Fiches_Clubs_Joueurs_26_27.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="485">
   <si>
     <t xml:space="preserve">FICHES CLUBS · D1 FUTSAL 2026-2027</t>
   </si>
@@ -328,7 +328,7 @@
     <t xml:space="preserve">MOUSSA HADDAD </t>
   </si>
   <si>
-    <t xml:space="preserve">Mousse</t>
+    <t xml:space="preserve">Moussa</t>
   </si>
   <si>
     <t xml:space="preserve">wassim-si-chaib</t>
@@ -479,9 +479,6 @@
   </si>
   <si>
     <t xml:space="preserve">MOUSSA DOUCOURE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moussa</t>
   </si>
   <si>
     <t xml:space="preserve">DOUCOURE</t>
@@ -2094,7 +2091,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2108,7 +2105,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2116,7 +2113,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2154,7 +2151,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2226,10 +2223,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>396</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>397</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -2242,7 +2239,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -2258,10 +2255,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>399</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>400</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -2274,7 +2271,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -2290,10 +2287,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>402</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>403</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -2306,7 +2303,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -2322,10 +2319,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>405</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>406</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -2338,7 +2335,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -2671,7 +2668,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2685,7 +2682,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2693,7 +2690,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2731,7 +2728,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2803,10 +2800,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>412</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>413</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -2819,7 +2816,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -2835,10 +2832,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>415</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>416</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -2851,7 +2848,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -2867,10 +2864,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>418</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>419</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -2883,7 +2880,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -2899,10 +2896,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>421</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>422</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -2915,7 +2912,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -2931,10 +2928,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>424</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>425</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -2947,7 +2944,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -2963,10 +2960,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>427</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>428</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -2979,7 +2976,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -2995,10 +2992,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>430</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>431</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -3011,7 +3008,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -3290,7 +3287,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3304,7 +3301,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3312,7 +3309,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3350,7 +3347,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3422,10 +3419,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>437</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>438</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -3438,7 +3435,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -3454,10 +3451,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>440</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>441</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -3470,7 +3467,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -3486,10 +3483,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>443</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>444</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -3502,7 +3499,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -3518,10 +3515,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>446</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>447</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -3534,7 +3531,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -3550,10 +3547,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>449</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>450</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -3566,7 +3563,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -3582,10 +3579,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>452</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>453</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -3598,7 +3595,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -3614,10 +3611,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>455</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>456</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -3630,7 +3627,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -3909,7 +3906,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3923,7 +3920,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3931,7 +3928,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3969,7 +3966,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4041,10 +4038,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>462</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>463</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -4057,7 +4054,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -4073,10 +4070,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>465</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>466</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -4089,7 +4086,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -4105,10 +4102,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>468</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>469</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -4121,7 +4118,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -4137,10 +4134,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>471</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>472</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -4153,7 +4150,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -4169,10 +4166,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>474</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>475</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -4185,7 +4182,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -4201,10 +4198,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>477</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>478</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -4217,7 +4214,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -4233,10 +4230,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>480</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>481</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -4249,7 +4246,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -4265,10 +4262,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>483</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>484</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -4281,7 +4278,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -5676,10 +5673,10 @@
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="12" t="s">
         <v>149</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>150</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>8</v>
@@ -5705,19 +5702,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="C21" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="D21" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="E21" s="12" t="s">
         <v>154</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>155</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>4</v>
@@ -5743,17 +5740,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>156</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>157</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
         <v>94</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>16</v>
@@ -5779,17 +5776,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>159</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>160</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="E23" s="12" t="s">
         <v>161</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>162</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>17</v>
@@ -5815,17 +5812,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>163</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>164</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E24" s="12" t="s">
         <v>165</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>166</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>21</v>
@@ -5851,17 +5848,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>167</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>168</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>1</v>
@@ -5881,17 +5878,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>171</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="E26" s="17" t="s">
         <v>172</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>173</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>25</v>
@@ -5911,17 +5908,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>174</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>175</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="E27" s="17" t="s">
         <v>176</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>177</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>24</v>
@@ -5943,17 +5940,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>178</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>179</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>14</v>
@@ -6146,7 +6143,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6160,7 +6157,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6168,7 +6165,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6176,7 +6173,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6184,7 +6181,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6198,7 +6195,7 @@
         <v>22</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6206,7 +6203,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6214,7 +6211,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6222,7 +6219,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6288,17 +6285,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>190</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>191</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="E17" s="12" t="s">
         <v>192</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>193</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>8</v>
@@ -6310,7 +6307,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -6326,17 +6323,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>194</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>195</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="E18" s="12" t="s">
         <v>196</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>197</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>6</v>
@@ -6348,7 +6345,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -6364,17 +6361,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>198</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>199</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E19" s="12" t="s">
         <v>200</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>201</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>22</v>
@@ -6386,7 +6383,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -6402,17 +6399,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>202</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>203</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="E20" s="12" t="s">
         <v>204</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>205</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>5</v>
@@ -6424,7 +6421,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -6440,17 +6437,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>206</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>207</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>208</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>209</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>1</v>
@@ -6462,7 +6459,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12"/>
@@ -6472,17 +6469,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>211</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>212</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E22" s="17" t="s">
         <v>213</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>214</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>7</v>
@@ -6494,7 +6491,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12"/>
@@ -6504,17 +6501,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>215</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>216</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="E23" s="17" t="s">
         <v>217</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>218</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>10</v>
@@ -6526,7 +6523,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12"/>
@@ -6536,17 +6533,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>219</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>220</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E24" s="17" t="s">
         <v>221</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>222</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>17</v>
@@ -6558,7 +6555,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12"/>
@@ -6568,17 +6565,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>223</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>224</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E25" s="17" t="s">
         <v>225</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>226</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>21</v>
@@ -6590,7 +6587,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12"/>
@@ -6600,17 +6597,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>227</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>228</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="E26" s="11" t="s">
         <v>228</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>229</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>23</v>
@@ -6622,7 +6619,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
       <c r="K26" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12"/>
@@ -6632,17 +6629,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>230</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>231</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="E27" s="11" t="s">
         <v>232</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>233</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>24</v>
@@ -6654,7 +6651,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12"/>
@@ -6664,19 +6661,19 @@
     </row>
     <row r="28" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="C28" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="D28" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="E28" s="17" t="s">
         <v>237</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>238</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>18</v>
@@ -6690,7 +6687,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
       <c r="K28" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="12"/>
@@ -6700,17 +6697,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>239</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>240</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="E29" s="17" t="s">
         <v>241</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>242</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>20</v>
@@ -6722,7 +6719,7 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12"/>
@@ -6887,7 +6884,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6901,7 +6898,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6909,7 +6906,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6947,7 +6944,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7019,10 +7016,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>247</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>248</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -7035,7 +7032,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -7051,10 +7048,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>250</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>251</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -7067,7 +7064,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -7083,10 +7080,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>253</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>254</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -7099,7 +7096,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -7115,10 +7112,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>256</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>257</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -7131,7 +7128,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -7147,10 +7144,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>259</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>260</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -7163,7 +7160,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -7179,10 +7176,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>262</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>263</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -7195,7 +7192,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -7211,10 +7208,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>265</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>266</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -7227,7 +7224,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -7506,7 +7503,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7520,7 +7517,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7528,7 +7525,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7566,7 +7563,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7638,10 +7635,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>272</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>273</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -7654,7 +7651,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -7670,10 +7667,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>275</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>276</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -7686,7 +7683,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -7702,10 +7699,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>278</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>279</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -7718,7 +7715,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -7734,10 +7731,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>281</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>282</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -7750,7 +7747,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -7766,10 +7763,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>284</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>285</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -7782,7 +7779,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -7798,10 +7795,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>287</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>288</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -7814,7 +7811,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -7830,10 +7827,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>290</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>291</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -7846,7 +7843,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -7862,10 +7859,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>293</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>294</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -7878,7 +7875,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -7894,10 +7891,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>296</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>297</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -7910,7 +7907,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -7926,10 +7923,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>299</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>300</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
@@ -7942,7 +7939,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
       <c r="K26" s="12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12" t="s">
@@ -7958,10 +7955,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>302</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>303</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
@@ -7974,7 +7971,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12" t="s">
@@ -8181,7 +8178,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8195,7 +8192,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8203,7 +8200,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8241,7 +8238,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8313,10 +8310,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>309</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>310</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -8329,7 +8326,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -8345,10 +8342,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>312</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>313</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -8361,7 +8358,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -8377,10 +8374,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>315</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>316</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -8393,7 +8390,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -8409,10 +8406,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>318</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>319</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -8425,7 +8422,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -8441,10 +8438,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>321</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>322</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -8457,7 +8454,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -8473,10 +8470,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>324</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>325</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -8489,7 +8486,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -8505,10 +8502,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>327</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>328</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -8521,7 +8518,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -8537,10 +8534,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>330</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>331</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -8553,7 +8550,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -8569,10 +8566,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>333</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>334</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -8585,7 +8582,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -8828,7 +8825,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8842,7 +8839,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8850,7 +8847,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8888,7 +8885,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8960,10 +8957,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>340</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>341</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -8976,7 +8973,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -8992,10 +8989,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>343</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>344</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -9008,7 +9005,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -9024,10 +9021,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>346</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>347</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -9040,7 +9037,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -9056,10 +9053,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>349</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>350</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -9072,7 +9069,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -9088,10 +9085,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>352</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>353</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -9104,7 +9101,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -9120,10 +9117,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>355</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>356</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -9136,7 +9133,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -9152,10 +9149,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>358</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>359</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -9168,7 +9165,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -9447,7 +9444,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9461,7 +9458,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9469,7 +9466,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9507,7 +9504,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9579,10 +9576,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>365</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>366</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -9595,7 +9592,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -9611,10 +9608,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>368</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>369</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -9627,7 +9624,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -9643,10 +9640,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>371</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>372</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -9659,7 +9656,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -9675,10 +9672,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>374</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>375</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -9691,7 +9688,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -9707,10 +9704,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>377</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>378</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -9723,7 +9720,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -9739,10 +9736,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>380</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>381</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -9755,7 +9752,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -9771,10 +9768,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>383</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>384</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -9787,7 +9784,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -9803,10 +9800,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>386</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>387</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -9819,7 +9816,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -9835,10 +9832,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>389</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>390</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -9851,7 +9848,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">

--- a/D1_Fiches_Clubs_Joueurs_26_27.xlsx
+++ b/D1_Fiches_Clubs_Joueurs_26_27.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Mode emploi" sheetId="1" state="visible" r:id="rId3"/>
@@ -649,7 +649,7 @@
     <t xml:space="preserve">ZAHRY</t>
   </si>
   <si>
-    <t xml:space="preserve">geoffroey-dubois</t>
+    <t xml:space="preserve">geoffrey-dubois</t>
   </si>
   <si>
     <t xml:space="preserve">GEOFFREY DUBOIS</t>
@@ -1655,7 +1655,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1726,10 +1726,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -2548,22 +2544,22 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
@@ -2582,31 +2578,31 @@
       <c r="A36" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B36" s="20"/>
+      <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="20"/>
+      <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="20"/>
+      <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="20"/>
+      <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="20"/>
+      <c r="B40" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -3167,22 +3163,22 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
@@ -3201,31 +3197,31 @@
       <c r="A36" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B36" s="20"/>
+      <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="20"/>
+      <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="20"/>
+      <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="20"/>
+      <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="20"/>
+      <c r="B40" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -3786,22 +3782,22 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
@@ -3820,31 +3816,31 @@
       <c r="A36" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B36" s="20"/>
+      <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="20"/>
+      <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="20"/>
+      <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="20"/>
+      <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="20"/>
+      <c r="B40" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -4419,22 +4415,22 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
@@ -4453,31 +4449,31 @@
       <c r="A36" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B36" s="20"/>
+      <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="20"/>
+      <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="20"/>
+      <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="20"/>
+      <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="20"/>
+      <c r="B40" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -5212,10 +5208,10 @@
       <c r="P30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="11" t="s">
         <v>115</v>
       </c>
       <c r="C31" s="12"/>
@@ -5250,10 +5246,10 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="11" t="s">
         <v>119</v>
       </c>
       <c r="C32" s="12"/>
@@ -5288,22 +5284,22 @@
       <c r="P32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19"/>
-      <c r="O33" s="19"/>
-      <c r="P33" s="19"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="18"/>
+      <c r="P33" s="18"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
@@ -6023,22 +6019,22 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
@@ -6057,31 +6053,31 @@
       <c r="A36" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B36" s="20"/>
+      <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="20"/>
+      <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="20"/>
+      <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="20"/>
+      <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="20"/>
+      <c r="B40" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -6764,22 +6760,22 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
@@ -6798,31 +6794,31 @@
       <c r="A36" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B36" s="20"/>
+      <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="20"/>
+      <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="20"/>
+      <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="20"/>
+      <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="20"/>
+      <c r="B40" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -7383,22 +7379,22 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
@@ -7417,31 +7413,31 @@
       <c r="A36" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B36" s="20"/>
+      <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="20"/>
+      <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="20"/>
+      <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="20"/>
+      <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="20"/>
+      <c r="B40" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -8058,22 +8054,22 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
@@ -8092,31 +8088,31 @@
       <c r="A36" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B36" s="20"/>
+      <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="20"/>
+      <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="20"/>
+      <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="20"/>
+      <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="20"/>
+      <c r="B40" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -8705,22 +8701,22 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
@@ -8739,31 +8735,31 @@
       <c r="A36" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B36" s="20"/>
+      <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="20"/>
+      <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="20"/>
+      <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="20"/>
+      <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="20"/>
+      <c r="B40" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -9324,22 +9320,22 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
@@ -9358,31 +9354,31 @@
       <c r="A36" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B36" s="20"/>
+      <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="20"/>
+      <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="20"/>
+      <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="20"/>
+      <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="20"/>
+      <c r="B40" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -9971,22 +9967,22 @@
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
@@ -10005,31 +10001,31 @@
       <c r="A36" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B36" s="20"/>
+      <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="20"/>
+      <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="20"/>
+      <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="20"/>
+      <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="20"/>
+      <c r="B40" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="5">

--- a/D1_Fiches_Clubs_Joueurs_26_27.xlsx
+++ b/D1_Fiches_Clubs_Joueurs_26_27.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Mode emploi" sheetId="1" state="visible" r:id="rId3"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="534">
   <si>
     <t xml:space="preserve">FICHES CLUBS · D1 FUTSAL 2026-2027</t>
   </si>
@@ -331,6 +331,9 @@
     <t xml:space="preserve">Moussa</t>
   </si>
   <si>
+    <t xml:space="preserve">HADDAD </t>
+  </si>
+  <si>
     <t xml:space="preserve">wassim-si-chaib</t>
   </si>
   <si>
@@ -661,7 +664,7 @@
     <t xml:space="preserve">DUBOIS</t>
   </si>
   <si>
-    <t xml:space="preserve">geoffroey-dubois.png</t>
+    <t xml:space="preserve">geoffrey-dubois.png</t>
   </si>
   <si>
     <t xml:space="preserve">yacine-kasmi </t>
@@ -1132,15 +1135,33 @@
     <t xml:space="preserve">FRANCISCO VALDELVIRA JIMENEZ</t>
   </si>
   <si>
+    <t xml:space="preserve">Valdelvira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALDELVIRA JIMENEZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">francisco-valdelvira-jimenez.jpg</t>
   </si>
   <si>
+    <t xml:space="preserve">site internet NMF</t>
+  </si>
+  <si>
     <t xml:space="preserve">michael-de-sa-andrade</t>
   </si>
   <si>
     <t xml:space="preserve">MICHAEL DE SA ANDRADE</t>
   </si>
   <si>
+    <t xml:space="preserve">MICHAEL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DE SA ANDRADE</t>
+  </si>
+  <si>
     <t xml:space="preserve">michael-de-sa-andrade.jpg</t>
   </si>
   <si>
@@ -1150,6 +1171,31 @@
     <t xml:space="preserve">EDUARDO RIANO GARCIA</t>
   </si>
   <si>
+    <t xml:space="preserve">Chuky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDUARDO </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">RIANO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> GARCIA</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">eduardo-riano-garcia.jpg</t>
   </si>
   <si>
@@ -1159,6 +1205,12 @@
     <t xml:space="preserve">JOY MINGOLO</t>
   </si>
   <si>
+    <t xml:space="preserve">JOY </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MINGOLO</t>
+  </si>
+  <si>
     <t xml:space="preserve">joy-mingolo.jpg</t>
   </si>
   <si>
@@ -1168,6 +1220,31 @@
     <t xml:space="preserve">LEONARDO ALMEIDA ROSA</t>
   </si>
   <si>
+    <t xml:space="preserve">Leozinho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEONARDO </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">ALMEIDA </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ROSA</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">leonardo-almeida-rosa.jpg</t>
   </si>
   <si>
@@ -1177,6 +1254,9 @@
     <t xml:space="preserve">MBEMBA SACKO</t>
   </si>
   <si>
+    <t xml:space="preserve">MBEMBA </t>
+  </si>
+  <si>
     <t xml:space="preserve">mbemba-sacko.jpg</t>
   </si>
   <si>
@@ -1186,6 +1266,12 @@
     <t xml:space="preserve">OTHMANE EL HOKARI</t>
   </si>
   <si>
+    <t xml:space="preserve">OTHMANE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL HOKARI</t>
+  </si>
+  <si>
     <t xml:space="preserve">othmane-el-hokari.jpg</t>
   </si>
   <si>
@@ -1195,6 +1281,12 @@
     <t xml:space="preserve">DAVID VELASCO GONZALEZ</t>
   </si>
   <si>
+    <t xml:space="preserve">DAVID VELASCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GONZALEZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">david-velasco-gonzalez.jpg</t>
   </si>
   <si>
@@ -1204,7 +1296,180 @@
     <t xml:space="preserve">STEVE BENDALI</t>
   </si>
   <si>
+    <t xml:space="preserve">STEVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BENDALI</t>
+  </si>
+  <si>
     <t xml:space="preserve">steve-bendali.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">malo-botella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALO BOTELLA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTELLA </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">malo-botella</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">.jpg</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">mustapha-rabou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUSTAPHA RABOU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUSTAPHA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RABOU </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">mustapha-rabou</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">.jpg</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">thibaut-garros </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THIBAUT GARROS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THIBAUT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARROS </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">thibaut-garros</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">.jpg</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">maxime-santagata </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAXIME SANTAGATA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAXIME </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTAGATA </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">maxime-santagata</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">.jpg</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">michal-hula </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICHAL HULA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICHAL  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HULA </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">michal-hula</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">.jpg</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">renatinho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENATINHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">renatinho.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">FICHE CLUB · NICE</t>
@@ -1496,7 +1761,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1585,6 +1850,17 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1655,7 +1931,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1734,6 +2010,14 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2087,7 +2371,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>391</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2101,7 +2385,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>392</v>
+        <v>441</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2109,7 +2393,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>393</v>
+        <v>442</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2147,7 +2431,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>394</v>
+        <v>443</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2211,18 +2495,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>395</v>
+        <v>444</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>396</v>
+        <v>445</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -2235,7 +2519,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>397</v>
+        <v>446</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -2251,10 +2535,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>398</v>
+        <v>447</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>399</v>
+        <v>448</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -2267,7 +2551,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>400</v>
+        <v>449</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -2283,10 +2567,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>401</v>
+        <v>450</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>402</v>
+        <v>451</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -2299,7 +2583,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>403</v>
+        <v>452</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -2315,10 +2599,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>404</v>
+        <v>453</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>405</v>
+        <v>454</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -2331,7 +2615,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>406</v>
+        <v>455</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -2563,12 +2847,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -2576,7 +2860,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B36" s="19"/>
     </row>
@@ -2588,13 +2872,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B39" s="19"/>
     </row>
@@ -2664,7 +2948,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>407</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2678,7 +2962,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>408</v>
+        <v>457</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2686,7 +2970,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>409</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2724,7 +3008,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>410</v>
+        <v>459</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2788,18 +3072,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>411</v>
+        <v>460</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>412</v>
+        <v>461</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -2812,7 +3096,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>413</v>
+        <v>462</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -2828,10 +3112,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>414</v>
+        <v>463</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>415</v>
+        <v>464</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -2844,7 +3128,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>416</v>
+        <v>465</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -2860,10 +3144,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>417</v>
+        <v>466</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>418</v>
+        <v>467</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -2876,7 +3160,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>419</v>
+        <v>468</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -2892,10 +3176,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>420</v>
+        <v>469</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>421</v>
+        <v>470</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -2908,7 +3192,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>422</v>
+        <v>471</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -2924,10 +3208,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>423</v>
+        <v>472</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>424</v>
+        <v>473</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -2940,7 +3224,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>425</v>
+        <v>474</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -2956,10 +3240,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>426</v>
+        <v>475</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>427</v>
+        <v>476</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -2972,7 +3256,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>428</v>
+        <v>477</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -2988,10 +3272,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>429</v>
+        <v>478</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>430</v>
+        <v>479</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -3004,7 +3288,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>431</v>
+        <v>480</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -3182,12 +3466,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -3195,7 +3479,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B36" s="19"/>
     </row>
@@ -3207,13 +3491,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B39" s="19"/>
     </row>
@@ -3283,7 +3567,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>432</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3297,7 +3581,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>433</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3305,7 +3589,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>434</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3343,7 +3627,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>435</v>
+        <v>484</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3407,18 +3691,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>436</v>
+        <v>485</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>437</v>
+        <v>486</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -3431,7 +3715,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>438</v>
+        <v>487</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -3447,10 +3731,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>439</v>
+        <v>488</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>440</v>
+        <v>489</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -3463,7 +3747,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>441</v>
+        <v>490</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -3479,10 +3763,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>442</v>
+        <v>491</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>443</v>
+        <v>492</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -3495,7 +3779,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>444</v>
+        <v>493</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -3511,10 +3795,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>445</v>
+        <v>494</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>446</v>
+        <v>495</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -3527,7 +3811,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>447</v>
+        <v>496</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -3543,10 +3827,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>448</v>
+        <v>497</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>449</v>
+        <v>498</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -3559,7 +3843,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>450</v>
+        <v>499</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -3575,10 +3859,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>451</v>
+        <v>500</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>452</v>
+        <v>501</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -3591,7 +3875,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>453</v>
+        <v>502</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -3607,10 +3891,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>454</v>
+        <v>503</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>455</v>
+        <v>504</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -3623,7 +3907,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>456</v>
+        <v>505</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -3801,12 +4085,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -3814,7 +4098,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B36" s="19"/>
     </row>
@@ -3826,13 +4110,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B39" s="19"/>
     </row>
@@ -3902,7 +4186,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>457</v>
+        <v>506</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3916,7 +4200,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>458</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3924,7 +4208,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>459</v>
+        <v>508</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3962,7 +4246,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>460</v>
+        <v>509</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4026,18 +4310,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>461</v>
+        <v>510</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>462</v>
+        <v>511</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -4050,7 +4334,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>463</v>
+        <v>512</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -4066,10 +4350,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>464</v>
+        <v>513</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>465</v>
+        <v>514</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -4082,7 +4366,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>466</v>
+        <v>515</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -4098,10 +4382,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>467</v>
+        <v>516</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>468</v>
+        <v>517</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -4114,7 +4398,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>469</v>
+        <v>518</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -4130,10 +4414,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>470</v>
+        <v>519</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>471</v>
+        <v>520</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -4146,7 +4430,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>472</v>
+        <v>521</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -4162,10 +4446,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>473</v>
+        <v>522</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>474</v>
+        <v>523</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -4178,7 +4462,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>475</v>
+        <v>524</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -4194,10 +4478,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>476</v>
+        <v>525</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>477</v>
+        <v>526</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -4210,7 +4494,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>478</v>
+        <v>527</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -4226,10 +4510,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>479</v>
+        <v>528</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>480</v>
+        <v>529</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -4242,7 +4526,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>481</v>
+        <v>530</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -4258,10 +4542,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>482</v>
+        <v>531</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>483</v>
+        <v>532</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -4274,7 +4558,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>484</v>
+        <v>533</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -4434,12 +4718,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -4447,7 +4731,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B36" s="19"/>
     </row>
@@ -4459,13 +4743,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B39" s="19"/>
     </row>
@@ -5065,7 +5349,7 @@
         <v>98</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>17</v>
@@ -5093,17 +5377,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>20</v>
@@ -5115,7 +5399,7 @@
         <v>54</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J28" s="12" t="s">
         <v>60</v>
@@ -5131,17 +5415,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>23</v>
@@ -5169,19 +5453,19 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>5</v>
@@ -5196,7 +5480,7 @@
         <v>52</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K30" s="12"/>
       <c r="L30" s="12"/>
@@ -5209,17 +5493,17 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>7</v>
@@ -5247,17 +5531,17 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C32" s="12"/>
       <c r="D32" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>11</v>
@@ -5303,12 +5587,12 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>32</v>
@@ -5316,7 +5600,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B37" s="17" t="s">
         <v>79</v>
@@ -5332,7 +5616,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B39" s="17" t="s">
         <v>71</v>
@@ -5340,7 +5624,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>46</v>
@@ -5414,7 +5698,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5428,7 +5712,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5436,7 +5720,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5444,7 +5728,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5452,7 +5736,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5466,7 +5750,7 @@
         <v>22</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5474,7 +5758,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5482,7 +5766,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5546,25 +5830,25 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
@@ -5590,17 +5874,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
         <v>77</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>7</v>
@@ -5626,17 +5910,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>13</v>
@@ -5662,17 +5946,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
         <v>98</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>8</v>
@@ -5698,19 +5982,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>4</v>
@@ -5736,17 +6020,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
         <v>94</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>16</v>
@@ -5772,17 +6056,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>17</v>
@@ -5808,17 +6092,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>21</v>
@@ -5844,17 +6128,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>1</v>
@@ -5874,17 +6158,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>25</v>
@@ -5904,17 +6188,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>24</v>
@@ -5924,7 +6208,7 @@
         <v>51</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J27" s="12"/>
       <c r="K27" s="12"/>
@@ -5936,17 +6220,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>14</v>
@@ -6038,12 +6322,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -6051,7 +6335,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B36" s="19"/>
     </row>
@@ -6063,13 +6347,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B39" s="19"/>
     </row>
@@ -6139,7 +6423,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6153,7 +6437,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6161,7 +6445,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6169,7 +6453,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6177,7 +6461,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6191,7 +6475,7 @@
         <v>22</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6199,7 +6483,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6207,7 +6491,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6215,7 +6499,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6273,25 +6557,25 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>8</v>
@@ -6303,7 +6587,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -6319,17 +6603,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>6</v>
@@ -6341,7 +6625,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -6357,17 +6641,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>22</v>
@@ -6379,7 +6663,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -6395,17 +6679,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>5</v>
@@ -6417,7 +6701,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -6433,17 +6717,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>1</v>
@@ -6455,7 +6739,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12"/>
@@ -6465,17 +6749,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>7</v>
@@ -6487,7 +6771,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12"/>
@@ -6497,17 +6781,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>10</v>
@@ -6519,7 +6803,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12"/>
@@ -6529,17 +6813,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>17</v>
@@ -6551,7 +6835,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12"/>
@@ -6561,17 +6845,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>21</v>
@@ -6583,7 +6867,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12"/>
@@ -6593,17 +6877,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>23</v>
@@ -6615,7 +6899,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
       <c r="K26" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12"/>
@@ -6625,17 +6909,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>24</v>
@@ -6647,7 +6931,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12"/>
@@ -6657,19 +6941,19 @@
     </row>
     <row r="28" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>18</v>
@@ -6683,7 +6967,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
       <c r="K28" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="12"/>
@@ -6693,17 +6977,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>20</v>
@@ -6715,7 +6999,7 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12"/>
@@ -6779,12 +7063,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -6792,7 +7076,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B36" s="19"/>
     </row>
@@ -6804,13 +7088,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B39" s="19"/>
     </row>
@@ -6880,7 +7164,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6894,7 +7178,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6902,7 +7186,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6940,7 +7224,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7004,18 +7288,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -7028,7 +7312,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -7044,10 +7328,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -7060,7 +7344,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -7076,10 +7360,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -7092,7 +7376,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -7108,10 +7392,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -7124,7 +7408,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -7140,10 +7424,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -7156,7 +7440,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -7172,10 +7456,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -7188,7 +7472,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -7204,10 +7488,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -7220,7 +7504,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -7398,12 +7682,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -7411,7 +7695,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B36" s="19"/>
     </row>
@@ -7423,13 +7707,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B39" s="19"/>
     </row>
@@ -7499,7 +7783,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7513,7 +7797,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7521,7 +7805,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7559,7 +7843,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7623,18 +7907,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -7647,7 +7931,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -7663,10 +7947,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -7679,7 +7963,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -7695,10 +7979,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -7711,7 +7995,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -7727,10 +8011,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -7743,7 +8027,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -7759,10 +8043,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -7775,7 +8059,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -7791,10 +8075,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -7807,7 +8091,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -7823,10 +8107,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -7839,7 +8123,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -7855,10 +8139,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -7871,7 +8155,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -7887,10 +8171,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -7903,7 +8187,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -7919,10 +8203,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
@@ -7935,7 +8219,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
       <c r="K26" s="12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12" t="s">
@@ -7951,10 +8235,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
@@ -7967,7 +8251,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12" t="s">
@@ -8073,12 +8357,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -8086,7 +8370,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B36" s="19"/>
     </row>
@@ -8098,13 +8382,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B39" s="19"/>
     </row>
@@ -8174,7 +8458,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8188,7 +8472,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8196,7 +8480,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8234,7 +8518,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8298,18 +8582,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -8322,7 +8606,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -8338,10 +8622,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -8354,7 +8638,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -8370,10 +8654,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -8386,7 +8670,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -8402,10 +8686,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -8418,7 +8702,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -8434,10 +8718,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -8450,7 +8734,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -8466,10 +8750,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -8482,7 +8766,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -8498,10 +8782,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -8514,7 +8798,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -8530,10 +8814,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -8546,7 +8830,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -8562,10 +8846,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -8578,7 +8862,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -8720,12 +9004,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -8733,7 +9017,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B36" s="19"/>
     </row>
@@ -8745,13 +9029,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B39" s="19"/>
     </row>
@@ -8821,7 +9105,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8835,7 +9119,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8843,7 +9127,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8881,7 +9165,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8945,18 +9229,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -8969,7 +9253,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -8985,10 +9269,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -9001,7 +9285,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -9017,10 +9301,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -9033,7 +9317,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -9049,10 +9333,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -9065,7 +9349,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -9081,10 +9365,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -9097,7 +9381,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -9113,10 +9397,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -9129,7 +9413,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -9145,10 +9429,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -9161,7 +9445,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -9339,12 +9623,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -9352,7 +9636,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B36" s="19"/>
     </row>
@@ -9364,13 +9648,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B39" s="19"/>
     </row>
@@ -9419,7 +9703,7 @@
     <tabColor rgb="FF111111"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -9440,7 +9724,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9454,7 +9738,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9462,7 +9746,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9500,7 +9784,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9560,411 +9844,613 @@
       <c r="M16" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="N16" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="O16" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="P16" s="13" t="s">
-        <v>135</v>
-      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
+        <v>366</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>66</v>
+      </c>
       <c r="H17" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="12"/>
+      <c r="I17" s="12" t="s">
+        <v>52</v>
+      </c>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="L17" s="12"/>
+        <v>370</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>371</v>
+      </c>
       <c r="M17" s="12" t="s">
         <v>54</v>
       </c>
       <c r="N17" s="12"/>
-      <c r="O17" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="P17" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
+      <c r="D18" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>59</v>
+      </c>
       <c r="H18" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="12"/>
+      <c r="I18" s="12" t="s">
+        <v>52</v>
+      </c>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="L18" s="12"/>
+        <v>376</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>371</v>
+      </c>
       <c r="M18" s="12" t="s">
         <v>54</v>
       </c>
       <c r="N18" s="12"/>
-      <c r="O18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
+        <v>378</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>381</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>50</v>
+      </c>
       <c r="H19" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="I19" s="12"/>
+      <c r="I19" s="12" t="s">
+        <v>52</v>
+      </c>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="L19" s="12"/>
+        <v>382</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>371</v>
+      </c>
       <c r="M19" s="12" t="s">
         <v>54</v>
       </c>
       <c r="N19" s="12"/>
-      <c r="O19" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="P19" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
+      <c r="D20" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>59</v>
+      </c>
       <c r="H20" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="12"/>
+      <c r="I20" s="12" t="s">
+        <v>52</v>
+      </c>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="L20" s="12"/>
+        <v>387</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>371</v>
+      </c>
       <c r="M20" s="12" t="s">
         <v>54</v>
       </c>
       <c r="N20" s="12"/>
-      <c r="O20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
+        <v>389</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>392</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>50</v>
+      </c>
       <c r="H21" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="I21" s="12"/>
+      <c r="I21" s="12" t="s">
+        <v>104</v>
+      </c>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="L21" s="12"/>
+        <v>393</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>371</v>
+      </c>
       <c r="M21" s="12" t="s">
         <v>54</v>
       </c>
       <c r="N21" s="12"/>
-      <c r="O21" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
+      <c r="D22" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>50</v>
+      </c>
       <c r="H22" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="12"/>
+      <c r="I22" s="12" t="s">
+        <v>52</v>
+      </c>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="L22" s="12"/>
+        <v>397</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>371</v>
+      </c>
       <c r="M22" s="12" t="s">
         <v>54</v>
       </c>
       <c r="N22" s="12"/>
-      <c r="O22" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="P22" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
+      <c r="D23" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>59</v>
+      </c>
       <c r="H23" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="12"/>
+      <c r="I23" s="12" t="s">
+        <v>52</v>
+      </c>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="L23" s="12"/>
+        <v>402</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>371</v>
+      </c>
       <c r="M23" s="12" t="s">
         <v>54</v>
       </c>
       <c r="N23" s="12"/>
-      <c r="O23" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P23" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="O23" s="14"/>
+      <c r="P23" s="14"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
+      <c r="D24" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>50</v>
+      </c>
       <c r="H24" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="12"/>
+      <c r="I24" s="12" t="s">
+        <v>104</v>
+      </c>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="L24" s="12"/>
+        <v>407</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>371</v>
+      </c>
       <c r="M24" s="12" t="s">
         <v>54</v>
       </c>
       <c r="N24" s="12"/>
-      <c r="O24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
+      <c r="D25" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>50</v>
+      </c>
       <c r="H25" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="I25" s="12"/>
+      <c r="I25" s="12" t="s">
+        <v>104</v>
+      </c>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>390</v>
-      </c>
-      <c r="L25" s="12"/>
+        <v>412</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>371</v>
+      </c>
       <c r="M25" s="12" t="s">
         <v>54</v>
       </c>
       <c r="N25" s="12"/>
-      <c r="O25" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="O25" s="14"/>
+      <c r="P25" s="14"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15"/>
-      <c r="B26" s="12"/>
+      <c r="A26" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>414</v>
+      </c>
       <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
+      <c r="D26" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="G26" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>52</v>
+      </c>
       <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
+      <c r="K26" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="N26" s="12"/>
       <c r="O26" s="12"/>
       <c r="P26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15"/>
-      <c r="B27" s="12"/>
+      <c r="A27" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>418</v>
+      </c>
       <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
+      <c r="D27" s="21" t="s">
+        <v>419</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>52</v>
+      </c>
       <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
+      <c r="K27" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="M27" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="N27" s="12"/>
       <c r="O27" s="12"/>
       <c r="P27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15"/>
-      <c r="B28" s="12"/>
+      <c r="A28" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>423</v>
+      </c>
       <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
+      <c r="D28" s="21" t="s">
+        <v>424</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>425</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>52</v>
+      </c>
       <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
+      <c r="K28" s="21" t="s">
+        <v>426</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="M28" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="N28" s="12"/>
       <c r="O28" s="12"/>
       <c r="P28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
+      <c r="A29" s="21" t="s">
+        <v>427</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>428</v>
+      </c>
+      <c r="C29" s="0"/>
+      <c r="D29" s="21" t="s">
+        <v>429</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>430</v>
+      </c>
+      <c r="F29" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J29" s="0"/>
+      <c r="K29" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="L29" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="M29" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="N29" s="0"/>
+      <c r="O29" s="0"/>
+      <c r="P29" s="0"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="12"/>
-      <c r="P30" s="12"/>
+      <c r="A30" s="21" t="s">
+        <v>432</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="C30" s="0"/>
+      <c r="D30" s="21" t="s">
+        <v>434</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>435</v>
+      </c>
+      <c r="F30" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="G30" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J30" s="0"/>
+      <c r="K30" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="M30" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="N30" s="0"/>
+      <c r="O30" s="0"/>
+      <c r="P30" s="0"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12"/>
+      <c r="A31" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="C31" s="0"/>
+      <c r="D31" s="0"/>
+      <c r="E31" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="F31" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="G31" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="H31" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="I31" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="J31" s="0"/>
+      <c r="K31" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="M31" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="N31" s="0"/>
+      <c r="O31" s="0"/>
+      <c r="P31" s="0"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="18"/>
@@ -9986,12 +10472,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -9999,54 +10485,96 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B36" s="19"/>
+        <v>124</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="19"/>
+      <c r="B37" s="12" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B38" s="19"/>
+        <v>125</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>365</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B39" s="19"/>
+        <v>126</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="19"/>
+      <c r="B40" s="15" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0"/>
+      <c r="B41" s="0"/>
+      <c r="C41" s="0"/>
+      <c r="D41" s="0"/>
+      <c r="E41" s="0"/>
+      <c r="F41" s="0"/>
+      <c r="G41" s="0"/>
+      <c r="H41" s="0"/>
+      <c r="I41" s="0"/>
+      <c r="J41" s="0"/>
+      <c r="K41" s="0"/>
+      <c r="L41" s="0"/>
+      <c r="M41" s="0"/>
+      <c r="N41" s="0"/>
+      <c r="O41" s="0"/>
+      <c r="P41" s="0"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0"/>
+      <c r="B42" s="0"/>
+      <c r="C42" s="0"/>
+      <c r="D42" s="0"/>
+      <c r="E42" s="0"/>
+      <c r="F42" s="0"/>
+      <c r="G42" s="0"/>
+      <c r="H42" s="0"/>
+      <c r="I42" s="0"/>
+      <c r="J42" s="0"/>
+      <c r="K42" s="0"/>
+      <c r="L42" s="0"/>
+      <c r="M42" s="0"/>
+      <c r="N42" s="0"/>
+      <c r="O42" s="0"/>
+      <c r="P42" s="0"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G17:G31" type="list">
+  <dataValidations count="4">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G17:G25 G27 G29" type="list">
       <formula1>"Gardien,Fixo,Ailier,Pivot,Universel"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H17:H31" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H17:H30" type="list">
       <formula1>"oui,non"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I17:I31" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I17:I30" type="list">
       <formula1>"Droit,Gauche,Les deux"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M17:M31" type="list">
       <formula1>"oui,non"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B36:B40" type="list">
-      <formula1>$A$17:$A$31</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/D1_Fiches_Clubs_Joueurs_26_27.xlsx
+++ b/D1_Fiches_Clubs_Joueurs_26_27.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Mode emploi" sheetId="1" state="visible" r:id="rId3"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="579">
   <si>
     <t xml:space="preserve">FICHES CLUBS · D1 FUTSAL 2026-2027</t>
   </si>
@@ -196,6 +196,9 @@
     <t xml:space="preserve">Français</t>
   </si>
   <si>
+    <t xml:space="preserve">Instagram PARIS ACASA</t>
+  </si>
+  <si>
     <t xml:space="preserve">oui</t>
   </si>
   <si>
@@ -1142,6 +1145,9 @@
   </si>
   <si>
     <t xml:space="preserve">VALDELVIRA JIMENEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espagnol</t>
   </si>
   <si>
     <t xml:space="preserve">francisco-valdelvira-jimenez.jpg</t>
@@ -1196,6 +1202,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Colombien</t>
+  </si>
+  <si>
     <t xml:space="preserve">eduardo-riano-garcia.jpg</t>
   </si>
   <si>
@@ -1243,6 +1252,9 @@
       </rPr>
       <t xml:space="preserve">ROSA</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Brésilien</t>
   </si>
   <si>
     <t xml:space="preserve">leonardo-almeida-rosa.jpg</t>
@@ -1442,6 +1454,9 @@
     <t xml:space="preserve">HULA </t>
   </si>
   <si>
+    <t xml:space="preserve">Tchèque</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1538,15 +1553,30 @@
     <t xml:space="preserve">FRANCISCO MARTINEZ VILLALBA</t>
   </si>
   <si>
+    <t xml:space="preserve">MARTINEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paraguayen</t>
+  </si>
+  <si>
     <t xml:space="preserve">francisco-martinez-villalba.jpg</t>
   </si>
   <si>
+    <t xml:space="preserve">site internet SPORTING PARIS</t>
+  </si>
+  <si>
     <t xml:space="preserve">sid-ahmed-belhaj</t>
   </si>
   <si>
     <t xml:space="preserve">SID AHMED BELHAJ</t>
   </si>
   <si>
+    <t xml:space="preserve">SID </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BELHAJ</t>
+  </si>
+  <si>
     <t xml:space="preserve">sid-ahmed-belhaj.jpg</t>
   </si>
   <si>
@@ -1556,6 +1586,12 @@
     <t xml:space="preserve">ANAS DAHANI</t>
   </si>
   <si>
+    <t xml:space="preserve">ANAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAHANI</t>
+  </si>
+  <si>
     <t xml:space="preserve">anas-dahani.jpg</t>
   </si>
   <si>
@@ -1565,6 +1601,12 @@
     <t xml:space="preserve">ARTHUR TCHAPTCHET TCHATO</t>
   </si>
   <si>
+    <t xml:space="preserve">ARTHUR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCHAPTCHET</t>
+  </si>
+  <si>
     <t xml:space="preserve">arthur-tchaptchet-tchato.jpg</t>
   </si>
   <si>
@@ -1574,6 +1616,12 @@
     <t xml:space="preserve">AL MAHDI AISSI</t>
   </si>
   <si>
+    <t xml:space="preserve">AL MAHDI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AISSI</t>
+  </si>
+  <si>
     <t xml:space="preserve">al-mahdi-aissi.jpg</t>
   </si>
   <si>
@@ -1583,6 +1631,12 @@
     <t xml:space="preserve">ALDO AMARILLA ORTIZ</t>
   </si>
   <si>
+    <t xml:space="preserve">ALDO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMARILLA </t>
+  </si>
+  <si>
     <t xml:space="preserve">aldo-amarilla-ortiz.jpg</t>
   </si>
   <si>
@@ -1592,7 +1646,168 @@
     <t xml:space="preserve">CAIO DOS SANTOS</t>
   </si>
   <si>
+    <t xml:space="preserve">CAIO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOS SANTOS</t>
+  </si>
+  <si>
     <t xml:space="preserve">caio-dos-santos.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">francis-lokoka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCIS-LOKOKA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOKOKA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">francis-lokoka</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">.jpg</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">walid-mehdaoui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WALID-MEHDAOUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WALID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEHDAOUI</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">walid-mehdaoui</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">.jpg</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">danny-lefoulon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANNY-LEFOULON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANNY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEFOULON</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">danny-lefoulon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">.jpg</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">damian-mareco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAMIAN-MARECO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAMIAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARECO</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">damian-mareco</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">.jpg</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">steven-ndukuta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STEVEN-NDUKUTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STEVEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUKUTA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">steven-ndukuta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">.jpg</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">FICHE CLUB · TOULON</t>
@@ -2371,7 +2586,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2385,7 +2600,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2393,7 +2608,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2431,7 +2646,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2495,18 +2710,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -2519,11 +2734,11 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N17" s="12"/>
       <c r="O17" s="14" t="n">
@@ -2535,10 +2750,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -2551,11 +2766,11 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N18" s="12"/>
       <c r="O18" s="14" t="n">
@@ -2567,10 +2782,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -2583,11 +2798,11 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N19" s="12"/>
       <c r="O19" s="14" t="n">
@@ -2599,10 +2814,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -2615,11 +2830,11 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N20" s="12"/>
       <c r="O20" s="14" t="n">
@@ -2847,12 +3062,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -2860,31 +3075,31 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B40" s="19"/>
     </row>
@@ -2948,7 +3163,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2962,7 +3177,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2970,7 +3185,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3008,7 +3223,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3068,326 +3283,488 @@
       <c r="M16" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="N16" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="O16" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="P16" s="13" t="s">
-        <v>136</v>
-      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
+      <c r="D17" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>11</v>
+      </c>
       <c r="G17" s="12"/>
       <c r="H17" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
+      <c r="I17" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>468</v>
+      </c>
       <c r="K17" s="12" t="s">
-        <v>462</v>
-      </c>
-      <c r="L17" s="12"/>
+        <v>469</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>470</v>
+      </c>
       <c r="M17" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N17" s="12"/>
-      <c r="O17" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="P17" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
+      <c r="D18" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>8</v>
+      </c>
       <c r="G18" s="12"/>
       <c r="H18" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
+      <c r="I18" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="K18" s="12" t="s">
-        <v>465</v>
-      </c>
-      <c r="L18" s="12"/>
+        <v>475</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>470</v>
+      </c>
       <c r="M18" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N18" s="12"/>
-      <c r="O18" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="P18" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
+      <c r="D19" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>10</v>
+      </c>
       <c r="G19" s="12"/>
       <c r="H19" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
+      <c r="I19" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>115</v>
+      </c>
       <c r="K19" s="12" t="s">
-        <v>468</v>
-      </c>
-      <c r="L19" s="12"/>
+        <v>480</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>470</v>
+      </c>
       <c r="M19" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N19" s="12"/>
-      <c r="O19" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="P19" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
+      <c r="D20" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>5</v>
+      </c>
       <c r="G20" s="12"/>
       <c r="H20" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
+      <c r="I20" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="K20" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="L20" s="12"/>
+        <v>485</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>470</v>
+      </c>
       <c r="M20" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N20" s="12"/>
-      <c r="O20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
+      <c r="D21" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>2</v>
+      </c>
       <c r="G21" s="12"/>
       <c r="H21" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
+      <c r="I21" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>115</v>
+      </c>
       <c r="K21" s="12" t="s">
-        <v>474</v>
-      </c>
-      <c r="L21" s="12"/>
+        <v>490</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>470</v>
+      </c>
       <c r="M21" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N21" s="12"/>
-      <c r="O21" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
+      <c r="D22" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>494</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>15</v>
+      </c>
       <c r="G22" s="12"/>
       <c r="H22" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
+      <c r="I22" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>468</v>
+      </c>
       <c r="K22" s="12" t="s">
-        <v>477</v>
-      </c>
-      <c r="L22" s="12"/>
+        <v>495</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>470</v>
+      </c>
       <c r="M22" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N22" s="12"/>
-      <c r="O22" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="P22" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>479</v>
-      </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
+        <v>497</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>19</v>
+      </c>
       <c r="G23" s="12"/>
       <c r="H23" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
+      <c r="I23" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>396</v>
+      </c>
       <c r="K23" s="12" t="s">
-        <v>480</v>
-      </c>
-      <c r="L23" s="12"/>
+        <v>500</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>470</v>
+      </c>
       <c r="M23" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N23" s="12"/>
-      <c r="O23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="14" t="n">
+      <c r="O23" s="14"/>
+      <c r="P23" s="14"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="15" t="s">
+        <v>501</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="C24" s="12"/>
+      <c r="D24" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>504</v>
+      </c>
+      <c r="F24" s="12" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
       <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
+      <c r="H24" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>505</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="M24" s="12" t="s">
+        <v>55</v>
+      </c>
       <c r="N24" s="12"/>
       <c r="O24" s="12"/>
       <c r="P24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15"/>
-      <c r="B25" s="12"/>
+      <c r="A25" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>507</v>
+      </c>
       <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
+      <c r="D25" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>509</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>20</v>
+      </c>
       <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
+      <c r="H25" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>510</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="M25" s="12" t="s">
+        <v>55</v>
+      </c>
       <c r="N25" s="12"/>
       <c r="O25" s="12"/>
       <c r="P25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15"/>
-      <c r="B26" s="12"/>
+      <c r="A26" s="15" t="s">
+        <v>511</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>512</v>
+      </c>
       <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
+      <c r="D26" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>514</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>25</v>
+      </c>
       <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
+      <c r="H26" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>515</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>55</v>
+      </c>
       <c r="N26" s="12"/>
       <c r="O26" s="12"/>
       <c r="P26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15"/>
-      <c r="B27" s="12"/>
+      <c r="A27" s="15" t="s">
+        <v>516</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>517</v>
+      </c>
       <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
+      <c r="D27" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>3</v>
+      </c>
       <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
+      <c r="H27" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>520</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="M27" s="12" t="s">
+        <v>55</v>
+      </c>
       <c r="N27" s="12"/>
       <c r="O27" s="12"/>
       <c r="P27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15"/>
-      <c r="B28" s="12"/>
+      <c r="A28" s="15" t="s">
+        <v>521</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>522</v>
+      </c>
       <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
+      <c r="D28" s="15" t="s">
+        <v>523</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>17</v>
+      </c>
       <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
+      <c r="H28" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>525</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="M28" s="12" t="s">
+        <v>55</v>
+      </c>
       <c r="N28" s="12"/>
       <c r="O28" s="12"/>
       <c r="P28" s="12"/>
@@ -3466,12 +3843,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -3479,36 +3856,46 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B36" s="19"/>
+        <v>125</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>501</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B37" s="19"/>
+        <v>60</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>471</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B38" s="19"/>
+        <v>126</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>476</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B39" s="19"/>
+        <v>127</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>496</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B40" s="19"/>
+        <v>67</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>481</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="4">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G17:G31" type="list">
       <formula1>"Gardien,Fixo,Ailier,Pivot,Universel"</formula1>
       <formula2>0</formula2>
@@ -3523,10 +3910,6 @@
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M17:M31" type="list">
       <formula1>"oui,non"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B36:B40" type="list">
-      <formula1>$A$17:$A$31</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -3567,7 +3950,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>481</v>
+        <v>526</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3581,7 +3964,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>482</v>
+        <v>527</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3589,7 +3972,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>483</v>
+        <v>528</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3627,7 +4010,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>484</v>
+        <v>529</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3691,18 +4074,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>485</v>
+        <v>530</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>486</v>
+        <v>531</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -3715,11 +4098,11 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>487</v>
+        <v>532</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N17" s="12"/>
       <c r="O17" s="14" t="n">
@@ -3731,10 +4114,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>488</v>
+        <v>533</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>489</v>
+        <v>534</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -3747,11 +4130,11 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>490</v>
+        <v>535</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N18" s="12"/>
       <c r="O18" s="14" t="n">
@@ -3763,10 +4146,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>491</v>
+        <v>536</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>492</v>
+        <v>537</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -3779,11 +4162,11 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>493</v>
+        <v>538</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N19" s="12"/>
       <c r="O19" s="14" t="n">
@@ -3795,10 +4178,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>494</v>
+        <v>539</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>495</v>
+        <v>540</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -3811,11 +4194,11 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>496</v>
+        <v>541</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N20" s="12"/>
       <c r="O20" s="14" t="n">
@@ -3827,10 +4210,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>497</v>
+        <v>542</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>498</v>
+        <v>543</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -3843,11 +4226,11 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>499</v>
+        <v>544</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N21" s="12"/>
       <c r="O21" s="14" t="n">
@@ -3859,10 +4242,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>500</v>
+        <v>545</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>501</v>
+        <v>546</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -3875,11 +4258,11 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>502</v>
+        <v>547</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N22" s="12"/>
       <c r="O22" s="14" t="n">
@@ -3891,10 +4274,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>503</v>
+        <v>548</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>504</v>
+        <v>549</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -3907,11 +4290,11 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>505</v>
+        <v>550</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N23" s="12"/>
       <c r="O23" s="14" t="n">
@@ -4085,12 +4468,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -4098,31 +4481,31 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B40" s="19"/>
     </row>
@@ -4186,7 +4569,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>506</v>
+        <v>551</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4200,7 +4583,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>507</v>
+        <v>552</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4208,7 +4591,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>508</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4246,7 +4629,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>509</v>
+        <v>554</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4310,18 +4693,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>510</v>
+        <v>555</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>511</v>
+        <v>556</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -4334,11 +4717,11 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>512</v>
+        <v>557</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N17" s="12"/>
       <c r="O17" s="14" t="n">
@@ -4350,10 +4733,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>513</v>
+        <v>558</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>514</v>
+        <v>559</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -4366,11 +4749,11 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>515</v>
+        <v>560</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N18" s="12"/>
       <c r="O18" s="14" t="n">
@@ -4382,10 +4765,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>516</v>
+        <v>561</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>517</v>
+        <v>562</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -4398,11 +4781,11 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>518</v>
+        <v>563</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N19" s="12"/>
       <c r="O19" s="14" t="n">
@@ -4414,10 +4797,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>519</v>
+        <v>564</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>520</v>
+        <v>565</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -4430,11 +4813,11 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>521</v>
+        <v>566</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N20" s="12"/>
       <c r="O20" s="14" t="n">
@@ -4446,10 +4829,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>522</v>
+        <v>567</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>523</v>
+        <v>568</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -4462,11 +4845,11 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>524</v>
+        <v>569</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N21" s="12"/>
       <c r="O21" s="14" t="n">
@@ -4478,10 +4861,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>525</v>
+        <v>570</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>526</v>
+        <v>571</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -4494,11 +4877,11 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>527</v>
+        <v>572</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N22" s="12"/>
       <c r="O22" s="14" t="n">
@@ -4510,10 +4893,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>528</v>
+        <v>573</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>529</v>
+        <v>574</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -4526,11 +4909,11 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>530</v>
+        <v>575</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N23" s="12"/>
       <c r="O23" s="14" t="n">
@@ -4542,10 +4925,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>531</v>
+        <v>576</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>532</v>
+        <v>577</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -4558,11 +4941,11 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>533</v>
+        <v>578</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N24" s="12"/>
       <c r="O24" s="14" t="n">
@@ -4718,12 +5101,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -4731,31 +5114,31 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B40" s="19"/>
     </row>
@@ -4985,9 +5368,11 @@
         <v>53</v>
       </c>
       <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
+      <c r="L17" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="M17" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N17" s="12"/>
       <c r="O17" s="14"/>
@@ -4995,23 +5380,23 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>6</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>51</v>
@@ -5020,12 +5405,14 @@
         <v>52</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
+      <c r="L18" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="M18" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N18" s="12"/>
       <c r="O18" s="14"/>
@@ -5033,25 +5420,25 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>19</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H19" s="12" t="s">
         <v>51</v>
@@ -5063,9 +5450,11 @@
         <v>53</v>
       </c>
       <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
+      <c r="L19" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="M19" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N19" s="12"/>
       <c r="O19" s="14"/>
@@ -5073,17 +5462,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>10</v>
@@ -5101,9 +5490,11 @@
         <v>53</v>
       </c>
       <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
+      <c r="L20" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="M20" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N20" s="12"/>
       <c r="O20" s="14"/>
@@ -5111,17 +5502,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>8</v>
@@ -5139,9 +5530,11 @@
         <v>53</v>
       </c>
       <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
+      <c r="L21" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="M21" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N21" s="12"/>
       <c r="O21" s="14"/>
@@ -5149,23 +5542,23 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>13</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>51</v>
@@ -5177,9 +5570,11 @@
         <v>53</v>
       </c>
       <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
+      <c r="L22" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="M22" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N22" s="12"/>
       <c r="O22" s="14"/>
@@ -5187,26 +5582,26 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I23" s="12" t="s">
         <v>52</v>
@@ -5215,9 +5610,11 @@
         <v>53</v>
       </c>
       <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
+      <c r="L23" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="M23" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N23" s="12"/>
       <c r="O23" s="14"/>
@@ -5225,17 +5622,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>22</v>
@@ -5253,9 +5650,11 @@
         <v>53</v>
       </c>
       <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
+      <c r="L24" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="M24" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N24" s="12"/>
       <c r="O24" s="14"/>
@@ -5263,17 +5662,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>18</v>
@@ -5291,9 +5690,11 @@
         <v>53</v>
       </c>
       <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
+      <c r="L25" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="M25" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N25" s="12"/>
       <c r="O25" s="14"/>
@@ -5301,17 +5702,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>21</v>
@@ -5326,12 +5727,14 @@
         <v>52</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
+      <c r="L26" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="M26" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N26" s="12"/>
       <c r="O26" s="12"/>
@@ -5339,17 +5742,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>17</v>
@@ -5364,12 +5767,14 @@
         <v>52</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
+      <c r="L27" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="M27" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N27" s="12"/>
       <c r="O27" s="12"/>
@@ -5377,37 +5782,39 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>20</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H28" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="J28" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
       <c r="M28" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N28" s="12"/>
       <c r="O28" s="12"/>
@@ -5415,23 +5822,23 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>23</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>51</v>
@@ -5443,9 +5850,11 @@
         <v>53</v>
       </c>
       <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
+      <c r="L29" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="M29" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N29" s="12"/>
       <c r="O29" s="12"/>
@@ -5453,19 +5862,19 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>5</v>
@@ -5480,12 +5889,14 @@
         <v>52</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
+      <c r="L30" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="M30" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N30" s="12"/>
       <c r="O30" s="12"/>
@@ -5493,17 +5904,17 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>7</v>
@@ -5521,9 +5932,11 @@
         <v>53</v>
       </c>
       <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
+      <c r="L31" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="M31" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N31" s="12"/>
       <c r="O31" s="12"/>
@@ -5531,17 +5944,17 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C32" s="12"/>
       <c r="D32" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>11</v>
@@ -5559,9 +5972,11 @@
         <v>53</v>
       </c>
       <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
+      <c r="L32" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="M32" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N32" s="12"/>
       <c r="O32" s="12"/>
@@ -5587,12 +6002,12 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>32</v>
@@ -5600,31 +6015,31 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>46</v>
@@ -5632,10 +6047,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -5698,7 +6113,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5712,7 +6127,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5720,7 +6135,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5728,7 +6143,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5736,7 +6151,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5750,7 +6165,7 @@
         <v>22</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5758,7 +6173,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5766,7 +6181,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5830,25 +6245,25 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
@@ -5862,7 +6277,7 @@
       <c r="K17" s="12"/>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N17" s="12"/>
       <c r="O17" s="14" t="n">
@@ -5874,17 +6289,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>7</v>
@@ -5898,7 +6313,7 @@
       <c r="K18" s="12"/>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N18" s="12"/>
       <c r="O18" s="14" t="n">
@@ -5910,17 +6325,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>13</v>
@@ -5934,7 +6349,7 @@
       <c r="K19" s="12"/>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N19" s="12"/>
       <c r="O19" s="14" t="n">
@@ -5946,17 +6361,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>8</v>
@@ -5970,7 +6385,7 @@
       <c r="K20" s="12"/>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N20" s="12"/>
       <c r="O20" s="14" t="n">
@@ -5982,19 +6397,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>4</v>
@@ -6008,7 +6423,7 @@
       <c r="K21" s="12"/>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N21" s="12"/>
       <c r="O21" s="14" t="n">
@@ -6020,17 +6435,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>16</v>
@@ -6044,7 +6459,7 @@
       <c r="K22" s="12"/>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N22" s="12"/>
       <c r="O22" s="14" t="n">
@@ -6056,17 +6471,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>17</v>
@@ -6080,7 +6495,7 @@
       <c r="K23" s="12"/>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N23" s="12"/>
       <c r="O23" s="14" t="n">
@@ -6092,17 +6507,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>21</v>
@@ -6116,7 +6531,7 @@
       <c r="K24" s="12"/>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N24" s="12"/>
       <c r="O24" s="14" t="n">
@@ -6128,24 +6543,24 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
@@ -6158,17 +6573,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>25</v>
@@ -6188,17 +6603,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>24</v>
@@ -6208,7 +6623,7 @@
         <v>51</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J27" s="12"/>
       <c r="K27" s="12"/>
@@ -6220,17 +6635,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>14</v>
@@ -6322,12 +6737,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -6335,31 +6750,31 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B40" s="19"/>
     </row>
@@ -6423,7 +6838,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6437,7 +6852,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6445,7 +6860,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6453,7 +6868,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6461,7 +6876,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6475,7 +6890,7 @@
         <v>22</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6483,7 +6898,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6491,7 +6906,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6499,7 +6914,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6557,25 +6972,25 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>8</v>
@@ -6587,11 +7002,11 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N17" s="12"/>
       <c r="O17" s="14" t="n">
@@ -6603,17 +7018,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>6</v>
@@ -6625,11 +7040,11 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N18" s="12"/>
       <c r="O18" s="14" t="n">
@@ -6641,17 +7056,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>22</v>
@@ -6663,11 +7078,11 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N19" s="12"/>
       <c r="O19" s="14" t="n">
@@ -6679,17 +7094,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>5</v>
@@ -6701,11 +7116,11 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N20" s="12"/>
       <c r="O20" s="14" t="n">
@@ -6717,29 +7132,29 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="12"/>
       <c r="H21" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12"/>
@@ -6749,17 +7164,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>7</v>
@@ -6771,7 +7186,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12"/>
@@ -6781,17 +7196,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>10</v>
@@ -6803,7 +7218,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12"/>
@@ -6813,17 +7228,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>17</v>
@@ -6835,7 +7250,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12"/>
@@ -6845,17 +7260,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>21</v>
@@ -6867,7 +7282,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12"/>
@@ -6877,17 +7292,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>23</v>
@@ -6899,7 +7314,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
       <c r="K26" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12"/>
@@ -6909,17 +7324,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>24</v>
@@ -6931,7 +7346,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12"/>
@@ -6941,19 +7356,19 @@
     </row>
     <row r="28" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>18</v>
@@ -6967,7 +7382,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
       <c r="K28" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="12"/>
@@ -6977,29 +7392,29 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>20</v>
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12"/>
@@ -7063,12 +7478,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -7076,31 +7491,31 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B40" s="19"/>
     </row>
@@ -7164,7 +7579,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7178,7 +7593,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7186,7 +7601,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7224,7 +7639,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7288,18 +7703,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -7312,11 +7727,11 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N17" s="12"/>
       <c r="O17" s="14" t="n">
@@ -7328,10 +7743,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -7344,11 +7759,11 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N18" s="12"/>
       <c r="O18" s="14" t="n">
@@ -7360,10 +7775,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -7376,11 +7791,11 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N19" s="12"/>
       <c r="O19" s="14" t="n">
@@ -7392,10 +7807,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -7408,11 +7823,11 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N20" s="12"/>
       <c r="O20" s="14" t="n">
@@ -7424,10 +7839,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -7440,11 +7855,11 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N21" s="12"/>
       <c r="O21" s="14" t="n">
@@ -7456,10 +7871,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -7472,11 +7887,11 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N22" s="12"/>
       <c r="O22" s="14" t="n">
@@ -7488,10 +7903,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -7504,11 +7919,11 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N23" s="12"/>
       <c r="O23" s="14" t="n">
@@ -7682,12 +8097,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -7695,31 +8110,31 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B40" s="19"/>
     </row>
@@ -7783,7 +8198,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7797,7 +8212,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7805,7 +8220,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7843,7 +8258,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7907,18 +8322,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -7931,11 +8346,11 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N17" s="12"/>
       <c r="O17" s="14" t="n">
@@ -7947,10 +8362,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -7963,11 +8378,11 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N18" s="12"/>
       <c r="O18" s="14" t="n">
@@ -7979,10 +8394,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -7995,11 +8410,11 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N19" s="12"/>
       <c r="O19" s="14" t="n">
@@ -8011,10 +8426,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -8027,11 +8442,11 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N20" s="12"/>
       <c r="O20" s="14" t="n">
@@ -8043,10 +8458,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -8059,11 +8474,11 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N21" s="12"/>
       <c r="O21" s="14" t="n">
@@ -8075,10 +8490,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -8091,11 +8506,11 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N22" s="12"/>
       <c r="O22" s="14" t="n">
@@ -8107,10 +8522,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -8123,11 +8538,11 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N23" s="12"/>
       <c r="O23" s="14" t="n">
@@ -8139,10 +8554,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -8155,11 +8570,11 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N24" s="12"/>
       <c r="O24" s="14" t="n">
@@ -8171,10 +8586,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -8187,11 +8602,11 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N25" s="12"/>
       <c r="O25" s="14" t="n">
@@ -8203,10 +8618,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
@@ -8219,11 +8634,11 @@
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
       <c r="K26" s="12" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N26" s="12"/>
       <c r="O26" s="14" t="n">
@@ -8235,10 +8650,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
@@ -8251,11 +8666,11 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N27" s="12"/>
       <c r="O27" s="14" t="n">
@@ -8357,12 +8772,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -8370,31 +8785,31 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B40" s="19"/>
     </row>
@@ -8458,7 +8873,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8472,7 +8887,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8480,7 +8895,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8518,7 +8933,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8582,18 +8997,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -8606,11 +9021,11 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N17" s="12"/>
       <c r="O17" s="14" t="n">
@@ -8622,10 +9037,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -8638,11 +9053,11 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N18" s="12"/>
       <c r="O18" s="14" t="n">
@@ -8654,10 +9069,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -8670,11 +9085,11 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N19" s="12"/>
       <c r="O19" s="14" t="n">
@@ -8686,10 +9101,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -8702,11 +9117,11 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N20" s="12"/>
       <c r="O20" s="14" t="n">
@@ -8718,10 +9133,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -8734,11 +9149,11 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N21" s="12"/>
       <c r="O21" s="14" t="n">
@@ -8750,10 +9165,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -8766,11 +9181,11 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N22" s="12"/>
       <c r="O22" s="14" t="n">
@@ -8782,10 +9197,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -8798,11 +9213,11 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N23" s="12"/>
       <c r="O23" s="14" t="n">
@@ -8814,10 +9229,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -8830,11 +9245,11 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N24" s="12"/>
       <c r="O24" s="14" t="n">
@@ -8846,10 +9261,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -8862,11 +9277,11 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N25" s="12"/>
       <c r="O25" s="14" t="n">
@@ -9004,12 +9419,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -9017,31 +9432,31 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B40" s="19"/>
     </row>
@@ -9105,7 +9520,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9119,7 +9534,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9127,7 +9542,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9165,7 +9580,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9229,18 +9644,18 @@
         <v>45</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -9253,11 +9668,11 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N17" s="12"/>
       <c r="O17" s="14" t="n">
@@ -9269,10 +9684,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -9285,11 +9700,11 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N18" s="12"/>
       <c r="O18" s="14" t="n">
@@ -9301,10 +9716,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -9317,11 +9732,11 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N19" s="12"/>
       <c r="O19" s="14" t="n">
@@ -9333,10 +9748,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -9349,11 +9764,11 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N20" s="12"/>
       <c r="O20" s="14" t="n">
@@ -9365,10 +9780,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
@@ -9381,11 +9796,11 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N21" s="12"/>
       <c r="O21" s="14" t="n">
@@ -9397,10 +9812,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -9413,11 +9828,11 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N22" s="12"/>
       <c r="O22" s="14" t="n">
@@ -9429,10 +9844,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
@@ -9445,11 +9860,11 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N23" s="12"/>
       <c r="O23" s="14" t="n">
@@ -9623,12 +10038,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -9636,31 +10051,31 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B40" s="19"/>
     </row>
@@ -9724,7 +10139,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9738,7 +10153,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9746,7 +10161,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9784,7 +10199,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9850,25 +10265,25 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>51</v>
@@ -9876,15 +10291,17 @@
       <c r="I17" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="J17" s="12"/>
+      <c r="J17" s="12" t="s">
+        <v>371</v>
+      </c>
       <c r="K17" s="12" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N17" s="12"/>
       <c r="O17" s="14"/>
@@ -9892,23 +10309,23 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>18</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>51</v>
@@ -9916,15 +10333,17 @@
       <c r="I18" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="12"/>
+      <c r="J18" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="K18" s="12" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N18" s="12"/>
       <c r="O18" s="14"/>
@@ -9932,19 +10351,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>7</v>
@@ -9958,15 +10377,17 @@
       <c r="I19" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="J19" s="12"/>
+      <c r="J19" s="12" t="s">
+        <v>384</v>
+      </c>
       <c r="K19" s="12" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M19" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N19" s="12"/>
       <c r="O19" s="14"/>
@@ -9974,23 +10395,23 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>10</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H20" s="12" t="s">
         <v>51</v>
@@ -9998,15 +10419,17 @@
       <c r="I20" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="J20" s="12"/>
+      <c r="J20" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="K20" s="12" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N20" s="12"/>
       <c r="O20" s="14"/>
@@ -10014,19 +10437,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>13</v>
@@ -10038,17 +10461,19 @@
         <v>51</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="J21" s="12"/>
+        <v>105</v>
+      </c>
+      <c r="J21" s="0" t="s">
+        <v>396</v>
+      </c>
       <c r="K21" s="12" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M21" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N21" s="12"/>
       <c r="O21" s="14"/>
@@ -10056,17 +10481,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>23</v>
@@ -10080,15 +10505,17 @@
       <c r="I22" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="12"/>
+      <c r="J22" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="K22" s="12" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N22" s="12"/>
       <c r="O22" s="14"/>
@@ -10096,23 +10523,23 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>5</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>51</v>
@@ -10120,15 +10547,17 @@
       <c r="I23" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="J23" s="12"/>
+      <c r="J23" s="12" t="s">
+        <v>115</v>
+      </c>
       <c r="K23" s="12" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N23" s="12"/>
       <c r="O23" s="14"/>
@@ -10136,17 +10565,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="20" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>8</v>
@@ -10158,17 +10587,19 @@
         <v>51</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="J24" s="12"/>
+        <v>105</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>371</v>
+      </c>
       <c r="K24" s="12" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M24" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N24" s="12"/>
       <c r="O24" s="14"/>
@@ -10176,17 +10607,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>17</v>
@@ -10198,17 +10629,19 @@
         <v>51</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="J25" s="12"/>
+        <v>105</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="K25" s="12" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N25" s="12"/>
       <c r="O25" s="14"/>
@@ -10216,39 +10649,41 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="21" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>20</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I26" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="J26" s="12"/>
+      <c r="J26" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="K26" s="15" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N26" s="12"/>
       <c r="O26" s="12"/>
@@ -10256,23 +10691,23 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="21" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>9</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>51</v>
@@ -10280,15 +10715,17 @@
       <c r="I27" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="12"/>
+      <c r="J27" s="12" t="s">
+        <v>115</v>
+      </c>
       <c r="K27" s="15" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N27" s="12"/>
       <c r="O27" s="12"/>
@@ -10296,39 +10733,41 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="21" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I28" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="J28" s="12"/>
+      <c r="J28" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="K28" s="21" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N28" s="12"/>
       <c r="O28" s="12"/>
@@ -10336,17 +10775,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C29" s="0"/>
       <c r="D29" s="21" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F29" s="0" t="n">
         <v>2</v>
@@ -10360,15 +10799,17 @@
       <c r="I29" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="J29" s="0"/>
+      <c r="J29" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="K29" s="21" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N29" s="0"/>
       <c r="O29" s="0"/>
@@ -10376,39 +10817,41 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C30" s="0"/>
       <c r="D30" s="21" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F30" s="0" t="n">
         <v>12</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I30" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="J30" s="0"/>
+      <c r="J30" s="0" t="s">
+        <v>440</v>
+      </c>
       <c r="K30" s="21" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N30" s="0"/>
       <c r="O30" s="0"/>
@@ -10416,21 +10859,21 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C31" s="0"/>
       <c r="D31" s="0"/>
       <c r="E31" s="0" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="F31" s="0" t="n">
         <v>15</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H31" s="0" t="s">
         <v>51</v>
@@ -10438,15 +10881,17 @@
       <c r="I31" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="J31" s="0"/>
+      <c r="J31" s="0" t="s">
+        <v>396</v>
+      </c>
       <c r="K31" s="0" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M31" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N31" s="0"/>
       <c r="O31" s="0"/>
@@ -10472,12 +10917,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>32</v>
@@ -10485,42 +10930,42 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/D1_Fiches_Clubs_Joueurs_26_27.xlsx
+++ b/D1_Fiches_Clubs_Joueurs_26_27.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Mode emploi" sheetId="1" state="visible" r:id="rId3"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2315" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="1094">
   <si>
     <t xml:space="preserve">FICHES CLUBS · D1 FUTSAL 2026-2027</t>
   </si>
@@ -2085,6 +2085,21 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">matheo-le-pessot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATHEO LE PESSOT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATHEO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LE PESSOT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">matheo-le-pessot.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">FICHE CLUB · LAVAL</t>
   </si>
   <si>
@@ -2359,6 +2374,12 @@
   </si>
   <si>
     <t xml:space="preserve">ABDESSAMAD MOHAMMED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABDESSAMAD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOHAMMED</t>
   </si>
   <si>
     <t xml:space="preserve">Abdessamad-mohammed.png</t>
@@ -3351,12 +3372,21 @@
     <t xml:space="preserve">TOULON</t>
   </si>
   <si>
+    <t xml:space="preserve">Toulon</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sergeï Padalinski </t>
   </si>
   <si>
+    <t xml:space="preserve">rouge foncé</t>
+  </si>
+  <si>
     <t xml:space="preserve">7.png</t>
   </si>
   <si>
+    <t xml:space="preserve">https://toulon-metropole-futsal.fr/futsal/d1</t>
+  </si>
+  <si>
     <t xml:space="preserve">alexis-dubois</t>
   </si>
   <si>
@@ -3579,10 +3609,22 @@
     <t xml:space="preserve">TOULOUSE</t>
   </si>
   <si>
+    <t xml:space="preserve">PETIT PALAIS DES SPORTS </t>
+  </si>
+  <si>
     <t xml:space="preserve">Pepe Narváez </t>
   </si>
   <si>
+    <t xml:space="preserve">rouge clair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blanc </t>
+  </si>
+  <si>
     <t xml:space="preserve">10.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ujs-toulouse.com/</t>
   </si>
   <si>
     <t xml:space="preserve">ayoub-bouita</t>
@@ -3949,12 +3991,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -4018,7 +4066,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4043,15 +4091,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4071,7 +4119,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4079,7 +4127,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4091,11 +4139,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4107,8 +4159,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -4461,8 +4521,8 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>765</v>
+      <c r="A1" s="19" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4476,7 +4536,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4484,7 +4544,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4522,7 +4582,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4588,19 +4648,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>9</v>
@@ -4612,7 +4672,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -4624,17 +4684,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>14</v>
@@ -4646,7 +4706,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -4658,19 +4718,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>19</v>
@@ -4682,7 +4742,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -4694,17 +4754,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>6</v>
@@ -4716,7 +4776,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -4728,17 +4788,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>12</v>
@@ -4750,7 +4810,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -4762,17 +4822,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>20</v>
@@ -4784,7 +4844,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -4796,17 +4856,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>3</v>
@@ -4818,7 +4878,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -4830,17 +4890,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
         <v>493</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>5</v>
@@ -4852,7 +4912,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -4864,19 +4924,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>18</v>
@@ -4888,7 +4948,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -4900,17 +4960,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>7</v>
@@ -4922,7 +4982,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
       <c r="K26" s="12" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12" t="s">
@@ -4934,17 +4994,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
         <v>467</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>8</v>
@@ -4956,7 +5016,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12" t="s">
@@ -4968,17 +5028,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>26</v>
@@ -4990,7 +5050,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
       <c r="K28" s="12" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="12" t="s">
@@ -5002,17 +5062,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>17</v>
@@ -5024,7 +5084,7 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="12" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12" t="s">
@@ -5036,17 +5096,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>26</v>
@@ -5058,7 +5118,7 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="12" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="L30" s="12"/>
       <c r="M30" s="12" t="s">
@@ -5121,31 +5181,31 @@
       <c r="A36" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B36" s="20"/>
+      <c r="B36" s="21"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="20"/>
+      <c r="B37" s="21"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B38" s="20"/>
+      <c r="B38" s="21"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B39" s="20"/>
+      <c r="B39" s="21"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B40" s="20"/>
+      <c r="B40" s="21"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -5207,7 +5267,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5221,7 +5281,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5229,7 +5289,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5237,7 +5297,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5245,7 +5305,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5253,7 +5313,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5261,7 +5321,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5277,7 +5337,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5285,7 +5345,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5293,7 +5353,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5347,17 +5407,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
@@ -5370,13 +5430,13 @@
         <v>53</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -5387,17 +5447,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>8</v>
@@ -5413,10 +5473,10 @@
         <v>54</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -5427,17 +5487,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>10</v>
@@ -5453,10 +5513,10 @@
         <v>129</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -5467,17 +5527,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>5</v>
@@ -5493,10 +5553,10 @@
         <v>54</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -5507,17 +5567,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>2</v>
@@ -5533,10 +5593,10 @@
         <v>129</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -5547,17 +5607,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>15</v>
@@ -5570,13 +5630,13 @@
         <v>53</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -5587,19 +5647,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>19</v>
@@ -5615,10 +5675,10 @@
         <v>308</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -5629,17 +5689,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="15" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>1</v>
@@ -5655,10 +5715,10 @@
         <v>54</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -5669,17 +5729,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="15" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>20</v>
@@ -5695,10 +5755,10 @@
         <v>54</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -5709,17 +5769,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="15" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>25</v>
@@ -5735,10 +5795,10 @@
         <v>54</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -5749,19 +5809,19 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>3</v>
@@ -5774,13 +5834,13 @@
         <v>53</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -5791,17 +5851,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="15" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>17</v>
@@ -5817,10 +5877,10 @@
         <v>54</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -5831,17 +5891,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>26</v>
@@ -5857,10 +5917,10 @@
         <v>54</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>911</v>
+        <v>918</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -5871,17 +5931,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>7</v>
@@ -5891,10 +5951,10 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="12" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -5957,7 +6017,7 @@
         <v>147</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5965,7 +6025,7 @@
         <v>62</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5973,7 +6033,7 @@
         <v>148</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5981,7 +6041,7 @@
         <v>149</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5989,7 +6049,7 @@
         <v>70</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
     </row>
   </sheetData>
@@ -6047,8 +6107,8 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>917</v>
+      <c r="A1" s="19" t="s">
+        <v>924</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6062,7 +6122,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6070,14 +6130,16 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="12"/>
+      <c r="B6" s="12" t="s">
+        <v>927</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
@@ -6090,40 +6152,48 @@
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="12"/>
+      <c r="B9" s="12" t="s">
+        <v>929</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="12"/>
+      <c r="B10" s="12" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>921</v>
+        <v>930</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="12"/>
+      <c r="B12" s="12" t="s">
+        <v>931</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="12"/>
+      <c r="B13" s="12" t="s">
+        <v>931</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -6182,14 +6252,14 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>922</v>
+        <v>932</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>924</v>
+        <v>934</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>271</v>
@@ -6205,10 +6275,10 @@
         <v>53</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>926</v>
+        <v>936</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -6224,17 +6294,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>927</v>
+        <v>937</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>928</v>
+        <v>938</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>929</v>
+        <v>939</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>930</v>
+        <v>940</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>6</v>
@@ -6247,10 +6317,10 @@
         <v>117</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>931</v>
+        <v>941</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -6266,19 +6336,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>932</v>
+        <v>942</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>933</v>
+        <v>943</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>934</v>
+        <v>944</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>935</v>
+        <v>945</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>936</v>
+        <v>946</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>17</v>
@@ -6292,7 +6362,7 @@
       </c>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>937</v>
+        <v>947</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -6308,17 +6378,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>938</v>
+        <v>948</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>939</v>
+        <v>949</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>941</v>
+        <v>951</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>7</v>
@@ -6331,10 +6401,10 @@
         <v>53</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>942</v>
+        <v>952</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -6350,17 +6420,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>943</v>
+        <v>953</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>944</v>
+        <v>954</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>945</v>
+        <v>955</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>946</v>
+        <v>956</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>10</v>
@@ -6374,7 +6444,7 @@
       </c>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>947</v>
+        <v>957</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -6390,17 +6460,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>948</v>
+        <v>958</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>949</v>
+        <v>959</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>950</v>
+        <v>960</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>951</v>
+        <v>961</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>19</v>
@@ -6413,10 +6483,10 @@
         <v>53</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>952</v>
+        <v>962</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -6432,17 +6502,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>953</v>
+        <v>963</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>954</v>
+        <v>964</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>955</v>
+        <v>965</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>956</v>
+        <v>966</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>20</v>
@@ -6458,7 +6528,7 @@
       </c>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>957</v>
+        <v>967</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -6474,17 +6544,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>961</v>
+        <v>971</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>5</v>
@@ -6497,10 +6567,10 @@
       </c>
       <c r="I24" s="12"/>
       <c r="J24" s="12" t="s">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>962</v>
+        <v>972</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -6512,17 +6582,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>963</v>
+        <v>973</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>964</v>
+        <v>974</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>965</v>
+        <v>975</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>966</v>
+        <v>976</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>11</v>
@@ -6534,7 +6604,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>967</v>
+        <v>977</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -6546,17 +6616,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>968</v>
+        <v>978</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>969</v>
+        <v>979</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>971</v>
+        <v>981</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>12</v>
@@ -6569,10 +6639,10 @@
       </c>
       <c r="I26" s="12"/>
       <c r="J26" s="12" t="s">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>972</v>
+        <v>982</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12" t="s">
@@ -6584,17 +6654,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>973</v>
+        <v>983</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>974</v>
+        <v>984</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>975</v>
+        <v>985</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>976</v>
+        <v>986</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>22</v>
@@ -6606,7 +6676,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>977</v>
+        <v>987</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12" t="s">
@@ -6618,17 +6688,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>978</v>
+        <v>988</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>979</v>
+        <v>989</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>981</v>
+        <v>991</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>21</v>
@@ -6640,7 +6710,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
       <c r="K28" s="12" t="s">
-        <v>982</v>
+        <v>992</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="12" t="s">
@@ -6652,17 +6722,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>983</v>
+        <v>993</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>984</v>
+        <v>994</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>985</v>
+        <v>995</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>986</v>
+        <v>996</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>9</v>
@@ -6674,7 +6744,7 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="12" t="s">
-        <v>987</v>
+        <v>997</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12" t="s">
@@ -6686,17 +6756,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>988</v>
+        <v>998</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>989</v>
+        <v>999</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>14</v>
@@ -6708,7 +6778,7 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="12" t="s">
-        <v>992</v>
+        <v>1002</v>
       </c>
       <c r="L30" s="12"/>
       <c r="M30" s="12" t="s">
@@ -6767,7 +6837,7 @@
         <v>147</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>953</v>
+        <v>963</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6775,7 +6845,7 @@
         <v>62</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>943</v>
+        <v>953</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6783,7 +6853,7 @@
         <v>148</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>932</v>
+        <v>942</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6791,7 +6861,7 @@
         <v>149</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>927</v>
+        <v>937</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6799,7 +6869,7 @@
         <v>70</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>922</v>
+        <v>932</v>
       </c>
     </row>
   </sheetData>
@@ -6857,8 +6927,8 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>993</v>
+      <c r="A1" s="19" t="s">
+        <v>1003</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6872,7 +6942,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>994</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6880,60 +6950,72 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="12"/>
+      <c r="B6" s="12" t="s">
+        <v>1005</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="12"/>
+      <c r="B7" s="25" t="s">
+        <v>1006</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>996</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="12"/>
+      <c r="B9" s="12" t="s">
+        <v>1008</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="12"/>
+      <c r="B10" s="12" t="s">
+        <v>1009</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>997</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="12"/>
+      <c r="B12" s="12" t="s">
+        <v>1011</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="12"/>
+      <c r="B13" s="12" t="s">
+        <v>1011</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -6983,17 +7065,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>998</v>
+        <v>1012</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>999</v>
+        <v>1013</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
         <v>467</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>1000</v>
+        <v>1014</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>6</v>
@@ -7008,10 +7090,10 @@
         <v>117</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>1001</v>
+        <v>1015</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -7020,17 +7102,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1002</v>
+        <v>1016</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>1003</v>
+        <v>1017</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>1004</v>
+        <v>1018</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>1005</v>
+        <v>1019</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>19</v>
@@ -7045,10 +7127,10 @@
         <v>53</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>1006</v>
+        <v>1020</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -7057,17 +7139,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1007</v>
+        <v>1021</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>1008</v>
+        <v>1022</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
         <v>182</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>1009</v>
+        <v>1023</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>8</v>
@@ -7085,7 +7167,7 @@
         <v>129</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>1010</v>
+        <v>1024</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -7094,17 +7176,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1011</v>
+        <v>1025</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>1012</v>
+        <v>1026</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>1013</v>
+        <v>1027</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>1014</v>
+        <v>1028</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>11</v>
@@ -7119,10 +7201,10 @@
         <v>53</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>1015</v>
+        <v>1029</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -7131,17 +7213,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>1016</v>
+        <v>1030</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>1017</v>
+        <v>1031</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>1018</v>
+        <v>1032</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>1019</v>
+        <v>1033</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>26</v>
@@ -7153,7 +7235,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>1020</v>
+        <v>1034</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -7162,17 +7244,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>1021</v>
+        <v>1035</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>1022</v>
+        <v>1036</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>1023</v>
+        <v>1037</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>1024</v>
+        <v>1038</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>10</v>
@@ -7187,10 +7269,10 @@
         <v>53</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>1025</v>
+        <v>1039</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -7199,17 +7281,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>1026</v>
+        <v>1040</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>1027</v>
+        <v>1041</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>1028</v>
+        <v>1042</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>1029</v>
+        <v>1043</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>4</v>
@@ -7224,10 +7306,10 @@
         <v>53</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>925</v>
+        <v>129</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>1030</v>
+        <v>1044</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -7236,17 +7318,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>1031</v>
+        <v>1045</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>1032</v>
+        <v>1046</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>1033</v>
+        <v>1047</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>1034</v>
+        <v>1048</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>9</v>
@@ -7257,10 +7339,14 @@
       <c r="H24" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
+      <c r="I24" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>129</v>
+      </c>
       <c r="K24" s="12" t="s">
-        <v>1035</v>
+        <v>1049</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -7269,17 +7355,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>1036</v>
+        <v>1050</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>1037</v>
+        <v>1051</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>1038</v>
+        <v>1052</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>1039</v>
+        <v>1053</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>25</v>
@@ -7291,7 +7377,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>1040</v>
+        <v>1054</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -7300,17 +7386,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>1041</v>
+        <v>1055</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>1024</v>
+        <v>1038</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>7</v>
@@ -7325,10 +7411,10 @@
         <v>53</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>1043</v>
+        <v>1057</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12" t="s">
@@ -7337,17 +7423,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>1044</v>
+        <v>1058</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>1045</v>
+        <v>1059</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>1046</v>
+        <v>1060</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>1047</v>
+        <v>1061</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>15</v>
@@ -7359,7 +7445,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>1048</v>
+        <v>1062</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12" t="s">
@@ -7368,17 +7454,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>1049</v>
+        <v>1063</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>1050</v>
+        <v>1064</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>1051</v>
+        <v>1065</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>1052</v>
+        <v>1066</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>18</v>
@@ -7390,7 +7476,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
       <c r="K28" s="12" t="s">
-        <v>1053</v>
+        <v>1067</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="12" t="s">
@@ -7399,17 +7485,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>1054</v>
+        <v>1068</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1055</v>
+        <v>1069</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>1004</v>
+        <v>1018</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>1056</v>
+        <v>1070</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>12</v>
@@ -7421,7 +7507,7 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="12" t="s">
-        <v>1057</v>
+        <v>1071</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12" t="s">
@@ -7430,17 +7516,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>1058</v>
+        <v>1072</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>1059</v>
+        <v>1073</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>1060</v>
+        <v>1074</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>1061</v>
+        <v>1075</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>1</v>
@@ -7454,7 +7540,7 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="12" t="s">
-        <v>1062</v>
+        <v>1076</v>
       </c>
       <c r="L30" s="12"/>
       <c r="M30" s="12" t="s">
@@ -7463,17 +7549,17 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>1063</v>
+        <v>1077</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>1064</v>
+        <v>1078</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12" t="s">
-        <v>1065</v>
+        <v>1079</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>1066</v>
+        <v>1080</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>3</v>
@@ -7485,7 +7571,7 @@
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
       <c r="K31" s="12" t="s">
-        <v>1067</v>
+        <v>1081</v>
       </c>
       <c r="L31" s="12"/>
       <c r="M31" s="12" t="s">
@@ -7494,17 +7580,17 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>1068</v>
+        <v>1082</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>1069</v>
+        <v>1083</v>
       </c>
       <c r="C32" s="12"/>
       <c r="D32" s="12" t="s">
         <v>182</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>1056</v>
+        <v>1070</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>21</v>
@@ -7519,10 +7605,10 @@
         <v>53</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>1070</v>
+        <v>1084</v>
       </c>
       <c r="L32" s="18"/>
       <c r="M32" s="12" t="s">
@@ -7531,17 +7617,17 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>1071</v>
+        <v>1085</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>1072</v>
+        <v>1086</v>
       </c>
       <c r="C33" s="12"/>
       <c r="D33" s="12" t="s">
         <v>451</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>1073</v>
+        <v>1087</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>20</v>
@@ -7550,7 +7636,7 @@
         <v>52</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>1074</v>
+        <v>1088</v>
       </c>
       <c r="M33" s="12" t="s">
         <v>57</v>
@@ -7558,17 +7644,17 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>1075</v>
+        <v>1089</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>1076</v>
+        <v>1090</v>
       </c>
       <c r="C34" s="12"/>
       <c r="D34" s="12" t="s">
-        <v>1077</v>
+        <v>1091</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>1078</v>
+        <v>1092</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>22</v>
@@ -7577,7 +7663,7 @@
         <v>52</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>1079</v>
+        <v>1093</v>
       </c>
       <c r="M34" s="12" t="s">
         <v>57</v>
@@ -7600,31 +7686,31 @@
       <c r="A38" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B38" s="20"/>
+      <c r="B38" s="21"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B39" s="20"/>
+      <c r="B39" s="21"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B40" s="20"/>
+      <c r="B40" s="21"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B41" s="20"/>
+      <c r="B41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B42" s="20"/>
+      <c r="B42" s="21"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -8668,7 +8754,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="19" t="s">
         <v>150</v>
       </c>
     </row>
@@ -9523,7 +9609,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="19" t="s">
         <v>238</v>
       </c>
     </row>
@@ -10373,7 +10459,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="19" t="s">
         <v>323</v>
       </c>
     </row>
@@ -11080,7 +11166,7 @@
         <v>408</v>
       </c>
       <c r="C32" s="18"/>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="20" t="s">
         <v>409</v>
       </c>
       <c r="E32" s="11" t="s">
@@ -11209,7 +11295,7 @@
       <c r="A40" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="20"/>
+      <c r="B40" s="21"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
@@ -11223,7 +11309,7 @@
       <c r="A42" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B42" s="20"/>
+      <c r="B42" s="21"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
@@ -11334,7 +11420,7 @@
       <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="22" t="s">
         <v>430</v>
       </c>
     </row>
@@ -12089,6 +12175,41 @@
       </c>
       <c r="M32" s="12" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>520</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="L33" s="12" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12218,7 +12339,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12232,7 +12353,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12240,7 +12361,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12248,7 +12369,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12261,16 +12382,16 @@
       <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="21" t="s">
-        <v>521</v>
+      <c r="B8" s="22" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="21" t="s">
-        <v>522</v>
+      <c r="B9" s="22" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12278,7 +12399,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12286,7 +12407,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12352,17 +12473,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
@@ -12380,10 +12501,10 @@
         <v>129</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -12394,17 +12515,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>10</v>
@@ -12416,16 +12537,16 @@
         <v>52</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="J18" s="12" t="s">
         <v>129</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -12436,17 +12557,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>18</v>
@@ -12464,10 +12585,10 @@
         <v>54</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -12478,17 +12599,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>5</v>
@@ -12506,10 +12627,10 @@
         <v>129</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -12520,17 +12641,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>9</v>
@@ -12548,10 +12669,10 @@
         <v>54</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -12562,17 +12683,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>7</v>
@@ -12590,10 +12711,10 @@
         <v>54</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -12604,17 +12725,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>6</v>
@@ -12632,10 +12753,10 @@
         <v>54</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -12646,17 +12767,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>20</v>
@@ -12674,10 +12795,10 @@
         <v>54</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -12688,17 +12809,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>14</v>
@@ -12716,10 +12837,10 @@
         <v>54</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -12730,17 +12851,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>1</v>
@@ -12758,10 +12879,10 @@
         <v>54</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -12772,17 +12893,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>3</v>
@@ -12800,10 +12921,10 @@
         <v>54</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -12814,17 +12935,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>2</v>
@@ -12842,10 +12963,10 @@
         <v>54</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -12856,17 +12977,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>13</v>
@@ -12884,10 +13005,10 @@
         <v>54</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -12898,19 +13019,19 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>8</v>
@@ -12928,10 +13049,10 @@
         <v>308</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -12942,17 +13063,17 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>12</v>
@@ -12970,10 +13091,10 @@
         <v>54</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M31" s="12" t="s">
         <v>57</v>
@@ -12984,17 +13105,17 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="C32" s="0"/>
       <c r="D32" s="0" t="s">
-        <v>603</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>604</v>
+        <v>608</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>609</v>
       </c>
       <c r="F32" s="0" t="n">
         <v>22</v>
@@ -13006,16 +13127,16 @@
         <v>52</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="J32" s="12" t="s">
         <v>54</v>
       </c>
       <c r="K32" s="0" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M32" s="12" t="s">
         <v>57</v>
@@ -13026,14 +13147,18 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="C33" s="0"/>
-      <c r="D33" s="0"/>
-      <c r="E33" s="0"/>
+      <c r="D33" s="0" t="s">
+        <v>614</v>
+      </c>
+      <c r="E33" s="24" t="s">
+        <v>615</v>
+      </c>
       <c r="F33" s="0" t="n">
         <v>19</v>
       </c>
@@ -13050,10 +13175,10 @@
         <v>54</v>
       </c>
       <c r="K33" s="0" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M33" s="12" t="s">
         <v>57</v>
@@ -13098,7 +13223,7 @@
         <v>147</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13106,7 +13231,7 @@
         <v>62</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13114,7 +13239,7 @@
         <v>148</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13122,7 +13247,7 @@
         <v>149</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13130,7 +13255,7 @@
         <v>70</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>
@@ -13188,8 +13313,8 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>610</v>
+      <c r="A1" s="19" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13203,7 +13328,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13211,7 +13336,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13231,7 +13356,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13251,7 +13376,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13323,19 +13448,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>10</v>
@@ -13347,10 +13472,10 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -13365,19 +13490,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>14</v>
@@ -13389,10 +13514,10 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -13407,17 +13532,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>8</v>
@@ -13429,10 +13554,10 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -13447,17 +13572,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
         <v>467</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>7</v>
@@ -13469,10 +13594,10 @@
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -13487,17 +13612,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>19</v>
@@ -13509,10 +13634,10 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -13527,17 +13652,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>18</v>
@@ -13549,10 +13674,10 @@
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -13567,17 +13692,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
         <v>115</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>17</v>
@@ -13589,10 +13714,10 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -13607,17 +13732,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>4</v>
@@ -13629,10 +13754,10 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="12" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -13643,17 +13768,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>12</v>
@@ -13665,10 +13790,10 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -13679,17 +13804,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>20</v>
@@ -13701,10 +13826,10 @@
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
       <c r="K26" s="12" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -13715,17 +13840,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
         <v>127</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>5</v>
@@ -13737,10 +13862,10 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -13751,17 +13876,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>9</v>
@@ -13773,10 +13898,10 @@
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
       <c r="K28" s="12" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -13787,17 +13912,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
         <v>451</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>15</v>
@@ -13809,10 +13934,10 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="12" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -13823,17 +13948,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>22</v>
@@ -13845,10 +13970,10 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="12" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -13910,31 +14035,31 @@
       <c r="A36" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B36" s="20"/>
+      <c r="B36" s="21"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="20"/>
+      <c r="B37" s="21"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B38" s="20"/>
+      <c r="B38" s="21"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B39" s="20"/>
+      <c r="B39" s="21"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B40" s="20"/>
+      <c r="B40" s="21"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -13996,7 +14121,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14010,7 +14135,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14018,7 +14143,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14038,7 +14163,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14058,7 +14183,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14124,19 +14249,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
@@ -14151,13 +14276,13 @@
         <v>53</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -14168,17 +14293,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>18</v>
@@ -14196,10 +14321,10 @@
         <v>54</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -14210,19 +14335,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>7</v>
@@ -14240,10 +14365,10 @@
         <v>442</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -14254,17 +14379,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>10</v>
@@ -14282,10 +14407,10 @@
         <v>54</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -14296,19 +14421,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>13</v>
@@ -14326,10 +14451,10 @@
         <v>308</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -14340,14 +14465,14 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>168</v>
@@ -14368,10 +14493,10 @@
         <v>54</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -14382,17 +14507,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
         <v>341</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>5</v>
@@ -14410,10 +14535,10 @@
         <v>129</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -14424,17 +14549,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>8</v>
@@ -14449,13 +14574,13 @@
         <v>117</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -14466,17 +14591,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>17</v>
@@ -14494,10 +14619,10 @@
         <v>54</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -14508,17 +14633,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="11" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>20</v>
@@ -14536,10 +14661,10 @@
         <v>54</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -14550,17 +14675,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="11" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>9</v>
@@ -14578,10 +14703,10 @@
         <v>129</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -14592,17 +14717,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="11" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>1</v>
@@ -14620,10 +14745,10 @@
         <v>54</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -14634,16 +14759,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>2</v>
@@ -14661,10 +14786,10 @@
         <v>54</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -14672,16 +14797,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>12</v>
@@ -14696,13 +14821,13 @@
         <v>53</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -14710,13 +14835,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>15</v>
@@ -14734,10 +14859,10 @@
         <v>308</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="M31" s="12" t="s">
         <v>57</v>
@@ -14779,7 +14904,7 @@
         <v>147</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14787,7 +14912,7 @@
         <v>62</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14795,7 +14920,7 @@
         <v>148</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14803,7 +14928,7 @@
         <v>149</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14811,7 +14936,7 @@
         <v>70</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
     </row>
   </sheetData>

--- a/D1_Fiches_Clubs_Joueurs_26_27.xlsx
+++ b/D1_Fiches_Clubs_Joueurs_26_27.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Mode emploi" sheetId="1" state="visible" r:id="rId3"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="1094">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2422" uniqueCount="1116">
   <si>
     <t xml:space="preserve">FICHES CLUBS · D1 FUTSAL 2026-2027</t>
   </si>
@@ -1756,10 +1756,25 @@
     <t xml:space="preserve">GOAL</t>
   </si>
   <si>
+    <t xml:space="preserve">Neuville sur Saone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gymnase Rosa Parks</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nicolas Karilaos</t>
   </si>
   <si>
+    <t xml:space="preserve">Doré</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noir</t>
+  </si>
+  <si>
     <t xml:space="preserve">5.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.goalfutsalclub.fr/</t>
   </si>
   <si>
     <t xml:space="preserve">marouane-rezzoug</t>
@@ -2394,9 +2409,15 @@
     <t xml:space="preserve">MONTPELLIER</t>
   </si>
   <si>
+    <t xml:space="preserve">Palais des Sports Pierre de Coubertin </t>
+  </si>
+  <si>
     <t xml:space="preserve">Mohamed Nezlioui </t>
   </si>
   <si>
+    <t xml:space="preserve">rose foncé</t>
+  </si>
+  <si>
     <t xml:space="preserve">6.png</t>
   </si>
   <si>
@@ -2481,10 +2502,13 @@
     <t xml:space="preserve">fabio-simiand.png</t>
   </si>
   <si>
-    <t xml:space="preserve">jhonatan-pereira-de-oliveira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JHONATAN PEREIRA DE OLIVEIRA</t>
+    <t xml:space="preserve">johnatan-pereira-de-oliveira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOHNATAN PEREIRA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOHNATAN RUAS</t>
   </si>
   <si>
     <t xml:space="preserve">Jhonatan</t>
@@ -2493,7 +2517,7 @@
     <t xml:space="preserve">PEREIRA DE OLIVEIRA</t>
   </si>
   <si>
-    <t xml:space="preserve">jhonatan-pereira-de-oliveira.png</t>
+    <t xml:space="preserve">johnatan-pereira-de-oliveira.png</t>
   </si>
   <si>
     <t xml:space="preserve">wassim-bakhti</t>
@@ -2527,6 +2551,9 @@
   </si>
   <si>
     <t xml:space="preserve">CRISTIANO ALEXANDRE BARBOSA MARQUES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTIANO MARQUES</t>
   </si>
   <si>
     <t xml:space="preserve">Cristiano</t>
@@ -2916,9 +2943,21 @@
     <t xml:space="preserve">NICE</t>
   </si>
   <si>
+    <t xml:space="preserve">Halle des Sports Charles Ehrmann </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elyesse Ben Salem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">doré</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.png</t>
   </si>
   <si>
+    <t xml:space="preserve">https://nicefutsalclub.com/</t>
+  </si>
+  <si>
     <t xml:space="preserve">lucas-nahuel-paroldo-ferreri</t>
   </si>
   <si>
@@ -2934,6 +2973,9 @@
     <t xml:space="preserve">PAROLDO FERRERI</t>
   </si>
   <si>
+    <t xml:space="preserve">Uruguayen </t>
+  </si>
+  <si>
     <t xml:space="preserve">Lucas-nahuel-paroldo-ferreri.png</t>
   </si>
   <si>
@@ -2964,6 +3006,9 @@
     <t xml:space="preserve"> DE ARAUJO</t>
   </si>
   <si>
+    <t xml:space="preserve">Azerbaïdjanais </t>
+  </si>
+  <si>
     <t xml:space="preserve">fineo-de-araujo.png</t>
   </si>
   <si>
@@ -3054,7 +3099,7 @@
     <t xml:space="preserve">franco-duque-cancela.png</t>
   </si>
   <si>
-    <t xml:space="preserve">jamal-elvbsahi</t>
+    <t xml:space="preserve">jamal-el-bsahi</t>
   </si>
   <si>
     <t xml:space="preserve">JAMAL EL BSAHI</t>
@@ -3066,7 +3111,7 @@
     <t xml:space="preserve">EL BSAHI</t>
   </si>
   <si>
-    <t xml:space="preserve">jamal-elvbsahi.png</t>
+    <t xml:space="preserve">jamal-el-bsahi.png</t>
   </si>
   <si>
     <t xml:space="preserve">ayoub-eladdad</t>
@@ -3123,6 +3168,21 @@
     <t xml:space="preserve">charles-nardy.png</t>
   </si>
   <si>
+    <t xml:space="preserve">salym-briki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALYM BRIKI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salym</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRIKI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salym-briki.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">FICHE CLUB · SPORTING</t>
   </si>
   <si>
@@ -3747,10 +3807,16 @@
     <t xml:space="preserve">RICARDO ANTONIO BENTO GONCALVES</t>
   </si>
   <si>
+    <t xml:space="preserve">BENTO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ricardo</t>
   </si>
   <si>
     <t xml:space="preserve">ANTONIO BENTO GONCALVES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cap Verdien</t>
   </si>
   <si>
     <t xml:space="preserve">ricardo-antonio-bento-goncalves.png</t>
@@ -4066,7 +4132,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4168,6 +4234,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4505,7 +4575,7 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8"/>
@@ -4522,7 +4592,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>772</v>
+        <v>781</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4536,7 +4606,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>773</v>
+        <v>782</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4544,58 +4614,72 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>774</v>
+        <v>783</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="12" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="12"/>
+      <c r="B7" s="25" t="s">
+        <v>784</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="12"/>
+      <c r="B8" s="26" t="s">
+        <v>785</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="12"/>
+      <c r="B9" s="12" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="12"/>
+      <c r="B10" s="12" t="s">
+        <v>786</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>775</v>
+        <v>787</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="12"/>
+      <c r="B12" s="12" t="s">
+        <v>788</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="12"/>
+      <c r="B13" s="12" t="s">
+        <v>788</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -4648,31 +4732,35 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>776</v>
+        <v>789</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>777</v>
+        <v>790</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>778</v>
+        <v>791</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>779</v>
+        <v>792</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>780</v>
+        <v>793</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G17" s="12"/>
+      <c r="G17" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H17" s="12" t="s">
         <v>52</v>
       </c>
       <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
+      <c r="J17" s="12" t="s">
+        <v>794</v>
+      </c>
       <c r="K17" s="12" t="s">
-        <v>781</v>
+        <v>795</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -4684,29 +4772,35 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>782</v>
+        <v>796</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>783</v>
+        <v>797</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>784</v>
+        <v>798</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>785</v>
+        <v>799</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="G18" s="12"/>
+      <c r="G18" s="12" t="s">
+        <v>70</v>
+      </c>
       <c r="H18" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
+      <c r="I18" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="K18" s="12" t="s">
-        <v>786</v>
+        <v>800</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -4718,31 +4812,37 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>787</v>
+        <v>801</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>788</v>
+        <v>802</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>789</v>
+        <v>803</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>789</v>
+        <v>803</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>790</v>
+        <v>804</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G19" s="12"/>
+      <c r="G19" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H19" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
+      <c r="I19" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J19" s="25" t="s">
+        <v>805</v>
+      </c>
       <c r="K19" s="12" t="s">
-        <v>791</v>
+        <v>806</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -4754,29 +4854,33 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>795</v>
+        <v>810</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G20" s="12"/>
+      <c r="G20" s="12" t="s">
+        <v>62</v>
+      </c>
       <c r="H20" s="12" t="s">
         <v>52</v>
       </c>
       <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
+      <c r="J20" s="12" t="s">
+        <v>129</v>
+      </c>
       <c r="K20" s="12" t="s">
-        <v>796</v>
+        <v>811</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -4788,29 +4892,33 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>797</v>
+        <v>812</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>798</v>
+        <v>813</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>799</v>
+        <v>814</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="G21" s="12"/>
+      <c r="G21" s="12" t="s">
+        <v>91</v>
+      </c>
       <c r="H21" s="12" t="s">
         <v>57</v>
       </c>
       <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
+      <c r="J21" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="K21" s="12" t="s">
-        <v>800</v>
+        <v>815</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -4822,29 +4930,33 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>801</v>
+        <v>816</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>802</v>
+        <v>817</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>803</v>
+        <v>818</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G22" s="12"/>
+      <c r="G22" s="12" t="s">
+        <v>91</v>
+      </c>
       <c r="H22" s="12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
+      <c r="J22" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="K22" s="12" t="s">
-        <v>805</v>
+        <v>820</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -4856,29 +4968,33 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>806</v>
+        <v>821</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>807</v>
+        <v>822</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>808</v>
+        <v>823</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>809</v>
+        <v>824</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="12"/>
+      <c r="G23" s="12" t="s">
+        <v>62</v>
+      </c>
       <c r="H23" s="12" t="s">
         <v>52</v>
       </c>
       <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
+      <c r="J23" s="12" t="s">
+        <v>63</v>
+      </c>
       <c r="K23" s="12" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -4890,29 +5006,35 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>811</v>
+        <v>826</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>812</v>
+        <v>827</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>813</v>
+        <v>828</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G24" s="12"/>
+      <c r="G24" s="12" t="s">
+        <v>62</v>
+      </c>
       <c r="H24" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
+      <c r="I24" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>308</v>
+      </c>
       <c r="K24" s="12" t="s">
-        <v>814</v>
+        <v>829</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -4924,31 +5046,35 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>815</v>
+        <v>830</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>816</v>
+        <v>831</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>817</v>
+        <v>832</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>818</v>
+        <v>833</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>819</v>
+        <v>834</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="G25" s="12"/>
+      <c r="G25" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H25" s="12" t="s">
         <v>52</v>
       </c>
       <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
+      <c r="J25" s="12" t="s">
+        <v>794</v>
+      </c>
       <c r="K25" s="12" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -4960,29 +5086,33 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>821</v>
+        <v>836</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>822</v>
+        <v>837</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>823</v>
+        <v>838</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>824</v>
+        <v>839</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G26" s="12"/>
+      <c r="G26" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H26" s="12" t="s">
         <v>52</v>
       </c>
       <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
+      <c r="J26" s="12" t="s">
+        <v>129</v>
+      </c>
       <c r="K26" s="12" t="s">
-        <v>825</v>
+        <v>840</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12" t="s">
@@ -4994,29 +5124,33 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>826</v>
+        <v>841</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>827</v>
+        <v>842</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>828</v>
+        <v>843</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G27" s="12"/>
+      <c r="G27" s="12" t="s">
+        <v>62</v>
+      </c>
       <c r="H27" s="12" t="s">
         <v>52</v>
       </c>
       <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
+      <c r="J27" s="12" t="s">
+        <v>129</v>
+      </c>
       <c r="K27" s="12" t="s">
-        <v>829</v>
+        <v>844</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12" t="s">
@@ -5028,29 +5162,33 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>830</v>
+        <v>845</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>831</v>
+        <v>846</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>832</v>
+        <v>847</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>833</v>
+        <v>848</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="G28" s="12"/>
+      <c r="G28" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H28" s="12" t="s">
         <v>52</v>
       </c>
       <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
+      <c r="J28" s="12" t="s">
+        <v>129</v>
+      </c>
       <c r="K28" s="12" t="s">
-        <v>834</v>
+        <v>849</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="12" t="s">
@@ -5062,29 +5200,33 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>835</v>
+        <v>850</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>836</v>
+        <v>851</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>808</v>
+        <v>823</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>837</v>
+        <v>852</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="G29" s="12"/>
+      <c r="G29" s="12" t="s">
+        <v>62</v>
+      </c>
       <c r="H29" s="12" t="s">
         <v>52</v>
       </c>
       <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
+      <c r="J29" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="K29" s="12" t="s">
-        <v>838</v>
+        <v>853</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12" t="s">
@@ -5096,29 +5238,33 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>839</v>
+        <v>854</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>841</v>
+        <v>856</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>842</v>
+        <v>857</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="G30" s="12"/>
+      <c r="G30" s="12" t="s">
+        <v>70</v>
+      </c>
       <c r="H30" s="12" t="s">
         <v>52</v>
       </c>
       <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
+      <c r="J30" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="K30" s="12" t="s">
-        <v>843</v>
+        <v>858</v>
       </c>
       <c r="L30" s="12"/>
       <c r="M30" s="12" t="s">
@@ -5129,17 +5275,35 @@
       <c r="P30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15"/>
-      <c r="B31" s="12"/>
+      <c r="A31" s="15" t="s">
+        <v>859</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>860</v>
+      </c>
       <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
+      <c r="D31" s="12" t="s">
+        <v>861</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>52</v>
+      </c>
       <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
+      <c r="J31" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>863</v>
+      </c>
       <c r="L31" s="12"/>
       <c r="M31" s="12"/>
       <c r="N31" s="12"/>
@@ -5267,7 +5431,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>844</v>
+        <v>864</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5281,7 +5445,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>845</v>
+        <v>865</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5289,7 +5453,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>846</v>
+        <v>866</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5297,7 +5461,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>847</v>
+        <v>867</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5305,7 +5469,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5313,7 +5477,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5321,7 +5485,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>850</v>
+        <v>870</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5337,7 +5501,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>851</v>
+        <v>871</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5345,7 +5509,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>852</v>
+        <v>872</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5353,7 +5517,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>852</v>
+        <v>872</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5407,17 +5571,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>853</v>
+        <v>873</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>854</v>
+        <v>874</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>699</v>
+        <v>708</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>855</v>
+        <v>875</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
@@ -5430,13 +5594,13 @@
         <v>53</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>856</v>
+        <v>876</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>857</v>
+        <v>877</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -5447,17 +5611,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>859</v>
+        <v>879</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>860</v>
+        <v>880</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>861</v>
+        <v>881</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>862</v>
+        <v>882</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>8</v>
@@ -5473,10 +5637,10 @@
         <v>54</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>863</v>
+        <v>883</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -5487,17 +5651,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>864</v>
+        <v>884</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>865</v>
+        <v>885</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>866</v>
+        <v>886</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>867</v>
+        <v>887</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>10</v>
@@ -5513,10 +5677,10 @@
         <v>129</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>868</v>
+        <v>888</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -5527,17 +5691,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>869</v>
+        <v>889</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>870</v>
+        <v>890</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>871</v>
+        <v>891</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>872</v>
+        <v>892</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>5</v>
@@ -5553,10 +5717,10 @@
         <v>54</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>873</v>
+        <v>893</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -5567,17 +5731,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>874</v>
+        <v>894</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>875</v>
+        <v>895</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>877</v>
+        <v>897</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>2</v>
@@ -5593,10 +5757,10 @@
         <v>129</v>
       </c>
       <c r="K21" s="12" t="s">
+        <v>898</v>
+      </c>
+      <c r="L21" s="12" t="s">
         <v>878</v>
-      </c>
-      <c r="L21" s="12" t="s">
-        <v>858</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -5607,17 +5771,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>879</v>
+        <v>899</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>881</v>
+        <v>901</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>15</v>
@@ -5630,13 +5794,13 @@
         <v>53</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>856</v>
+        <v>876</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -5647,19 +5811,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>887</v>
+        <v>907</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>19</v>
@@ -5675,10 +5839,10 @@
         <v>308</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -5689,17 +5853,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>889</v>
+        <v>909</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>890</v>
+        <v>910</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="15" t="s">
-        <v>891</v>
+        <v>911</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>892</v>
+        <v>912</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>1</v>
@@ -5715,10 +5879,10 @@
         <v>54</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>893</v>
+        <v>913</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -5729,17 +5893,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>895</v>
+        <v>915</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="15" t="s">
-        <v>896</v>
+        <v>916</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>897</v>
+        <v>917</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>20</v>
@@ -5755,10 +5919,10 @@
         <v>54</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>898</v>
+        <v>918</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -5769,17 +5933,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>899</v>
+        <v>919</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="15" t="s">
-        <v>901</v>
+        <v>921</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>902</v>
+        <v>922</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>25</v>
@@ -5795,10 +5959,10 @@
         <v>54</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>903</v>
+        <v>923</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -5809,19 +5973,19 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>904</v>
+        <v>924</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>905</v>
+        <v>925</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>907</v>
+        <v>927</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>3</v>
@@ -5834,13 +5998,13 @@
         <v>53</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>856</v>
+        <v>876</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>908</v>
+        <v>928</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -5851,17 +6015,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>909</v>
+        <v>929</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>910</v>
+        <v>930</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="15" t="s">
-        <v>911</v>
+        <v>931</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>17</v>
@@ -5877,10 +6041,10 @@
         <v>54</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>913</v>
+        <v>933</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -5891,17 +6055,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>914</v>
+        <v>934</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>915</v>
+        <v>935</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>916</v>
+        <v>936</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>917</v>
+        <v>937</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>26</v>
@@ -5917,10 +6081,10 @@
         <v>54</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>918</v>
+        <v>938</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -5931,17 +6095,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>919</v>
+        <v>939</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>920</v>
+        <v>940</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>921</v>
+        <v>941</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>922</v>
+        <v>942</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>7</v>
@@ -5951,10 +6115,10 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="12" t="s">
-        <v>923</v>
+        <v>943</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -6017,7 +6181,7 @@
         <v>147</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>889</v>
+        <v>909</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6025,7 +6189,7 @@
         <v>62</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>859</v>
+        <v>879</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6033,7 +6197,7 @@
         <v>148</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>864</v>
+        <v>884</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6041,7 +6205,7 @@
         <v>149</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6049,7 +6213,7 @@
         <v>70</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>869</v>
+        <v>889</v>
       </c>
     </row>
   </sheetData>
@@ -6108,7 +6272,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>924</v>
+        <v>944</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6122,7 +6286,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>925</v>
+        <v>945</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6130,7 +6294,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>926</v>
+        <v>946</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6138,7 +6302,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>927</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6152,7 +6316,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>928</v>
+        <v>948</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6160,7 +6324,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>929</v>
+        <v>949</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6176,7 +6340,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>930</v>
+        <v>950</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6184,7 +6348,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>931</v>
+        <v>951</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6192,7 +6356,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>931</v>
+        <v>951</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6252,14 +6416,14 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>932</v>
+        <v>952</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>933</v>
+        <v>953</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>934</v>
+        <v>954</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>271</v>
@@ -6275,10 +6439,10 @@
         <v>53</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>935</v>
+        <v>955</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>936</v>
+        <v>956</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -6294,17 +6458,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>937</v>
+        <v>957</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>938</v>
+        <v>958</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>939</v>
+        <v>959</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>940</v>
+        <v>960</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>6</v>
@@ -6317,10 +6481,10 @@
         <v>117</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>935</v>
+        <v>955</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>941</v>
+        <v>961</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -6336,19 +6500,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>942</v>
+        <v>962</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>943</v>
+        <v>963</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>944</v>
+        <v>964</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>945</v>
+        <v>965</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>946</v>
+        <v>966</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>17</v>
@@ -6362,7 +6526,7 @@
       </c>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>947</v>
+        <v>967</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -6378,17 +6542,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>948</v>
+        <v>968</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>949</v>
+        <v>969</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>951</v>
+        <v>971</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>7</v>
@@ -6401,10 +6565,10 @@
         <v>53</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>935</v>
+        <v>955</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>952</v>
+        <v>972</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -6420,17 +6584,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>953</v>
+        <v>973</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>954</v>
+        <v>974</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>955</v>
+        <v>975</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>956</v>
+        <v>976</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>10</v>
@@ -6444,7 +6608,7 @@
       </c>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>957</v>
+        <v>977</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -6460,17 +6624,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>958</v>
+        <v>978</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>959</v>
+        <v>979</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>960</v>
+        <v>980</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>961</v>
+        <v>981</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>19</v>
@@ -6483,10 +6647,10 @@
         <v>53</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>935</v>
+        <v>955</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>962</v>
+        <v>982</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -6502,17 +6666,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>963</v>
+        <v>983</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>964</v>
+        <v>984</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>965</v>
+        <v>985</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>966</v>
+        <v>986</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>20</v>
@@ -6528,7 +6692,7 @@
       </c>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>967</v>
+        <v>987</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -6544,17 +6708,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>968</v>
+        <v>988</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>969</v>
+        <v>989</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>971</v>
+        <v>991</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>5</v>
@@ -6567,10 +6731,10 @@
       </c>
       <c r="I24" s="12"/>
       <c r="J24" s="12" t="s">
-        <v>935</v>
+        <v>955</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>972</v>
+        <v>992</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -6582,17 +6746,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>973</v>
+        <v>993</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>974</v>
+        <v>994</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>975</v>
+        <v>995</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>976</v>
+        <v>996</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>11</v>
@@ -6604,7 +6768,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>977</v>
+        <v>997</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -6616,17 +6780,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>978</v>
+        <v>998</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>979</v>
+        <v>999</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>981</v>
+        <v>1001</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>12</v>
@@ -6639,10 +6803,10 @@
       </c>
       <c r="I26" s="12"/>
       <c r="J26" s="12" t="s">
-        <v>935</v>
+        <v>955</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>982</v>
+        <v>1002</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12" t="s">
@@ -6654,17 +6818,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>983</v>
+        <v>1003</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>984</v>
+        <v>1004</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>985</v>
+        <v>1005</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>986</v>
+        <v>1006</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>22</v>
@@ -6676,7 +6840,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>987</v>
+        <v>1007</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12" t="s">
@@ -6688,17 +6852,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>988</v>
+        <v>1008</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>989</v>
+        <v>1009</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>990</v>
+        <v>1010</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>991</v>
+        <v>1011</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>21</v>
@@ -6710,7 +6874,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
       <c r="K28" s="12" t="s">
-        <v>992</v>
+        <v>1012</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="12" t="s">
@@ -6722,17 +6886,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>993</v>
+        <v>1013</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>994</v>
+        <v>1014</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>995</v>
+        <v>1015</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>996</v>
+        <v>1016</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>9</v>
@@ -6744,7 +6908,7 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="12" t="s">
-        <v>997</v>
+        <v>1017</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12" t="s">
@@ -6756,17 +6920,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>998</v>
+        <v>1018</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>999</v>
+        <v>1019</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>1000</v>
+        <v>1020</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>1001</v>
+        <v>1021</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>14</v>
@@ -6778,7 +6942,7 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="12" t="s">
-        <v>1002</v>
+        <v>1022</v>
       </c>
       <c r="L30" s="12"/>
       <c r="M30" s="12" t="s">
@@ -6837,7 +7001,7 @@
         <v>147</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>963</v>
+        <v>983</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6845,7 +7009,7 @@
         <v>62</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>953</v>
+        <v>973</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6853,7 +7017,7 @@
         <v>148</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>942</v>
+        <v>962</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6861,7 +7025,7 @@
         <v>149</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>937</v>
+        <v>957</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6869,7 +7033,7 @@
         <v>70</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>932</v>
+        <v>952</v>
       </c>
     </row>
   </sheetData>
@@ -6928,7 +7092,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>1003</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6942,7 +7106,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1004</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6950,7 +7114,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1005</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6958,7 +7122,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1005</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6966,7 +7130,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>1006</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6974,7 +7138,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>1007</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6982,7 +7146,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1008</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6990,7 +7154,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>1009</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6998,7 +7162,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>1010</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7006,7 +7170,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>1011</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7014,7 +7178,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>1011</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7065,17 +7229,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1012</v>
+        <v>1032</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1013</v>
+        <v>1033</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>1014</v>
+        <v>1034</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>6</v>
@@ -7090,10 +7254,10 @@
         <v>117</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>935</v>
+        <v>955</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>1015</v>
+        <v>1035</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -7102,17 +7266,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1016</v>
+        <v>1036</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>1017</v>
+        <v>1037</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>1018</v>
+        <v>1038</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>1019</v>
+        <v>1039</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>19</v>
@@ -7127,10 +7291,10 @@
         <v>53</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>935</v>
+        <v>955</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>1020</v>
+        <v>1040</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -7139,17 +7303,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1021</v>
+        <v>1041</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>1022</v>
+        <v>1042</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
         <v>182</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>1023</v>
+        <v>1043</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>8</v>
@@ -7167,7 +7331,7 @@
         <v>129</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>1024</v>
+        <v>1044</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -7176,17 +7340,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1025</v>
+        <v>1045</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>1026</v>
+        <v>1046</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>1027</v>
+        <v>1047</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>1028</v>
+        <v>1048</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>11</v>
@@ -7201,10 +7365,10 @@
         <v>53</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>935</v>
+        <v>955</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>1029</v>
+        <v>1049</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -7213,17 +7377,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>1030</v>
+        <v>1050</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>1031</v>
+        <v>1051</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>1032</v>
+        <v>1052</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>1033</v>
+        <v>1053</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>26</v>
@@ -7235,7 +7399,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>1034</v>
+        <v>1054</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -7244,17 +7408,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>1035</v>
+        <v>1055</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>1036</v>
+        <v>1056</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>1037</v>
+        <v>1057</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>1038</v>
+        <v>1058</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>10</v>
@@ -7269,10 +7433,10 @@
         <v>53</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>935</v>
+        <v>955</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>1039</v>
+        <v>1059</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -7281,17 +7445,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>1040</v>
+        <v>1060</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>1041</v>
+        <v>1061</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>1042</v>
+        <v>1062</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>1043</v>
+        <v>1063</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>4</v>
@@ -7309,7 +7473,7 @@
         <v>129</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>1044</v>
+        <v>1064</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -7318,17 +7482,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>1045</v>
+        <v>1065</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>1046</v>
+        <v>1066</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>1047</v>
+        <v>1067</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>1048</v>
+        <v>1068</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>9</v>
@@ -7346,7 +7510,7 @@
         <v>129</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>1049</v>
+        <v>1069</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -7355,29 +7519,37 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>1050</v>
+        <v>1070</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C25" s="12"/>
+        <v>1071</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>1072</v>
+      </c>
       <c r="D25" s="12" t="s">
-        <v>1052</v>
+        <v>1073</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>1053</v>
+        <v>1074</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G25" s="12"/>
+      <c r="G25" s="12" t="s">
+        <v>91</v>
+      </c>
       <c r="H25" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
+        <v>57</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>1075</v>
+      </c>
       <c r="K25" s="12" t="s">
-        <v>1054</v>
+        <v>1076</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -7386,17 +7558,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>1055</v>
+        <v>1077</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>1056</v>
+        <v>1078</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>803</v>
+        <v>818</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>1038</v>
+        <v>1058</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>7</v>
@@ -7411,10 +7583,10 @@
         <v>53</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>935</v>
+        <v>955</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>1057</v>
+        <v>1079</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12" t="s">
@@ -7423,17 +7595,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>1058</v>
+        <v>1080</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>1059</v>
+        <v>1081</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>1060</v>
+        <v>1082</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>1061</v>
+        <v>1083</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>15</v>
@@ -7445,7 +7617,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>1062</v>
+        <v>1084</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12" t="s">
@@ -7454,17 +7626,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>1063</v>
+        <v>1085</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>1064</v>
+        <v>1086</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>1065</v>
+        <v>1087</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>1066</v>
+        <v>1088</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>18</v>
@@ -7474,9 +7646,11 @@
         <v>52</v>
       </c>
       <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
+      <c r="J28" s="1" t="s">
+        <v>129</v>
+      </c>
       <c r="K28" s="12" t="s">
-        <v>1067</v>
+        <v>1089</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="12" t="s">
@@ -7485,17 +7659,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>1068</v>
+        <v>1090</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1069</v>
+        <v>1091</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>1018</v>
+        <v>1038</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>1070</v>
+        <v>1092</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>12</v>
@@ -7505,9 +7679,11 @@
         <v>52</v>
       </c>
       <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
+      <c r="J29" s="1" t="s">
+        <v>129</v>
+      </c>
       <c r="K29" s="12" t="s">
-        <v>1071</v>
+        <v>1093</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12" t="s">
@@ -7516,17 +7692,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>1072</v>
+        <v>1094</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>1073</v>
+        <v>1095</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>1074</v>
+        <v>1096</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>1075</v>
+        <v>1097</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>1</v>
@@ -7540,7 +7716,7 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="12" t="s">
-        <v>1076</v>
+        <v>1098</v>
       </c>
       <c r="L30" s="12"/>
       <c r="M30" s="12" t="s">
@@ -7549,17 +7725,17 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>1077</v>
+        <v>1099</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>1078</v>
+        <v>1100</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12" t="s">
-        <v>1079</v>
+        <v>1101</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>1080</v>
+        <v>1102</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>3</v>
@@ -7571,7 +7747,7 @@
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
       <c r="K31" s="12" t="s">
-        <v>1081</v>
+        <v>1103</v>
       </c>
       <c r="L31" s="12"/>
       <c r="M31" s="12" t="s">
@@ -7580,17 +7756,17 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>1082</v>
+        <v>1104</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>1083</v>
+        <v>1105</v>
       </c>
       <c r="C32" s="12"/>
       <c r="D32" s="12" t="s">
         <v>182</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>1070</v>
+        <v>1092</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>21</v>
@@ -7605,10 +7781,10 @@
         <v>53</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>935</v>
+        <v>955</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>1084</v>
+        <v>1106</v>
       </c>
       <c r="L32" s="18"/>
       <c r="M32" s="12" t="s">
@@ -7617,26 +7793,32 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>1085</v>
+        <v>1107</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>1086</v>
+        <v>1108</v>
       </c>
       <c r="C33" s="12"/>
       <c r="D33" s="12" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>1087</v>
+        <v>1109</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>20</v>
       </c>
+      <c r="G33" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="H33" s="12" t="s">
-        <v>52</v>
+        <v>57</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>1088</v>
+        <v>1110</v>
       </c>
       <c r="M33" s="12" t="s">
         <v>57</v>
@@ -7644,17 +7826,17 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>1089</v>
+        <v>1111</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>1090</v>
+        <v>1112</v>
       </c>
       <c r="C34" s="12"/>
       <c r="D34" s="12" t="s">
-        <v>1091</v>
+        <v>1113</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>1092</v>
+        <v>1114</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>22</v>
@@ -7663,7 +7845,7 @@
         <v>52</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>1093</v>
+        <v>1115</v>
       </c>
       <c r="M34" s="12" t="s">
         <v>57</v>
@@ -11408,53 +11590,65 @@
       <c r="A6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="12"/>
+      <c r="B6" s="12" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="16"/>
+      <c r="B7" s="16" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="12"/>
+      <c r="B9" s="12" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="12"/>
+      <c r="B10" s="12" t="s">
+        <v>434</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="12"/>
+      <c r="B12" s="12" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="12"/>
+      <c r="B13" s="12" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -11507,17 +11701,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
@@ -11535,10 +11729,10 @@
         <v>54</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -11549,17 +11743,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>14</v>
@@ -11574,13 +11768,13 @@
         <v>53</v>
       </c>
       <c r="J18" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="L18" s="12" t="s">
         <v>442</v>
-      </c>
-      <c r="K18" s="12" t="s">
-        <v>443</v>
-      </c>
-      <c r="L18" s="12" t="s">
-        <v>437</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -11591,17 +11785,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>4</v>
@@ -11619,10 +11813,10 @@
         <v>129</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -11633,17 +11827,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>6</v>
@@ -11661,10 +11855,10 @@
         <v>54</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -11675,17 +11869,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>17</v>
@@ -11703,10 +11897,10 @@
         <v>54</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -11717,17 +11911,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>5</v>
@@ -11742,13 +11936,13 @@
         <v>117</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -11759,17 +11953,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>9</v>
@@ -11787,10 +11981,10 @@
         <v>54</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -11801,19 +11995,19 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>2</v>
@@ -11831,10 +12025,10 @@
         <v>308</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -11845,17 +12039,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>20</v>
@@ -11873,10 +12067,10 @@
         <v>54</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -11887,17 +12081,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>7</v>
@@ -11915,10 +12109,10 @@
         <v>129</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -11929,17 +12123,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>3</v>
@@ -11957,10 +12151,10 @@
         <v>129</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -11971,17 +12165,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>1</v>
@@ -11996,13 +12190,13 @@
         <v>53</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -12013,17 +12207,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>10</v>
@@ -12041,10 +12235,10 @@
         <v>54</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -12055,17 +12249,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>19</v>
@@ -12083,10 +12277,10 @@
         <v>54</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -12097,19 +12291,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>12</v>
@@ -12127,10 +12321,10 @@
         <v>54</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M31" s="12" t="s">
         <v>57</v>
@@ -12141,16 +12335,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>13</v>
@@ -12168,10 +12362,10 @@
         <v>54</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M32" s="12" t="s">
         <v>57</v>
@@ -12179,16 +12373,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>8</v>
@@ -12206,10 +12400,10 @@
         <v>54</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12248,7 +12442,7 @@
         <v>147</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12256,7 +12450,7 @@
         <v>62</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12264,7 +12458,7 @@
         <v>148</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12272,7 +12466,7 @@
         <v>149</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12280,7 +12474,7 @@
         <v>70</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -12339,7 +12533,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12353,7 +12547,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12361,7 +12555,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12369,7 +12563,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12383,7 +12577,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12391,7 +12585,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12399,7 +12593,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12407,7 +12601,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12473,17 +12667,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
@@ -12501,10 +12695,10 @@
         <v>129</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -12515,17 +12709,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>10</v>
@@ -12537,16 +12731,16 @@
         <v>52</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="J18" s="12" t="s">
         <v>129</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -12557,17 +12751,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>18</v>
@@ -12585,10 +12779,10 @@
         <v>54</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -12599,17 +12793,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>5</v>
@@ -12627,10 +12821,10 @@
         <v>129</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -12641,17 +12835,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>9</v>
@@ -12669,10 +12863,10 @@
         <v>54</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -12683,17 +12877,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>7</v>
@@ -12711,10 +12905,10 @@
         <v>54</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -12725,17 +12919,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>6</v>
@@ -12753,10 +12947,10 @@
         <v>54</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -12767,17 +12961,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>20</v>
@@ -12795,10 +12989,10 @@
         <v>54</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -12809,17 +13003,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>14</v>
@@ -12837,10 +13031,10 @@
         <v>54</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -12851,17 +13045,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>1</v>
@@ -12879,10 +13073,10 @@
         <v>54</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -12893,17 +13087,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>3</v>
@@ -12921,10 +13115,10 @@
         <v>54</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -12935,17 +13129,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>2</v>
@@ -12963,10 +13157,10 @@
         <v>54</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -12977,17 +13171,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>13</v>
@@ -13005,10 +13199,10 @@
         <v>54</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -13019,19 +13213,19 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>8</v>
@@ -13049,10 +13243,10 @@
         <v>308</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -13063,17 +13257,17 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>12</v>
@@ -13091,10 +13285,10 @@
         <v>54</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M31" s="12" t="s">
         <v>57</v>
@@ -13105,17 +13299,17 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="C32" s="0"/>
       <c r="D32" s="0" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="F32" s="0" t="n">
         <v>22</v>
@@ -13127,16 +13321,16 @@
         <v>52</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="J32" s="12" t="s">
         <v>54</v>
       </c>
       <c r="K32" s="0" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M32" s="12" t="s">
         <v>57</v>
@@ -13147,17 +13341,17 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="C33" s="0"/>
       <c r="D33" s="0" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="F33" s="0" t="n">
         <v>19</v>
@@ -13175,10 +13369,10 @@
         <v>54</v>
       </c>
       <c r="K33" s="0" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="M33" s="12" t="s">
         <v>57</v>
@@ -13223,7 +13417,7 @@
         <v>147</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13231,7 +13425,7 @@
         <v>62</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13239,7 +13433,7 @@
         <v>148</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13247,7 +13441,7 @@
         <v>149</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13255,7 +13449,7 @@
         <v>70</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
     </row>
   </sheetData>
@@ -13314,7 +13508,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13328,7 +13522,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13336,47 +13530,55 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="12"/>
+      <c r="B6" s="12" t="s">
+        <v>624</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="12"/>
+      <c r="B7" s="25" t="s">
+        <v>625</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="12"/>
+      <c r="B9" s="12" t="s">
+        <v>627</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="12"/>
+      <c r="B10" s="12" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13448,34 +13650,36 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G17" s="12"/>
+      <c r="G17" s="12" t="s">
+        <v>62</v>
+      </c>
       <c r="H17" s="12" t="s">
         <v>52</v>
       </c>
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -13490,19 +13694,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>14</v>
@@ -13514,10 +13718,10 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -13532,32 +13736,36 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G19" s="12"/>
+      <c r="G19" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H19" s="12" t="s">
         <v>52</v>
       </c>
       <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
+      <c r="J19" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="K19" s="12" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -13572,32 +13780,36 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G20" s="12"/>
+      <c r="G20" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H20" s="12" t="s">
         <v>52</v>
       </c>
       <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
+      <c r="J20" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="K20" s="12" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -13612,32 +13824,36 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G21" s="12"/>
+      <c r="G21" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H21" s="12" t="s">
         <v>52</v>
       </c>
       <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
+      <c r="J21" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="K21" s="12" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -13652,32 +13868,38 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>650</v>
-      </c>
-      <c r="C22" s="12"/>
+        <v>657</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>658</v>
+      </c>
       <c r="D22" s="12" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="G22" s="12"/>
+      <c r="G22" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H22" s="12" t="s">
         <v>52</v>
       </c>
       <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
+      <c r="J22" s="12" t="s">
+        <v>308</v>
+      </c>
       <c r="K22" s="12" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -13692,17 +13914,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
         <v>115</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>17</v>
@@ -13712,12 +13934,14 @@
         <v>52</v>
       </c>
       <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
+      <c r="J23" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="K23" s="12" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -13732,32 +13956,36 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G24" s="12"/>
+      <c r="G24" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H24" s="12" t="s">
         <v>52</v>
       </c>
       <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
+      <c r="J24" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="K24" s="12" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -13768,32 +13996,38 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>664</v>
-      </c>
-      <c r="C25" s="12"/>
+        <v>672</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>673</v>
+      </c>
       <c r="D25" s="12" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="G25" s="12"/>
+      <c r="G25" s="12" t="s">
+        <v>91</v>
+      </c>
       <c r="H25" s="12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
+      <c r="J25" s="12" t="s">
+        <v>468</v>
+      </c>
       <c r="K25" s="12" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -13804,32 +14038,36 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>670</v>
+        <v>679</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G26" s="12"/>
+      <c r="G26" s="12" t="s">
+        <v>91</v>
+      </c>
       <c r="H26" s="12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
+      <c r="J26" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="K26" s="12" t="s">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -13840,17 +14078,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>673</v>
+        <v>682</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>674</v>
+        <v>683</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
         <v>127</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>5</v>
@@ -13862,10 +14100,10 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -13876,17 +14114,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>678</v>
+        <v>687</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>679</v>
+        <v>688</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>680</v>
+        <v>689</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>9</v>
@@ -13898,10 +14136,10 @@
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
       <c r="K28" s="12" t="s">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -13912,17 +14150,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>682</v>
+        <v>691</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>683</v>
+        <v>692</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>684</v>
+        <v>693</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>15</v>
@@ -13934,10 +14172,10 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="12" t="s">
-        <v>685</v>
+        <v>694</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -13948,17 +14186,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>687</v>
+        <v>696</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>688</v>
+        <v>697</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>689</v>
+        <v>698</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>22</v>
@@ -13970,10 +14208,10 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="12" t="s">
-        <v>690</v>
+        <v>699</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -14121,7 +14359,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>691</v>
+        <v>700</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14135,7 +14373,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>692</v>
+        <v>701</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14143,7 +14381,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>693</v>
+        <v>702</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14163,7 +14401,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>694</v>
+        <v>703</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14183,7 +14421,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>695</v>
+        <v>704</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14249,19 +14487,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>696</v>
+        <v>705</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>697</v>
+        <v>706</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>698</v>
+        <v>707</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>699</v>
+        <v>708</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
@@ -14276,13 +14514,13 @@
         <v>53</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>702</v>
+        <v>711</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -14293,17 +14531,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>704</v>
+        <v>713</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>706</v>
+        <v>715</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>18</v>
@@ -14321,10 +14559,10 @@
         <v>54</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>708</v>
+        <v>717</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -14335,19 +14573,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>709</v>
+        <v>718</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>712</v>
+        <v>721</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>713</v>
+        <v>722</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>7</v>
@@ -14362,13 +14600,13 @@
         <v>53</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>714</v>
+        <v>723</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -14379,17 +14617,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>716</v>
+        <v>725</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>717</v>
+        <v>726</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>718</v>
+        <v>727</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>10</v>
@@ -14407,10 +14645,10 @@
         <v>54</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>719</v>
+        <v>728</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -14421,19 +14659,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>723</v>
+        <v>732</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>724</v>
+        <v>733</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>13</v>
@@ -14451,10 +14689,10 @@
         <v>308</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>725</v>
+        <v>734</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -14465,14 +14703,14 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>726</v>
+        <v>735</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>727</v>
+        <v>736</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>728</v>
+        <v>737</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>168</v>
@@ -14493,10 +14731,10 @@
         <v>54</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>729</v>
+        <v>738</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -14507,17 +14745,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>730</v>
+        <v>739</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>731</v>
+        <v>740</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
         <v>341</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>732</v>
+        <v>741</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>5</v>
@@ -14535,10 +14773,10 @@
         <v>129</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -14549,17 +14787,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>734</v>
+        <v>743</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>735</v>
+        <v>744</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>737</v>
+        <v>746</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>8</v>
@@ -14574,13 +14812,13 @@
         <v>117</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>738</v>
+        <v>747</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -14591,17 +14829,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>739</v>
+        <v>748</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>740</v>
+        <v>749</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>741</v>
+        <v>750</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>742</v>
+        <v>751</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>17</v>
@@ -14619,10 +14857,10 @@
         <v>54</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>743</v>
+        <v>752</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -14633,17 +14871,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>744</v>
+        <v>753</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="11" t="s">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>746</v>
+        <v>755</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>20</v>
@@ -14661,10 +14899,10 @@
         <v>54</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>747</v>
+        <v>756</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -14675,17 +14913,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>748</v>
+        <v>757</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>749</v>
+        <v>758</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="11" t="s">
-        <v>750</v>
+        <v>759</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>751</v>
+        <v>760</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>9</v>
@@ -14703,10 +14941,10 @@
         <v>129</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>752</v>
+        <v>761</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -14717,17 +14955,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>754</v>
+        <v>763</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="11" t="s">
-        <v>755</v>
+        <v>764</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>756</v>
+        <v>765</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>1</v>
@@ -14745,10 +14983,10 @@
         <v>54</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>757</v>
+        <v>766</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -14759,16 +14997,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>759</v>
+        <v>768</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>2</v>
@@ -14786,10 +15024,10 @@
         <v>54</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>762</v>
+        <v>771</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -14797,16 +15035,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>763</v>
+        <v>772</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>764</v>
+        <v>773</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>765</v>
+        <v>774</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>12</v>
@@ -14821,13 +15059,13 @@
         <v>53</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>767</v>
+        <v>776</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -14835,13 +15073,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>769</v>
+        <v>778</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>770</v>
+        <v>779</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>770</v>
+        <v>779</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>15</v>
@@ -14859,10 +15097,10 @@
         <v>308</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>771</v>
+        <v>780</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="M31" s="12" t="s">
         <v>57</v>
@@ -14904,7 +15142,7 @@
         <v>147</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>753</v>
+        <v>762</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14912,7 +15150,7 @@
         <v>62</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>715</v>
+        <v>724</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14920,7 +15158,7 @@
         <v>148</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>696</v>
+        <v>705</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14928,7 +15166,7 @@
         <v>149</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>739</v>
+        <v>748</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14936,7 +15174,7 @@
         <v>70</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>748</v>
+        <v>757</v>
       </c>
     </row>
   </sheetData>

--- a/D1_Fiches_Clubs_Joueurs_26_27.xlsx
+++ b/D1_Fiches_Clubs_Joueurs_26_27.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Mode emploi" sheetId="1" state="visible" r:id="rId3"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2422" uniqueCount="1116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2462" uniqueCount="1117">
   <si>
     <t xml:space="preserve">FICHES CLUBS · D1 FUTSAL 2026-2027</t>
   </si>
@@ -608,6 +608,9 @@
     <t xml:space="preserve">Hakan-bulbul.png</t>
   </si>
   <si>
+    <t xml:space="preserve">Instagram ARTISTES FUTSAL</t>
+  </si>
+  <si>
     <t xml:space="preserve">mamadou-sako</t>
   </si>
   <si>
@@ -1077,7 +1080,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">islem berrada </t>
+    <t xml:space="preserve">Islem-berrada </t>
   </si>
   <si>
     <t xml:space="preserve">ISLEM BERRADA </t>
@@ -1097,7 +1100,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">islem berrada</t>
+      <t xml:space="preserve">Islem-berrada</t>
     </r>
     <r>
       <rPr>
@@ -4592,7 +4595,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4606,7 +4609,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4614,7 +4617,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4622,7 +4625,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4630,7 +4633,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4638,7 +4641,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4654,7 +4657,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4662,7 +4665,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4670,7 +4673,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4678,7 +4681,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4732,19 +4735,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>9</v>
@@ -4757,10 +4760,10 @@
       </c>
       <c r="I17" s="12"/>
       <c r="J17" s="12" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -4772,17 +4775,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>14</v>
@@ -4800,7 +4803,7 @@
         <v>54</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -4812,19 +4815,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>19</v>
@@ -4839,10 +4842,10 @@
         <v>53</v>
       </c>
       <c r="J19" s="25" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -4854,17 +4857,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>6</v>
@@ -4880,7 +4883,7 @@
         <v>129</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -4892,17 +4895,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>12</v>
@@ -4918,7 +4921,7 @@
         <v>54</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -4930,17 +4933,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>20</v>
@@ -4956,7 +4959,7 @@
         <v>54</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -4968,17 +4971,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>3</v>
@@ -4994,7 +4997,7 @@
         <v>63</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -5006,17 +5009,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>5</v>
@@ -5031,10 +5034,10 @@
         <v>117</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -5046,19 +5049,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>18</v>
@@ -5071,10 +5074,10 @@
       </c>
       <c r="I25" s="12"/>
       <c r="J25" s="12" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -5086,17 +5089,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>7</v>
@@ -5112,7 +5115,7 @@
         <v>129</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12" t="s">
@@ -5124,17 +5127,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>8</v>
@@ -5150,7 +5153,7 @@
         <v>129</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12" t="s">
@@ -5162,17 +5165,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>26</v>
@@ -5188,7 +5191,7 @@
         <v>129</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="12" t="s">
@@ -5200,17 +5203,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>17</v>
@@ -5226,7 +5229,7 @@
         <v>54</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12" t="s">
@@ -5238,17 +5241,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>26</v>
@@ -5264,7 +5267,7 @@
         <v>54</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="L30" s="12"/>
       <c r="M30" s="12" t="s">
@@ -5276,17 +5279,17 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>10</v>
@@ -5302,7 +5305,7 @@
         <v>63</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="L31" s="12"/>
       <c r="M31" s="12"/>
@@ -5431,7 +5434,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5445,7 +5448,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5453,7 +5456,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5461,7 +5464,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5469,7 +5472,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5477,7 +5480,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5485,7 +5488,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5493,7 +5496,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5501,7 +5504,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5509,7 +5512,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5517,7 +5520,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5571,22 +5574,24 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="G17" s="12"/>
+      <c r="G17" s="12" t="s">
+        <v>70</v>
+      </c>
       <c r="H17" s="12" t="s">
         <v>52</v>
       </c>
@@ -5594,13 +5599,13 @@
         <v>53</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -5611,22 +5616,24 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G18" s="12"/>
+      <c r="G18" s="12" t="s">
+        <v>62</v>
+      </c>
       <c r="H18" s="12" t="s">
         <v>52</v>
       </c>
@@ -5637,10 +5644,10 @@
         <v>54</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -5651,22 +5658,24 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G19" s="12"/>
+      <c r="G19" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H19" s="12" t="s">
         <v>52</v>
       </c>
@@ -5677,10 +5686,10 @@
         <v>129</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -5691,22 +5700,24 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="G20" s="12"/>
+      <c r="G20" s="12" t="s">
+        <v>70</v>
+      </c>
       <c r="H20" s="12" t="s">
         <v>52</v>
       </c>
@@ -5717,10 +5728,10 @@
         <v>54</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -5731,22 +5742,24 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G21" s="12"/>
+      <c r="G21" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H21" s="12" t="s">
         <v>52</v>
       </c>
@@ -5757,10 +5770,10 @@
         <v>129</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -5771,22 +5784,24 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="G22" s="12"/>
+      <c r="G22" s="12" t="s">
+        <v>70</v>
+      </c>
       <c r="H22" s="12" t="s">
         <v>52</v>
       </c>
@@ -5794,13 +5809,13 @@
         <v>53</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -5811,24 +5826,26 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G23" s="12"/>
+      <c r="G23" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H23" s="12" t="s">
         <v>52</v>
       </c>
@@ -5836,13 +5853,13 @@
         <v>53</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -5853,22 +5870,24 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="15" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="12"/>
+      <c r="G24" s="12" t="s">
+        <v>91</v>
+      </c>
       <c r="H24" s="12" t="s">
         <v>57</v>
       </c>
@@ -5879,10 +5898,10 @@
         <v>54</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -5893,22 +5912,24 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="15" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="G25" s="12"/>
+      <c r="G25" s="12" t="s">
+        <v>91</v>
+      </c>
       <c r="H25" s="12" t="s">
         <v>57</v>
       </c>
@@ -5919,10 +5940,10 @@
         <v>54</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -5933,22 +5954,24 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="15" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G26" s="12"/>
+      <c r="G26" s="12" t="s">
+        <v>91</v>
+      </c>
       <c r="H26" s="12" t="s">
         <v>57</v>
       </c>
@@ -5959,10 +5982,10 @@
         <v>54</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -5973,24 +5996,26 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D27" s="15" t="s">
+        <v>928</v>
+      </c>
+      <c r="E27" s="15" t="s">
         <v>927</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>926</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G27" s="12"/>
+      <c r="G27" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H27" s="12" t="s">
         <v>52</v>
       </c>
@@ -5998,13 +6023,13 @@
         <v>53</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -6015,22 +6040,24 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="15" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="G28" s="12"/>
+      <c r="G28" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H28" s="12" t="s">
         <v>52</v>
       </c>
@@ -6041,10 +6068,10 @@
         <v>54</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -6055,22 +6082,24 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="G29" s="12"/>
+      <c r="G29" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H29" s="12" t="s">
         <v>52</v>
       </c>
@@ -6081,10 +6110,10 @@
         <v>54</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -6095,30 +6124,36 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
+      <c r="G30" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="J30" s="12"/>
       <c r="K30" s="12" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -6181,7 +6216,7 @@
         <v>147</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6189,7 +6224,7 @@
         <v>62</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6197,7 +6232,7 @@
         <v>148</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6205,7 +6240,7 @@
         <v>149</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6213,7 +6248,7 @@
         <v>70</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
   </sheetData>
@@ -6272,7 +6307,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6286,7 +6321,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6294,7 +6329,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6302,7 +6337,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6316,7 +6351,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6324,7 +6359,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6340,7 +6375,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6348,7 +6383,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6356,7 +6391,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6408,25 +6443,25 @@
         <v>46</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>8</v>
@@ -6439,10 +6474,10 @@
         <v>53</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -6458,17 +6493,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>6</v>
@@ -6481,10 +6516,10 @@
         <v>117</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -6500,19 +6535,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>17</v>
@@ -6526,7 +6561,7 @@
       </c>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -6542,17 +6577,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>7</v>
@@ -6565,10 +6600,10 @@
         <v>53</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -6584,17 +6619,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>10</v>
@@ -6608,7 +6643,7 @@
       </c>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -6624,17 +6659,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>19</v>
@@ -6647,10 +6682,10 @@
         <v>53</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -6666,17 +6701,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>20</v>
@@ -6692,7 +6727,7 @@
       </c>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -6708,17 +6743,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>5</v>
@@ -6731,10 +6766,10 @@
       </c>
       <c r="I24" s="12"/>
       <c r="J24" s="12" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -6746,17 +6781,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>11</v>
@@ -6768,7 +6803,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -6780,17 +6815,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>12</v>
@@ -6803,10 +6838,10 @@
       </c>
       <c r="I26" s="12"/>
       <c r="J26" s="12" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12" t="s">
@@ -6818,17 +6853,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>22</v>
@@ -6840,7 +6875,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12" t="s">
@@ -6852,17 +6887,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>21</v>
@@ -6874,7 +6909,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
       <c r="K28" s="12" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="12" t="s">
@@ -6886,17 +6921,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>9</v>
@@ -6908,7 +6943,7 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="12" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12" t="s">
@@ -6920,17 +6955,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>14</v>
@@ -6942,7 +6977,7 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="12" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="L30" s="12"/>
       <c r="M30" s="12" t="s">
@@ -7001,7 +7036,7 @@
         <v>147</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7009,7 +7044,7 @@
         <v>62</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7017,7 +7052,7 @@
         <v>148</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7025,7 +7060,7 @@
         <v>149</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7033,7 +7068,7 @@
         <v>70</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
   </sheetData>
@@ -7092,7 +7127,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7106,7 +7141,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7114,7 +7149,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7122,7 +7157,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7130,7 +7165,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7138,7 +7173,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7146,7 +7181,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7154,7 +7189,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7162,7 +7197,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7170,7 +7205,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7178,7 +7213,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7229,17 +7264,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>6</v>
@@ -7254,10 +7289,10 @@
         <v>117</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -7266,17 +7301,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>19</v>
@@ -7291,10 +7326,10 @@
         <v>53</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -7303,17 +7338,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>8</v>
@@ -7331,7 +7366,7 @@
         <v>129</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -7340,17 +7375,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>11</v>
@@ -7365,10 +7400,10 @@
         <v>53</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -7377,17 +7412,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>26</v>
@@ -7399,7 +7434,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -7408,17 +7443,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>10</v>
@@ -7433,10 +7468,10 @@
         <v>53</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -7445,17 +7480,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>4</v>
@@ -7473,7 +7508,7 @@
         <v>129</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -7482,17 +7517,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>9</v>
@@ -7510,7 +7545,7 @@
         <v>129</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -7519,19 +7554,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>25</v>
@@ -7546,10 +7581,10 @@
         <v>53</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -7558,17 +7593,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>7</v>
@@ -7583,10 +7618,10 @@
         <v>53</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12" t="s">
@@ -7595,17 +7630,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>15</v>
@@ -7617,7 +7652,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12" t="s">
@@ -7626,17 +7661,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>18</v>
@@ -7650,7 +7685,7 @@
         <v>129</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="12" t="s">
@@ -7659,17 +7694,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>12</v>
@@ -7683,7 +7718,7 @@
         <v>129</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12" t="s">
@@ -7692,17 +7727,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>1</v>
@@ -7716,7 +7751,7 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="12" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="L30" s="12"/>
       <c r="M30" s="12" t="s">
@@ -7725,17 +7760,17 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>3</v>
@@ -7747,7 +7782,7 @@
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
       <c r="K31" s="12" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="L31" s="12"/>
       <c r="M31" s="12" t="s">
@@ -7756,17 +7791,17 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="C32" s="12"/>
       <c r="D32" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>21</v>
@@ -7781,10 +7816,10 @@
         <v>53</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="L32" s="18"/>
       <c r="M32" s="12" t="s">
@@ -7793,17 +7828,17 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C33" s="12"/>
       <c r="D33" s="12" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>20</v>
@@ -7818,7 +7853,7 @@
         <v>129</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="M33" s="12" t="s">
         <v>57</v>
@@ -7826,17 +7861,17 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C34" s="12"/>
       <c r="D34" s="12" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>22</v>
@@ -7845,7 +7880,7 @@
         <v>52</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="M34" s="12" t="s">
         <v>57</v>
@@ -8039,7 +8074,9 @@
       <c r="A13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="12"/>
+      <c r="B13" s="12" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -9105,7 +9142,9 @@
       <c r="K17" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="L17" s="12"/>
+      <c r="L17" s="12" t="s">
+        <v>166</v>
+      </c>
       <c r="M17" s="12"/>
       <c r="N17" s="12"/>
       <c r="O17" s="14"/>
@@ -9113,17 +9152,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
         <v>84</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>7</v>
@@ -9141,9 +9180,11 @@
         <v>54</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="L18" s="12"/>
+        <v>170</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>166</v>
+      </c>
       <c r="M18" s="12"/>
       <c r="N18" s="12"/>
       <c r="O18" s="14"/>
@@ -9151,17 +9192,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>13</v>
@@ -9179,9 +9220,11 @@
         <v>54</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="L19" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>166</v>
+      </c>
       <c r="M19" s="12"/>
       <c r="N19" s="12"/>
       <c r="O19" s="14"/>
@@ -9189,17 +9232,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
         <v>110</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>8</v>
@@ -9217,9 +9260,11 @@
         <v>54</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="L20" s="12"/>
+        <v>179</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>166</v>
+      </c>
       <c r="M20" s="12"/>
       <c r="N20" s="12"/>
       <c r="O20" s="14"/>
@@ -9227,19 +9272,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>4</v>
@@ -9257,9 +9302,11 @@
         <v>54</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="L21" s="12"/>
+        <v>185</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>166</v>
+      </c>
       <c r="M21" s="12"/>
       <c r="N21" s="12"/>
       <c r="O21" s="14"/>
@@ -9267,17 +9314,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
         <v>105</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>16</v>
@@ -9295,9 +9342,11 @@
         <v>54</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="L22" s="12"/>
+        <v>189</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>166</v>
+      </c>
       <c r="M22" s="12"/>
       <c r="N22" s="12"/>
       <c r="O22" s="14"/>
@@ -9305,17 +9354,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>17</v>
@@ -9333,9 +9382,11 @@
         <v>54</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="L23" s="12"/>
+        <v>194</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>166</v>
+      </c>
       <c r="M23" s="12"/>
       <c r="N23" s="12"/>
       <c r="O23" s="14"/>
@@ -9343,17 +9394,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>21</v>
@@ -9371,9 +9422,11 @@
         <v>129</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="L24" s="12"/>
+        <v>199</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>166</v>
+      </c>
       <c r="M24" s="12"/>
       <c r="N24" s="12"/>
       <c r="O24" s="14"/>
@@ -9381,17 +9434,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>1</v>
@@ -9409,9 +9462,11 @@
         <v>129</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="L25" s="12"/>
+        <v>203</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>166</v>
+      </c>
       <c r="M25" s="12"/>
       <c r="N25" s="12"/>
       <c r="O25" s="14"/>
@@ -9419,17 +9474,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>25</v>
@@ -9444,12 +9499,14 @@
         <v>53</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="L26" s="12"/>
+        <v>209</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>166</v>
+      </c>
       <c r="M26" s="12"/>
       <c r="N26" s="12"/>
       <c r="O26" s="12"/>
@@ -9457,17 +9514,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>24</v>
@@ -9485,9 +9542,11 @@
         <v>63</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="L27" s="12"/>
+        <v>214</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>166</v>
+      </c>
       <c r="M27" s="12"/>
       <c r="N27" s="12"/>
       <c r="O27" s="12"/>
@@ -9495,17 +9554,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>14</v>
@@ -9523,9 +9582,11 @@
         <v>54</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="L28" s="12"/>
+        <v>218</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>166</v>
+      </c>
       <c r="M28" s="12"/>
       <c r="N28" s="12"/>
       <c r="O28" s="12"/>
@@ -9533,17 +9594,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>5</v>
@@ -9561,9 +9622,11 @@
         <v>54</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="L29" s="12"/>
+        <v>223</v>
+      </c>
+      <c r="L29" s="12" t="s">
+        <v>166</v>
+      </c>
       <c r="M29" s="12"/>
       <c r="N29" s="12"/>
       <c r="O29" s="12"/>
@@ -9571,17 +9634,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>19</v>
@@ -9599,9 +9662,11 @@
         <v>54</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="L30" s="12"/>
+        <v>228</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>166</v>
+      </c>
       <c r="M30" s="12"/>
       <c r="N30" s="12"/>
       <c r="O30" s="12"/>
@@ -9609,17 +9674,17 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>10</v>
@@ -9637,9 +9702,11 @@
         <v>54</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="L31" s="12"/>
+        <v>233</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>166</v>
+      </c>
       <c r="M31" s="12"/>
       <c r="N31" s="12"/>
       <c r="O31" s="12"/>
@@ -9647,22 +9714,25 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>9</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9701,7 +9771,7 @@
         <v>147</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9709,7 +9779,7 @@
         <v>62</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9717,7 +9787,7 @@
         <v>148</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9733,7 +9803,7 @@
         <v>70</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -9792,7 +9862,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9806,7 +9876,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9814,7 +9884,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9822,7 +9892,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9830,7 +9900,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9838,7 +9908,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9854,7 +9924,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9862,7 +9932,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9870,7 +9940,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9878,7 +9948,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9933,17 +10003,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>8</v>
@@ -9961,10 +10031,10 @@
         <v>54</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M17" s="12"/>
       <c r="N17" s="12"/>
@@ -9973,17 +10043,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>6</v>
@@ -10001,10 +10071,10 @@
         <v>129</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M18" s="12"/>
       <c r="N18" s="12"/>
@@ -10013,17 +10083,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>22</v>
@@ -10041,10 +10111,10 @@
         <v>63</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M19" s="12"/>
       <c r="N19" s="12"/>
@@ -10053,17 +10123,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>5</v>
@@ -10081,10 +10151,10 @@
         <v>129</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M20" s="12"/>
       <c r="N20" s="12"/>
@@ -10093,17 +10163,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>1</v>
@@ -10121,10 +10191,10 @@
         <v>54</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M21" s="12"/>
       <c r="N21" s="12"/>
@@ -10133,17 +10203,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>7</v>
@@ -10159,10 +10229,10 @@
         <v>54</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M22" s="12"/>
       <c r="N22" s="12"/>
@@ -10171,17 +10241,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>10</v>
@@ -10199,10 +10269,10 @@
         <v>54</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M23" s="12"/>
       <c r="N23" s="12"/>
@@ -10211,17 +10281,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>17</v>
@@ -10239,10 +10309,10 @@
         <v>54</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M24" s="12"/>
       <c r="N24" s="12"/>
@@ -10251,17 +10321,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>21</v>
@@ -10276,13 +10346,13 @@
         <v>53</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M25" s="12"/>
       <c r="N25" s="12"/>
@@ -10291,17 +10361,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>23</v>
@@ -10317,10 +10387,10 @@
         <v>54</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M26" s="12"/>
       <c r="N26" s="12"/>
@@ -10329,17 +10399,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>24</v>
@@ -10355,10 +10425,10 @@
         <v>54</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M27" s="12"/>
       <c r="N27" s="12"/>
@@ -10367,19 +10437,19 @@
     </row>
     <row r="28" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>18</v>
@@ -10394,13 +10464,13 @@
         <v>117</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M28" s="12"/>
       <c r="N28" s="12"/>
@@ -10409,17 +10479,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>20</v>
@@ -10437,10 +10507,10 @@
         <v>54</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M29" s="12"/>
       <c r="N29" s="12"/>
@@ -10449,17 +10519,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="15" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>12</v>
@@ -10477,10 +10547,10 @@
         <v>54</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M30" s="12"/>
       <c r="N30" s="12"/>
@@ -10489,10 +10559,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
@@ -10501,14 +10571,16 @@
         <v>15</v>
       </c>
       <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
+      <c r="H31" s="12" t="s">
+        <v>52</v>
+      </c>
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
       <c r="K31" s="12" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M31" s="12"/>
       <c r="N31" s="12"/>
@@ -10551,7 +10623,7 @@
         <v>147</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10559,7 +10631,7 @@
         <v>62</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10567,7 +10639,7 @@
         <v>148</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10575,7 +10647,7 @@
         <v>149</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10583,7 +10655,7 @@
         <v>70</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -10642,7 +10714,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10656,7 +10728,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10664,7 +10736,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10672,7 +10744,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10680,7 +10752,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10694,7 +10766,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10702,7 +10774,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10710,7 +10782,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10718,14 +10790,16 @@
         <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="12"/>
+      <c r="B13" s="12" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -10776,25 +10850,25 @@
         <v>46</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>5</v>
@@ -10806,7 +10880,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12" t="s">
@@ -10822,17 +10896,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>9</v>
@@ -10844,7 +10918,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12" t="s">
@@ -10860,14 +10934,14 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>134</v>
@@ -10882,7 +10956,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12" t="s">
@@ -10898,17 +10972,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>10</v>
@@ -10926,7 +11000,7 @@
         <v>54</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="12" t="s">
@@ -10942,14 +11016,14 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>50</v>
@@ -10964,7 +11038,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="12" t="s">
@@ -10980,17 +11054,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>23</v>
@@ -10999,10 +11073,14 @@
       <c r="H22" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
+      <c r="I22" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="K22" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="12" t="s">
@@ -11018,17 +11096,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>14</v>
@@ -11040,7 +11118,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="12" t="s">
@@ -11056,17 +11134,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>7</v>
@@ -11084,7 +11162,7 @@
         <v>54</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="12" t="s">
@@ -11096,17 +11174,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>4</v>
@@ -11118,7 +11196,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="12" t="s">
@@ -11130,17 +11208,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="12" t="s">
@@ -11156,7 +11234,7 @@
         <v>129</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="12" t="s">
@@ -11168,17 +11246,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>1</v>
@@ -11192,7 +11270,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12" t="s">
@@ -11204,17 +11282,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>20</v>
@@ -11228,7 +11306,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
       <c r="K28" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="12" t="s">
@@ -11240,17 +11318,17 @@
     </row>
     <row r="29" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>16</v>
@@ -11262,7 +11340,7 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="12" t="s">
@@ -11274,17 +11352,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>19</v>
@@ -11296,7 +11374,7 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L30" s="12"/>
       <c r="M30" s="12" t="s">
@@ -11308,17 +11386,17 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>23</v>
@@ -11330,7 +11408,7 @@
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
       <c r="K31" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L31" s="12"/>
       <c r="M31" s="12" t="s">
@@ -11342,17 +11420,17 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C32" s="18"/>
       <c r="D32" s="20" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F32" s="18" t="n">
         <v>24</v>
@@ -11364,7 +11442,7 @@
       <c r="I32" s="18"/>
       <c r="J32" s="18"/>
       <c r="K32" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L32" s="18"/>
       <c r="M32" s="12" t="s">
@@ -11376,16 +11454,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>17</v>
@@ -11394,7 +11472,7 @@
         <v>52</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M33" s="12" t="s">
         <v>57</v>
@@ -11402,16 +11480,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>8</v>
@@ -11420,7 +11498,7 @@
         <v>52</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M34" s="12" t="s">
         <v>57</v>
@@ -11428,25 +11506,34 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="G35" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="H35" s="1" t="s">
         <v>57</v>
       </c>
+      <c r="I35" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="K35" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M35" s="12" t="s">
         <v>57</v>
@@ -11470,7 +11557,7 @@
         <v>147</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11484,7 +11571,7 @@
         <v>148</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11498,7 +11585,7 @@
         <v>70</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -11561,7 +11648,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11575,7 +11662,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11583,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11591,7 +11678,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11599,7 +11686,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11607,7 +11694,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11615,7 +11702,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11623,7 +11710,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11631,7 +11718,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11639,7 +11726,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11647,7 +11734,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11701,17 +11788,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
@@ -11729,10 +11816,10 @@
         <v>54</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -11743,17 +11830,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>14</v>
@@ -11768,13 +11855,13 @@
         <v>53</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -11785,17 +11872,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>4</v>
@@ -11813,10 +11900,10 @@
         <v>129</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -11827,17 +11914,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>6</v>
@@ -11855,10 +11942,10 @@
         <v>54</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -11869,17 +11956,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>17</v>
@@ -11897,10 +11984,10 @@
         <v>54</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -11911,17 +11998,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>5</v>
@@ -11936,13 +12023,13 @@
         <v>117</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -11953,17 +12040,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>9</v>
@@ -11981,10 +12068,10 @@
         <v>54</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -11995,19 +12082,19 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>2</v>
@@ -12022,13 +12109,13 @@
         <v>53</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -12039,17 +12126,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>20</v>
@@ -12067,10 +12154,10 @@
         <v>54</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -12081,17 +12168,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>7</v>
@@ -12109,10 +12196,10 @@
         <v>129</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -12123,17 +12210,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>3</v>
@@ -12151,10 +12238,10 @@
         <v>129</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -12165,17 +12252,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>1</v>
@@ -12190,13 +12277,13 @@
         <v>53</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -12207,17 +12294,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>10</v>
@@ -12235,10 +12322,10 @@
         <v>54</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -12249,17 +12336,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>19</v>
@@ -12277,10 +12364,10 @@
         <v>54</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -12291,19 +12378,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>12</v>
@@ -12321,10 +12408,10 @@
         <v>54</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M31" s="12" t="s">
         <v>57</v>
@@ -12335,16 +12422,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>13</v>
@@ -12362,10 +12449,10 @@
         <v>54</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M32" s="12" t="s">
         <v>57</v>
@@ -12373,16 +12460,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>8</v>
@@ -12400,10 +12487,10 @@
         <v>54</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12442,7 +12529,7 @@
         <v>147</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12450,7 +12537,7 @@
         <v>62</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12458,7 +12545,7 @@
         <v>148</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12466,7 +12553,7 @@
         <v>149</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12474,7 +12561,7 @@
         <v>70</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -12533,7 +12620,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12547,7 +12634,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12555,7 +12642,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12563,7 +12650,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12577,7 +12664,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12585,7 +12672,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12593,7 +12680,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12601,7 +12688,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12667,17 +12754,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
@@ -12695,10 +12782,10 @@
         <v>129</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -12709,17 +12796,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>10</v>
@@ -12731,16 +12818,16 @@
         <v>52</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="J18" s="12" t="s">
         <v>129</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -12751,17 +12838,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>18</v>
@@ -12779,10 +12866,10 @@
         <v>54</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -12793,17 +12880,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>5</v>
@@ -12821,10 +12908,10 @@
         <v>129</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -12835,17 +12922,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>9</v>
@@ -12863,10 +12950,10 @@
         <v>54</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -12877,17 +12964,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>7</v>
@@ -12905,10 +12992,10 @@
         <v>54</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -12919,17 +13006,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>6</v>
@@ -12947,10 +13034,10 @@
         <v>54</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -12961,17 +13048,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>20</v>
@@ -12989,10 +13076,10 @@
         <v>54</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -13003,17 +13090,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>14</v>
@@ -13031,10 +13118,10 @@
         <v>54</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -13045,17 +13132,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>1</v>
@@ -13073,10 +13160,10 @@
         <v>54</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -13087,17 +13174,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>3</v>
@@ -13115,10 +13202,10 @@
         <v>54</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -13129,17 +13216,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>2</v>
@@ -13157,10 +13244,10 @@
         <v>54</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -13171,17 +13258,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>13</v>
@@ -13199,10 +13286,10 @@
         <v>54</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -13213,19 +13300,19 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>8</v>
@@ -13240,13 +13327,13 @@
         <v>53</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -13257,17 +13344,17 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>12</v>
@@ -13285,10 +13372,10 @@
         <v>54</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M31" s="12" t="s">
         <v>57</v>
@@ -13299,17 +13386,17 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C32" s="0"/>
       <c r="D32" s="0" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F32" s="0" t="n">
         <v>22</v>
@@ -13321,16 +13408,16 @@
         <v>52</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="J32" s="12" t="s">
         <v>54</v>
       </c>
       <c r="K32" s="0" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M32" s="12" t="s">
         <v>57</v>
@@ -13341,17 +13428,17 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C33" s="0"/>
       <c r="D33" s="0" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F33" s="0" t="n">
         <v>19</v>
@@ -13369,10 +13456,10 @@
         <v>54</v>
       </c>
       <c r="K33" s="0" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M33" s="12" t="s">
         <v>57</v>
@@ -13417,7 +13504,7 @@
         <v>147</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13425,7 +13512,7 @@
         <v>62</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13433,7 +13520,7 @@
         <v>148</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13441,7 +13528,7 @@
         <v>149</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13449,7 +13536,7 @@
         <v>70</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
   </sheetData>
@@ -13508,7 +13595,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13522,7 +13609,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13530,7 +13617,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13538,7 +13625,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13546,7 +13633,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13554,7 +13641,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13562,7 +13649,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13570,7 +13657,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13578,7 +13665,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13642,27 +13729,27 @@
         <v>46</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>10</v>
@@ -13676,10 +13763,10 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -13694,19 +13781,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>14</v>
@@ -13718,10 +13805,10 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -13736,17 +13823,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>8</v>
@@ -13762,10 +13849,10 @@
         <v>54</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -13780,17 +13867,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>7</v>
@@ -13806,10 +13893,10 @@
         <v>54</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -13824,17 +13911,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>19</v>
@@ -13850,10 +13937,10 @@
         <v>54</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -13868,19 +13955,19 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>18</v>
@@ -13893,13 +13980,13 @@
       </c>
       <c r="I22" s="12"/>
       <c r="J22" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -13914,17 +14001,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
         <v>115</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>17</v>
@@ -13938,10 +14025,10 @@
         <v>54</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -13956,17 +14043,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>4</v>
@@ -13982,10 +14069,10 @@
         <v>54</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -13996,19 +14083,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>12</v>
@@ -14021,13 +14108,13 @@
       </c>
       <c r="I25" s="12"/>
       <c r="J25" s="12" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -14038,17 +14125,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>20</v>
@@ -14064,10 +14151,10 @@
         <v>54</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -14078,17 +14165,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
         <v>127</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>5</v>
@@ -14100,10 +14187,10 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -14114,17 +14201,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>9</v>
@@ -14136,10 +14223,10 @@
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
       <c r="K28" s="12" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -14150,17 +14237,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>15</v>
@@ -14172,10 +14259,10 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="12" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -14186,17 +14273,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>22</v>
@@ -14208,10 +14295,10 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="12" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -14359,7 +14446,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14373,7 +14460,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14381,7 +14468,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14401,7 +14488,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14421,7 +14508,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14487,19 +14574,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
@@ -14514,13 +14601,13 @@
         <v>53</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -14531,17 +14618,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>18</v>
@@ -14559,10 +14646,10 @@
         <v>54</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -14573,19 +14660,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>7</v>
@@ -14600,13 +14687,13 @@
         <v>53</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -14617,17 +14704,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>10</v>
@@ -14645,10 +14732,10 @@
         <v>54</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -14659,19 +14746,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>13</v>
@@ -14686,13 +14773,13 @@
         <v>117</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -14703,17 +14790,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>23</v>
@@ -14731,10 +14818,10 @@
         <v>54</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -14745,17 +14832,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>5</v>
@@ -14773,10 +14860,10 @@
         <v>129</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -14787,17 +14874,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>8</v>
@@ -14812,13 +14899,13 @@
         <v>117</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -14829,17 +14916,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>17</v>
@@ -14857,10 +14944,10 @@
         <v>54</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -14871,17 +14958,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="11" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>20</v>
@@ -14899,10 +14986,10 @@
         <v>54</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -14913,17 +15000,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="11" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>9</v>
@@ -14941,10 +15028,10 @@
         <v>129</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -14955,17 +15042,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="11" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>1</v>
@@ -14983,10 +15070,10 @@
         <v>54</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -14997,16 +15084,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>2</v>
@@ -15024,10 +15111,10 @@
         <v>54</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -15035,16 +15122,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>12</v>
@@ -15059,13 +15146,13 @@
         <v>53</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -15073,13 +15160,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>15</v>
@@ -15094,13 +15181,13 @@
         <v>53</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M31" s="12" t="s">
         <v>57</v>
@@ -15142,7 +15229,7 @@
         <v>147</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15150,7 +15237,7 @@
         <v>62</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15158,7 +15245,7 @@
         <v>148</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15166,7 +15253,7 @@
         <v>149</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15174,7 +15261,7 @@
         <v>70</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
   </sheetData>

--- a/D1_Fiches_Clubs_Joueurs_26_27.xlsx
+++ b/D1_Fiches_Clubs_Joueurs_26_27.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Mode emploi" sheetId="1" state="visible" r:id="rId3"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2462" uniqueCount="1117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="1128">
   <si>
     <t xml:space="preserve">FICHES CLUBS · D1 FUTSAL 2026-2027</t>
   </si>
@@ -1375,12 +1375,6 @@
     <t xml:space="preserve">https://www.facebook.com/futsalgargesdjibson/?locale=fr_FR</t>
   </si>
   <si>
-    <t xml:space="preserve">buts (info)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passes (info)</t>
-  </si>
-  <si>
     <t xml:space="preserve">halim-hadji-ali</t>
   </si>
   <si>
@@ -1394,6 +1388,9 @@
   </si>
   <si>
     <t xml:space="preserve">halim-hadji-ali.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instagram GARGES FUTSAL</t>
   </si>
   <si>
     <t xml:space="preserve">othmane-chanai</t>
@@ -2130,6 +2127,9 @@
     <t xml:space="preserve">Laval</t>
   </si>
   <si>
+    <t xml:space="preserve">Espace Mayenne </t>
+  </si>
+  <si>
     <t xml:space="preserve">Manolo Moya</t>
   </si>
   <si>
@@ -2142,6 +2142,9 @@
     <t xml:space="preserve">3.png</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.laval-futsal.com/</t>
+  </si>
+  <si>
     <t xml:space="preserve">bilal-bakkali</t>
   </si>
   <si>
@@ -2424,6 +2427,15 @@
     <t xml:space="preserve">6.png</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.instagram.com/montpellierfutsal/?hl=fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">buts (info)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passes (info)</t>
+  </si>
+  <si>
     <t xml:space="preserve">david-mesquita-rodrigues</t>
   </si>
   <si>
@@ -2646,10 +2658,22 @@
     <t xml:space="preserve">NANTES</t>
   </si>
   <si>
+    <t xml:space="preserve">Nantes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salle Mangin Beaulieu</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fabrice Gacougnolle </t>
   </si>
   <si>
+    <t xml:space="preserve">Bleu</t>
+  </si>
+  <si>
     <t xml:space="preserve">9.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://nantesmetropolefutsal.fr/</t>
   </si>
   <si>
     <t xml:space="preserve">francisco-valdelvira-jimenez</t>
@@ -2982,6 +3006,9 @@
     <t xml:space="preserve">Lucas-nahuel-paroldo-ferreri.png</t>
   </si>
   <si>
+    <t xml:space="preserve">Instagram NICE FUTSAL</t>
+  </si>
+  <si>
     <t xml:space="preserve">alexandre-teixeira</t>
   </si>
   <si>
@@ -3465,6 +3492,9 @@
     <t xml:space="preserve">Alexis-dubois.png</t>
   </si>
   <si>
+    <t xml:space="preserve">Instagram TOULON FUTSAL</t>
+  </si>
+  <si>
     <t xml:space="preserve">jerome-pasquier</t>
   </si>
   <si>
@@ -3700,6 +3730,9 @@
   </si>
   <si>
     <t xml:space="preserve">ayoub-bouita.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instagram UJS TOULOUSE</t>
   </si>
   <si>
     <t xml:space="preserve">mohamed-diaoune</t>
@@ -4595,7 +4628,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4609,7 +4642,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4617,7 +4650,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4625,7 +4658,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4633,7 +4666,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4641,7 +4674,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4657,7 +4690,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4665,7 +4698,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4673,7 +4706,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4681,7 +4714,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4726,28 +4759,26 @@
       <c r="L16" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="M16" s="13" t="s">
-        <v>45</v>
-      </c>
+      <c r="M16" s="13"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13"/>
       <c r="P16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>9</v>
@@ -4760,32 +4791,32 @@
       </c>
       <c r="I17" s="12"/>
       <c r="J17" s="12" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>796</v>
-      </c>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>804</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="M17" s="12"/>
       <c r="N17" s="12"/>
       <c r="O17" s="14"/>
       <c r="P17" s="14"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>797</v>
+        <v>806</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>798</v>
+        <v>807</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>799</v>
+        <v>808</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>800</v>
+        <v>809</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>14</v>
@@ -4803,31 +4834,31 @@
         <v>54</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>801</v>
-      </c>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>810</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="M18" s="12"/>
       <c r="N18" s="12"/>
       <c r="O18" s="14"/>
       <c r="P18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>803</v>
+        <v>812</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>804</v>
+        <v>813</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>804</v>
+        <v>813</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>805</v>
+        <v>814</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>19</v>
@@ -4842,32 +4873,32 @@
         <v>53</v>
       </c>
       <c r="J19" s="25" t="s">
-        <v>806</v>
+        <v>815</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>807</v>
-      </c>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>816</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="M19" s="12"/>
       <c r="N19" s="12"/>
       <c r="O19" s="14"/>
       <c r="P19" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>808</v>
+        <v>817</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>809</v>
+        <v>818</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>810</v>
+        <v>819</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>811</v>
+        <v>820</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>6</v>
@@ -4883,29 +4914,29 @@
         <v>129</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>812</v>
-      </c>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>821</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="M20" s="12"/>
       <c r="N20" s="12"/>
       <c r="O20" s="14"/>
       <c r="P20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>815</v>
+        <v>824</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>12</v>
@@ -4921,29 +4952,29 @@
         <v>54</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>816</v>
-      </c>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>825</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="M21" s="12"/>
       <c r="N21" s="12"/>
       <c r="O21" s="12"/>
       <c r="P21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>817</v>
+        <v>826</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>818</v>
+        <v>827</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>819</v>
+        <v>828</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>820</v>
+        <v>829</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>20</v>
@@ -4959,29 +4990,29 @@
         <v>54</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>821</v>
-      </c>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>830</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="M22" s="12"/>
       <c r="N22" s="12"/>
       <c r="O22" s="12"/>
       <c r="P22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>822</v>
+        <v>831</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>823</v>
+        <v>832</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>824</v>
+        <v>833</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>825</v>
+        <v>834</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>3</v>
@@ -4997,29 +5028,29 @@
         <v>63</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>826</v>
-      </c>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>835</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="M23" s="12"/>
       <c r="N23" s="12"/>
       <c r="O23" s="12"/>
       <c r="P23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>827</v>
+        <v>836</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>828</v>
+        <v>837</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>829</v>
+        <v>838</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>5</v>
@@ -5037,31 +5068,31 @@
         <v>309</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>830</v>
-      </c>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>839</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="M24" s="12"/>
       <c r="N24" s="12"/>
       <c r="O24" s="12"/>
       <c r="P24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>831</v>
+        <v>840</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>832</v>
+        <v>841</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>833</v>
+        <v>842</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>834</v>
+        <v>843</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>835</v>
+        <v>844</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>18</v>
@@ -5074,32 +5105,32 @@
       </c>
       <c r="I25" s="12"/>
       <c r="J25" s="12" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>836</v>
-      </c>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>845</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="M25" s="12"/>
       <c r="N25" s="12"/>
       <c r="O25" s="12"/>
       <c r="P25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>837</v>
+        <v>846</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>838</v>
+        <v>847</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>839</v>
+        <v>848</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>840</v>
+        <v>849</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>7</v>
@@ -5115,29 +5146,29 @@
         <v>129</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>841</v>
-      </c>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>850</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="M26" s="12"/>
       <c r="N26" s="12"/>
       <c r="O26" s="12"/>
       <c r="P26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>842</v>
+        <v>851</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>844</v>
+        <v>853</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>8</v>
@@ -5153,29 +5184,29 @@
         <v>129</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>845</v>
-      </c>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>854</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="M27" s="12"/>
       <c r="N27" s="12"/>
       <c r="O27" s="12"/>
       <c r="P27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>846</v>
+        <v>855</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>847</v>
+        <v>856</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>848</v>
+        <v>857</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>849</v>
+        <v>858</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>26</v>
@@ -5191,29 +5222,29 @@
         <v>129</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>850</v>
-      </c>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>859</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="M28" s="12"/>
       <c r="N28" s="12"/>
       <c r="O28" s="12"/>
       <c r="P28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>852</v>
+        <v>861</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>824</v>
+        <v>833</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>853</v>
+        <v>862</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>17</v>
@@ -5229,29 +5260,29 @@
         <v>54</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>854</v>
-      </c>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>863</v>
+      </c>
+      <c r="L29" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="M29" s="12"/>
       <c r="N29" s="12"/>
       <c r="O29" s="12"/>
       <c r="P29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>855</v>
+        <v>864</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>856</v>
+        <v>865</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>857</v>
+        <v>866</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>858</v>
+        <v>867</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>26</v>
@@ -5267,29 +5298,29 @@
         <v>54</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>859</v>
-      </c>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>868</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="M30" s="12"/>
       <c r="N30" s="12"/>
       <c r="O30" s="12"/>
       <c r="P30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>860</v>
+        <v>869</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>861</v>
+        <v>870</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12" t="s">
-        <v>862</v>
+        <v>871</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>863</v>
+        <v>872</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>10</v>
@@ -5305,9 +5336,11 @@
         <v>63</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>864</v>
-      </c>
-      <c r="L31" s="12"/>
+        <v>873</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>805</v>
+      </c>
       <c r="M31" s="12"/>
       <c r="N31" s="12"/>
       <c r="O31" s="12"/>
@@ -5434,7 +5467,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>865</v>
+        <v>874</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5448,7 +5481,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>866</v>
+        <v>875</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5456,7 +5489,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5464,7 +5497,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>868</v>
+        <v>877</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5472,7 +5505,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>869</v>
+        <v>878</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5480,7 +5513,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>870</v>
+        <v>879</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5488,7 +5521,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>871</v>
+        <v>880</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5504,7 +5537,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>872</v>
+        <v>881</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5512,7 +5545,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>873</v>
+        <v>882</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5520,7 +5553,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>873</v>
+        <v>882</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5574,17 +5607,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>874</v>
+        <v>883</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>875</v>
+        <v>884</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>876</v>
+        <v>885</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
@@ -5599,13 +5632,13 @@
         <v>53</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>877</v>
+        <v>886</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>878</v>
+        <v>887</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -5616,17 +5649,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>880</v>
+        <v>889</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>881</v>
+        <v>890</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>882</v>
+        <v>891</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>883</v>
+        <v>892</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>8</v>
@@ -5644,10 +5677,10 @@
         <v>54</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>884</v>
+        <v>893</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -5658,17 +5691,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>885</v>
+        <v>894</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>886</v>
+        <v>895</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>887</v>
+        <v>896</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>10</v>
@@ -5686,10 +5719,10 @@
         <v>129</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -5700,17 +5733,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>891</v>
+        <v>900</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>892</v>
+        <v>901</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>893</v>
+        <v>902</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>5</v>
@@ -5728,10 +5761,10 @@
         <v>54</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>894</v>
+        <v>903</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -5742,17 +5775,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>895</v>
+        <v>904</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>896</v>
+        <v>905</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>897</v>
+        <v>906</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>898</v>
+        <v>907</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>2</v>
@@ -5770,10 +5803,10 @@
         <v>129</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>899</v>
+        <v>908</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -5784,17 +5817,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>900</v>
+        <v>909</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>901</v>
+        <v>910</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>902</v>
+        <v>911</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>903</v>
+        <v>912</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>15</v>
@@ -5809,13 +5842,13 @@
         <v>53</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>877</v>
+        <v>886</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>904</v>
+        <v>913</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -5826,19 +5859,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>905</v>
+        <v>914</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>906</v>
+        <v>915</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>907</v>
+        <v>916</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>907</v>
+        <v>916</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>908</v>
+        <v>917</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>19</v>
@@ -5856,10 +5889,10 @@
         <v>309</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>909</v>
+        <v>918</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -5870,17 +5903,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="15" t="s">
-        <v>912</v>
+        <v>921</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>913</v>
+        <v>922</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>1</v>
@@ -5898,10 +5931,10 @@
         <v>54</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>914</v>
+        <v>923</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -5912,17 +5945,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>915</v>
+        <v>924</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="15" t="s">
-        <v>917</v>
+        <v>926</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>918</v>
+        <v>927</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>20</v>
@@ -5940,10 +5973,10 @@
         <v>54</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>919</v>
+        <v>928</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -5954,17 +5987,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>920</v>
+        <v>929</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>921</v>
+        <v>930</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="15" t="s">
-        <v>922</v>
+        <v>931</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>25</v>
@@ -5982,10 +6015,10 @@
         <v>54</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>924</v>
+        <v>933</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -5996,19 +6029,19 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>925</v>
+        <v>934</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>926</v>
+        <v>935</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>927</v>
+        <v>936</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>928</v>
+        <v>937</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>927</v>
+        <v>936</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>3</v>
@@ -6023,13 +6056,13 @@
         <v>53</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>877</v>
+        <v>886</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>929</v>
+        <v>938</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -6040,17 +6073,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>931</v>
+        <v>940</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="15" t="s">
-        <v>932</v>
+        <v>941</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>933</v>
+        <v>942</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>17</v>
@@ -6068,10 +6101,10 @@
         <v>54</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>934</v>
+        <v>943</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -6082,17 +6115,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>935</v>
+        <v>944</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>936</v>
+        <v>945</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>937</v>
+        <v>946</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>938</v>
+        <v>947</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>26</v>
@@ -6110,10 +6143,10 @@
         <v>54</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>939</v>
+        <v>948</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -6124,17 +6157,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>940</v>
+        <v>949</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>941</v>
+        <v>950</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>943</v>
+        <v>952</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>7</v>
@@ -6150,10 +6183,10 @@
       </c>
       <c r="J30" s="12"/>
       <c r="K30" s="12" t="s">
-        <v>944</v>
+        <v>953</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>879</v>
+        <v>888</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -6216,7 +6249,7 @@
         <v>147</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6224,7 +6257,7 @@
         <v>62</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>880</v>
+        <v>889</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6232,7 +6265,7 @@
         <v>148</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>885</v>
+        <v>894</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6240,7 +6273,7 @@
         <v>149</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>905</v>
+        <v>914</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6248,7 +6281,7 @@
         <v>70</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
     </row>
   </sheetData>
@@ -6307,7 +6340,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>945</v>
+        <v>954</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6321,7 +6354,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>946</v>
+        <v>955</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6329,7 +6362,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>947</v>
+        <v>956</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6337,7 +6370,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>948</v>
+        <v>957</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6351,7 +6384,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>949</v>
+        <v>958</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6359,7 +6392,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>950</v>
+        <v>959</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6375,7 +6408,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>951</v>
+        <v>960</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6383,7 +6416,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>952</v>
+        <v>961</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6391,7 +6424,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>952</v>
+        <v>961</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6443,22 +6476,22 @@
         <v>46</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>333</v>
+        <v>632</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>334</v>
+        <v>633</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>953</v>
+        <v>962</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>954</v>
+        <v>963</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>955</v>
+        <v>964</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>272</v>
@@ -6474,12 +6507,14 @@
         <v>53</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="L17" s="12"/>
+        <v>966</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>967</v>
+      </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
       </c>
@@ -6493,17 +6528,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>961</v>
+        <v>971</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>6</v>
@@ -6516,12 +6551,14 @@
         <v>117</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>962</v>
-      </c>
-      <c r="L18" s="12"/>
+        <v>972</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>967</v>
+      </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
       </c>
@@ -6535,19 +6572,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>963</v>
+        <v>973</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>964</v>
+        <v>974</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>965</v>
+        <v>975</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>966</v>
+        <v>976</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>967</v>
+        <v>977</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>17</v>
@@ -6561,9 +6598,11 @@
       </c>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>968</v>
-      </c>
-      <c r="L19" s="12"/>
+        <v>978</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>967</v>
+      </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
       </c>
@@ -6577,17 +6616,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>969</v>
+        <v>979</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>971</v>
+        <v>981</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>972</v>
+        <v>982</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>7</v>
@@ -6600,12 +6639,14 @@
         <v>53</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>973</v>
-      </c>
-      <c r="L20" s="12"/>
+        <v>983</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>967</v>
+      </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
       </c>
@@ -6619,17 +6660,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>974</v>
+        <v>984</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>975</v>
+        <v>985</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>976</v>
+        <v>986</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>977</v>
+        <v>987</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>10</v>
@@ -6643,9 +6684,11 @@
       </c>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>978</v>
-      </c>
-      <c r="L21" s="12"/>
+        <v>988</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>967</v>
+      </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
       </c>
@@ -6659,17 +6702,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>979</v>
+        <v>989</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>981</v>
+        <v>991</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>982</v>
+        <v>992</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>19</v>
@@ -6682,12 +6725,14 @@
         <v>53</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>983</v>
-      </c>
-      <c r="L22" s="12"/>
+        <v>993</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>967</v>
+      </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
       </c>
@@ -6701,17 +6746,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>984</v>
+        <v>994</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>985</v>
+        <v>995</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>986</v>
+        <v>996</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>987</v>
+        <v>997</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>20</v>
@@ -6727,9 +6772,11 @@
       </c>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>988</v>
-      </c>
-      <c r="L23" s="12"/>
+        <v>998</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>967</v>
+      </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
       </c>
@@ -6743,17 +6790,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>989</v>
+        <v>999</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>991</v>
+        <v>1001</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>992</v>
+        <v>1002</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>5</v>
@@ -6766,12 +6813,14 @@
       </c>
       <c r="I24" s="12"/>
       <c r="J24" s="12" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>993</v>
-      </c>
-      <c r="L24" s="12"/>
+        <v>1003</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>967</v>
+      </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
       </c>
@@ -6781,17 +6830,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>994</v>
+        <v>1004</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>996</v>
+        <v>1006</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>997</v>
+        <v>1007</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>11</v>
@@ -6803,9 +6852,11 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="12" t="s">
-        <v>998</v>
-      </c>
-      <c r="L25" s="12"/>
+        <v>1008</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>967</v>
+      </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
       </c>
@@ -6815,17 +6866,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>999</v>
+        <v>1009</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>1001</v>
+        <v>1011</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>1002</v>
+        <v>1012</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>12</v>
@@ -6838,12 +6889,14 @@
       </c>
       <c r="I26" s="12"/>
       <c r="J26" s="12" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>1003</v>
-      </c>
-      <c r="L26" s="12"/>
+        <v>1013</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>967</v>
+      </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
       </c>
@@ -6853,17 +6906,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>1004</v>
+        <v>1014</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>1005</v>
+        <v>1015</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>1006</v>
+        <v>1016</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>1007</v>
+        <v>1017</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>22</v>
@@ -6875,9 +6928,11 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>1008</v>
-      </c>
-      <c r="L27" s="12"/>
+        <v>1018</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>967</v>
+      </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
       </c>
@@ -6887,17 +6942,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>1009</v>
+        <v>1019</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>1011</v>
+        <v>1021</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>1012</v>
+        <v>1022</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>21</v>
@@ -6909,9 +6964,11 @@
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
       <c r="K28" s="12" t="s">
-        <v>1013</v>
-      </c>
-      <c r="L28" s="12"/>
+        <v>1023</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>967</v>
+      </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
       </c>
@@ -6921,17 +6978,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>1014</v>
+        <v>1024</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>1016</v>
+        <v>1026</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>9</v>
@@ -6943,9 +7000,11 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="12" t="s">
-        <v>1018</v>
-      </c>
-      <c r="L29" s="12"/>
+        <v>1028</v>
+      </c>
+      <c r="L29" s="12" t="s">
+        <v>967</v>
+      </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
       </c>
@@ -6955,17 +7014,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>1019</v>
+        <v>1029</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>1021</v>
+        <v>1031</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>1022</v>
+        <v>1032</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>14</v>
@@ -6977,9 +7036,11 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="12" t="s">
-        <v>1023</v>
-      </c>
-      <c r="L30" s="12"/>
+        <v>1033</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>967</v>
+      </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
       </c>
@@ -7036,7 +7097,7 @@
         <v>147</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>984</v>
+        <v>994</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7044,7 +7105,7 @@
         <v>62</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>974</v>
+        <v>984</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7052,7 +7113,7 @@
         <v>148</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>963</v>
+        <v>973</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7060,7 +7121,7 @@
         <v>149</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7068,7 +7129,7 @@
         <v>70</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>953</v>
+        <v>962</v>
       </c>
     </row>
   </sheetData>
@@ -7127,7 +7188,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>1024</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7141,7 +7202,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1025</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7149,7 +7210,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1026</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7157,7 +7218,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1026</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7165,7 +7226,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7173,7 +7234,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>1028</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7181,7 +7242,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1029</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7189,7 +7250,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>1030</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7197,7 +7258,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>1031</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7205,7 +7266,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>1032</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7213,7 +7274,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>1032</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7264,17 +7325,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>1033</v>
+        <v>1043</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>1035</v>
+        <v>1045</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>6</v>
@@ -7289,29 +7350,31 @@
         <v>117</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>1036</v>
-      </c>
-      <c r="L17" s="12"/>
+        <v>1046</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>1047</v>
+      </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1037</v>
+        <v>1048</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>1038</v>
+        <v>1049</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>1039</v>
+        <v>1050</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>1040</v>
+        <v>1051</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>19</v>
@@ -7326,29 +7389,31 @@
         <v>53</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>1041</v>
-      </c>
-      <c r="L18" s="12"/>
+        <v>1052</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>1047</v>
+      </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>1042</v>
+        <v>1053</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>1043</v>
+        <v>1054</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
         <v>183</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>1044</v>
+        <v>1055</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>8</v>
@@ -7366,26 +7431,28 @@
         <v>129</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>1045</v>
-      </c>
-      <c r="L19" s="12"/>
+        <v>1056</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>1047</v>
+      </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1046</v>
+        <v>1057</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>1047</v>
+        <v>1058</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>1048</v>
+        <v>1059</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>1049</v>
+        <v>1060</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>11</v>
@@ -7400,29 +7467,31 @@
         <v>53</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>1050</v>
-      </c>
-      <c r="L20" s="12"/>
+        <v>1061</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>1047</v>
+      </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>1051</v>
+        <v>1062</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>1052</v>
+        <v>1063</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>1053</v>
+        <v>1064</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>1054</v>
+        <v>1065</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>26</v>
@@ -7434,26 +7503,28 @@
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12" t="s">
-        <v>1055</v>
-      </c>
-      <c r="L21" s="12"/>
+        <v>1066</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>1047</v>
+      </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>1056</v>
+        <v>1067</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>1057</v>
+        <v>1068</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>1058</v>
+        <v>1069</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>1059</v>
+        <v>1070</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>10</v>
@@ -7468,29 +7539,31 @@
         <v>53</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>1060</v>
-      </c>
-      <c r="L22" s="12"/>
+        <v>1071</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>1047</v>
+      </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>1061</v>
+        <v>1072</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>1062</v>
+        <v>1073</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>1063</v>
+        <v>1074</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>4</v>
@@ -7508,26 +7581,28 @@
         <v>129</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>1065</v>
-      </c>
-      <c r="L23" s="12"/>
+        <v>1076</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>1047</v>
+      </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>1066</v>
+        <v>1077</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>1068</v>
+        <v>1079</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>1069</v>
+        <v>1080</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>9</v>
@@ -7545,28 +7620,30 @@
         <v>129</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>1070</v>
-      </c>
-      <c r="L24" s="12"/>
+        <v>1081</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>1047</v>
+      </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>1072</v>
+        <v>1083</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>1073</v>
+        <v>1084</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>1074</v>
+        <v>1085</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>1075</v>
+        <v>1086</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>25</v>
@@ -7581,29 +7658,31 @@
         <v>53</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>1076</v>
+        <v>1087</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>1077</v>
-      </c>
-      <c r="L25" s="12"/>
+        <v>1088</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>1047</v>
+      </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>1078</v>
+        <v>1089</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>1079</v>
+        <v>1090</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>819</v>
+        <v>828</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>1059</v>
+        <v>1070</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>7</v>
@@ -7618,29 +7697,31 @@
         <v>53</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>1080</v>
-      </c>
-      <c r="L26" s="12"/>
+        <v>1091</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>1047</v>
+      </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>1081</v>
+        <v>1092</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>1082</v>
+        <v>1093</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>1083</v>
+        <v>1094</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>1084</v>
+        <v>1095</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>15</v>
@@ -7652,26 +7733,28 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>1085</v>
-      </c>
-      <c r="L27" s="12"/>
+        <v>1096</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>1047</v>
+      </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>1086</v>
+        <v>1097</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>1087</v>
+        <v>1098</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>1088</v>
+        <v>1099</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>1089</v>
+        <v>1100</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>18</v>
@@ -7685,26 +7768,28 @@
         <v>129</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>1090</v>
-      </c>
-      <c r="L28" s="12"/>
+        <v>1101</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>1047</v>
+      </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>1091</v>
+        <v>1102</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>1092</v>
+        <v>1103</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>1039</v>
+        <v>1050</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>1093</v>
+        <v>1104</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>12</v>
@@ -7718,26 +7803,28 @@
         <v>129</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>1094</v>
-      </c>
-      <c r="L29" s="12"/>
+        <v>1105</v>
+      </c>
+      <c r="L29" s="12" t="s">
+        <v>1047</v>
+      </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>1095</v>
+        <v>1106</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>1096</v>
+        <v>1107</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>1097</v>
+        <v>1108</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>1098</v>
+        <v>1109</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>1</v>
@@ -7751,26 +7838,28 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="12" t="s">
-        <v>1099</v>
-      </c>
-      <c r="L30" s="12"/>
+        <v>1110</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>1047</v>
+      </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>1100</v>
+        <v>1111</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>1101</v>
+        <v>1112</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12" t="s">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>1103</v>
+        <v>1114</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>3</v>
@@ -7782,26 +7871,28 @@
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
       <c r="K31" s="12" t="s">
-        <v>1104</v>
-      </c>
-      <c r="L31" s="12"/>
+        <v>1115</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>1047</v>
+      </c>
       <c r="M31" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>1105</v>
+        <v>1116</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>1106</v>
+        <v>1117</v>
       </c>
       <c r="C32" s="12"/>
       <c r="D32" s="12" t="s">
         <v>183</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>1093</v>
+        <v>1104</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>21</v>
@@ -7816,29 +7907,31 @@
         <v>53</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>1107</v>
-      </c>
-      <c r="L32" s="18"/>
+        <v>1118</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>1047</v>
+      </c>
       <c r="M32" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>1108</v>
+        <v>1119</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>1109</v>
+        <v>1120</v>
       </c>
       <c r="C33" s="12"/>
       <c r="D33" s="12" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>1110</v>
+        <v>1121</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>20</v>
@@ -7853,7 +7946,10 @@
         <v>129</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>1111</v>
+        <v>1122</v>
+      </c>
+      <c r="L33" s="12" t="s">
+        <v>1047</v>
       </c>
       <c r="M33" s="12" t="s">
         <v>57</v>
@@ -7861,17 +7957,17 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>1112</v>
+        <v>1123</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>1113</v>
+        <v>1124</v>
       </c>
       <c r="C34" s="12"/>
       <c r="D34" s="12" t="s">
-        <v>1114</v>
+        <v>1125</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>1115</v>
+        <v>1126</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>22</v>
@@ -7880,7 +7976,10 @@
         <v>52</v>
       </c>
       <c r="K34" s="12" t="s">
-        <v>1116</v>
+        <v>1127</v>
+      </c>
+      <c r="L34" s="12" t="s">
+        <v>1047</v>
       </c>
       <c r="M34" s="12" t="s">
         <v>57</v>
@@ -10843,32 +10942,24 @@
       <c r="L16" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="M16" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="N16" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="O16" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="P16" s="13" t="s">
-        <v>334</v>
-      </c>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>5</v>
@@ -10880,33 +10971,29 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M17" s="12"/>
       <c r="N17" s="12"/>
-      <c r="O17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="14" t="n">
-        <v>3</v>
-      </c>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>340</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>341</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="E18" s="12" t="s">
         <v>342</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>343</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>9</v>
@@ -10918,30 +11005,26 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M18" s="12"/>
       <c r="N18" s="12"/>
-      <c r="O18" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="P18" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>345</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>346</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>134</v>
@@ -10956,33 +11039,29 @@
       <c r="I19" s="12"/>
       <c r="J19" s="12"/>
       <c r="K19" s="12" t="s">
-        <v>348</v>
-      </c>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M19" s="12"/>
       <c r="N19" s="12"/>
-      <c r="O19" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>349</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>350</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="E20" s="12" t="s">
         <v>351</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>352</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>10</v>
@@ -11000,30 +11079,26 @@
         <v>54</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M20" s="12"/>
       <c r="N20" s="12"/>
-      <c r="O20" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" s="14" t="n">
-        <v>1</v>
-      </c>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>354</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>355</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>50</v>
@@ -11035,36 +11110,36 @@
       <c r="H21" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
+      <c r="I21" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>208</v>
+      </c>
       <c r="K21" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M21" s="12"/>
       <c r="N21" s="12"/>
-      <c r="O21" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>358</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>359</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="E22" s="12" t="s">
         <v>360</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>361</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>23</v>
@@ -11080,33 +11155,29 @@
         <v>54</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M22" s="12"/>
       <c r="N22" s="12"/>
-      <c r="O22" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>363</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>364</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="E23" s="12" t="s">
         <v>365</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>366</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>14</v>
@@ -11118,33 +11189,29 @@
       <c r="I23" s="12"/>
       <c r="J23" s="12"/>
       <c r="K23" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M23" s="12"/>
       <c r="N23" s="12"/>
-      <c r="O23" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P23" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="O23" s="14"/>
+      <c r="P23" s="14"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>368</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>369</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="E24" s="17" t="s">
         <v>370</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>371</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>7</v>
@@ -11162,29 +11229,29 @@
         <v>54</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M24" s="12"/>
       <c r="N24" s="12"/>
       <c r="O24" s="12"/>
       <c r="P24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>373</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>374</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="E25" s="17" t="s">
         <v>375</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>376</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>4</v>
@@ -11196,29 +11263,29 @@
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
       <c r="K25" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M25" s="12"/>
       <c r="N25" s="12"/>
       <c r="O25" s="12"/>
       <c r="P25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>378</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>379</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="E26" s="17" t="s">
         <v>380</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>381</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="12" t="s">
@@ -11234,29 +11301,29 @@
         <v>129</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>382</v>
-      </c>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M26" s="12"/>
       <c r="N26" s="12"/>
       <c r="O26" s="12"/>
       <c r="P26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>383</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>384</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="E27" s="17" t="s">
         <v>385</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>386</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>1</v>
@@ -11270,29 +11337,29 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="11" t="s">
-        <v>387</v>
-      </c>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M27" s="12"/>
       <c r="N27" s="12"/>
       <c r="O27" s="12"/>
       <c r="P27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>388</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>389</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="E28" s="17" t="s">
         <v>390</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>391</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>20</v>
@@ -11306,29 +11373,29 @@
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
       <c r="K28" s="11" t="s">
-        <v>392</v>
-      </c>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M28" s="12"/>
       <c r="N28" s="12"/>
       <c r="O28" s="12"/>
       <c r="P28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>393</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>394</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="E29" s="17" t="s">
         <v>395</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>396</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>16</v>
@@ -11340,29 +11407,29 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="11" t="s">
-        <v>397</v>
-      </c>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="L29" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M29" s="12"/>
       <c r="N29" s="12"/>
       <c r="O29" s="12"/>
       <c r="P29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>398</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>399</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="E30" s="17" t="s">
         <v>400</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>401</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>19</v>
@@ -11374,29 +11441,29 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="11" t="s">
-        <v>402</v>
-      </c>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M30" s="12"/>
       <c r="N30" s="12"/>
       <c r="O30" s="12"/>
       <c r="P30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>403</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>404</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="E31" s="17" t="s">
         <v>405</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>406</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>23</v>
@@ -11408,29 +11475,29 @@
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
       <c r="K31" s="11" t="s">
-        <v>407</v>
-      </c>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M31" s="12"/>
       <c r="N31" s="12"/>
       <c r="O31" s="12"/>
       <c r="P31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="B32" s="11" t="s">
         <v>408</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>409</v>
       </c>
       <c r="C32" s="18"/>
       <c r="D32" s="20" t="s">
+        <v>409</v>
+      </c>
+      <c r="E32" s="11" t="s">
         <v>410</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>411</v>
       </c>
       <c r="F32" s="18" t="n">
         <v>24</v>
@@ -11442,28 +11509,28 @@
       <c r="I32" s="18"/>
       <c r="J32" s="18"/>
       <c r="K32" s="11" t="s">
-        <v>412</v>
-      </c>
-      <c r="L32" s="18"/>
-      <c r="M32" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M32" s="12"/>
       <c r="N32" s="18"/>
       <c r="O32" s="18"/>
       <c r="P32" s="18"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="D33" s="11" t="s">
         <v>414</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="E33" s="16" t="s">
         <v>415</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>416</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>17</v>
@@ -11472,24 +11539,25 @@
         <v>52</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>417</v>
-      </c>
-      <c r="M33" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="L33" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M33" s="12"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="B34" s="11" t="s">
         <v>418</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="D34" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="E34" s="16" t="s">
         <v>420</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>421</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>8</v>
@@ -11498,24 +11566,25 @@
         <v>52</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>422</v>
-      </c>
-      <c r="M34" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="L34" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M34" s="12"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="16" t="s">
         <v>425</v>
-      </c>
-      <c r="E35" s="16" t="s">
-        <v>426</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>1</v>
@@ -11533,11 +11602,12 @@
         <v>63</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="M35" s="12" t="s">
-        <v>57</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="L35" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="M35" s="12"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
@@ -11557,7 +11627,7 @@
         <v>147</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11571,7 +11641,7 @@
         <v>148</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11585,7 +11655,7 @@
         <v>70</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -11648,7 +11718,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11662,7 +11732,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11670,7 +11740,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11678,7 +11748,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11686,7 +11756,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11694,7 +11764,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11702,7 +11772,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11710,7 +11780,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11718,7 +11788,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11726,7 +11796,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11734,7 +11804,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11788,17 +11858,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>438</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>439</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="E17" s="12" t="s">
         <v>440</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>441</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
@@ -11816,10 +11886,10 @@
         <v>54</v>
       </c>
       <c r="K17" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="L17" s="12" t="s">
         <v>442</v>
-      </c>
-      <c r="L17" s="12" t="s">
-        <v>443</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -11830,17 +11900,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>444</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>445</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="E18" s="12" t="s">
         <v>446</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>447</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>14</v>
@@ -11855,13 +11925,13 @@
         <v>53</v>
       </c>
       <c r="J18" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="K18" s="12" t="s">
         <v>448</v>
       </c>
-      <c r="K18" s="12" t="s">
-        <v>449</v>
-      </c>
       <c r="L18" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -11872,17 +11942,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>450</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>451</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="E19" s="12" t="s">
         <v>452</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>453</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>4</v>
@@ -11900,10 +11970,10 @@
         <v>129</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -11914,17 +11984,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>455</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>456</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="E20" s="12" t="s">
         <v>457</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>458</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>6</v>
@@ -11942,10 +12012,10 @@
         <v>54</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -11956,17 +12026,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>460</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>461</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>462</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>463</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>17</v>
@@ -11984,10 +12054,10 @@
         <v>54</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -11998,17 +12068,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>465</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>466</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="E22" s="12" t="s">
         <v>467</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>468</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>5</v>
@@ -12023,13 +12093,13 @@
         <v>117</v>
       </c>
       <c r="J22" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="K22" s="12" t="s">
         <v>469</v>
       </c>
-      <c r="K22" s="12" t="s">
-        <v>470</v>
-      </c>
       <c r="L22" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -12040,17 +12110,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>471</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>472</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="E23" s="12" t="s">
         <v>473</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>474</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>9</v>
@@ -12068,10 +12138,10 @@
         <v>54</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -12082,19 +12152,19 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>476</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="C24" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="D24" s="12" t="s">
         <v>478</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="E24" s="12" t="s">
         <v>479</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>480</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>2</v>
@@ -12112,10 +12182,10 @@
         <v>309</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -12126,17 +12196,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>482</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>483</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="E25" s="12" t="s">
         <v>484</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>485</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>20</v>
@@ -12154,10 +12224,10 @@
         <v>54</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -12168,17 +12238,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>487</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>488</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="E26" s="12" t="s">
         <v>489</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>490</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>7</v>
@@ -12196,10 +12266,10 @@
         <v>129</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -12210,17 +12280,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>492</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>493</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="E27" s="12" t="s">
         <v>494</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>495</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>3</v>
@@ -12238,10 +12308,10 @@
         <v>129</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -12252,17 +12322,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
+        <v>496</v>
+      </c>
+      <c r="B28" s="12" t="s">
         <v>497</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>498</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
+        <v>498</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>499</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>500</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>1</v>
@@ -12277,13 +12347,13 @@
         <v>53</v>
       </c>
       <c r="J28" s="12" t="s">
+        <v>500</v>
+      </c>
+      <c r="K28" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="K28" s="12" t="s">
-        <v>502</v>
-      </c>
       <c r="L28" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -12294,17 +12364,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
+        <v>502</v>
+      </c>
+      <c r="B29" s="12" t="s">
         <v>503</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>504</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>10</v>
@@ -12322,10 +12392,10 @@
         <v>54</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -12336,17 +12406,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="B30" s="12" t="s">
         <v>507</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>508</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="E30" s="12" t="s">
         <v>509</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>510</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>19</v>
@@ -12364,10 +12434,10 @@
         <v>54</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -12378,19 +12448,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="B31" s="12" t="s">
         <v>512</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="C31" s="12" t="s">
         <v>513</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="D31" s="12" t="s">
         <v>514</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="E31" s="12" t="s">
         <v>515</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>516</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>12</v>
@@ -12408,10 +12478,10 @@
         <v>54</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M31" s="12" t="s">
         <v>57</v>
@@ -12422,16 +12492,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="D32" s="12" t="s">
         <v>519</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="E32" s="12" t="s">
         <v>520</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>521</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>13</v>
@@ -12449,10 +12519,10 @@
         <v>54</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M32" s="12" t="s">
         <v>57</v>
@@ -12460,16 +12530,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="23" t="s">
         <v>525</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>526</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>8</v>
@@ -12487,10 +12557,10 @@
         <v>54</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12529,7 +12599,7 @@
         <v>147</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12537,7 +12607,7 @@
         <v>62</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12545,7 +12615,7 @@
         <v>148</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12553,7 +12623,7 @@
         <v>149</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12561,7 +12631,7 @@
         <v>70</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -12620,7 +12690,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12634,7 +12704,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12642,7 +12712,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12650,14 +12720,16 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="12"/>
+      <c r="B7" s="12" t="s">
+        <v>531</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
@@ -12695,13 +12767,17 @@
       <c r="A12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="12"/>
+      <c r="B12" s="12" t="s">
+        <v>536</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="12"/>
+      <c r="B13" s="12" t="s">
+        <v>536</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -12754,17 +12830,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
@@ -12782,10 +12858,10 @@
         <v>129</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -12796,17 +12872,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>10</v>
@@ -12818,16 +12894,16 @@
         <v>52</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J18" s="12" t="s">
         <v>129</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -12838,17 +12914,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>18</v>
@@ -12866,10 +12942,10 @@
         <v>54</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -12880,17 +12956,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>5</v>
@@ -12908,10 +12984,10 @@
         <v>129</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -12922,17 +12998,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>9</v>
@@ -12950,10 +13026,10 @@
         <v>54</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -12964,17 +13040,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>7</v>
@@ -12992,10 +13068,10 @@
         <v>54</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -13006,17 +13082,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>6</v>
@@ -13034,10 +13110,10 @@
         <v>54</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -13048,17 +13124,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>20</v>
@@ -13076,10 +13152,10 @@
         <v>54</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -13090,17 +13166,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>14</v>
@@ -13118,10 +13194,10 @@
         <v>54</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -13132,17 +13208,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>1</v>
@@ -13160,10 +13236,10 @@
         <v>54</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -13174,17 +13250,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>3</v>
@@ -13202,10 +13278,10 @@
         <v>54</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -13216,17 +13292,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
         <v>121</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>2</v>
@@ -13244,10 +13320,10 @@
         <v>54</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -13258,17 +13334,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>13</v>
@@ -13286,10 +13362,10 @@
         <v>54</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -13300,19 +13376,19 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>8</v>
@@ -13330,10 +13406,10 @@
         <v>309</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -13344,17 +13420,17 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>12</v>
@@ -13372,10 +13448,10 @@
         <v>54</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M31" s="12" t="s">
         <v>57</v>
@@ -13386,17 +13462,17 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C32" s="0"/>
       <c r="D32" s="0" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F32" s="0" t="n">
         <v>22</v>
@@ -13408,16 +13484,16 @@
         <v>52</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="J32" s="12" t="s">
         <v>54</v>
       </c>
       <c r="K32" s="0" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M32" s="12" t="s">
         <v>57</v>
@@ -13428,17 +13504,17 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C33" s="0"/>
       <c r="D33" s="0" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F33" s="0" t="n">
         <v>19</v>
@@ -13456,10 +13532,10 @@
         <v>54</v>
       </c>
       <c r="K33" s="0" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M33" s="12" t="s">
         <v>57</v>
@@ -13504,7 +13580,7 @@
         <v>147</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13512,7 +13588,7 @@
         <v>62</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13520,7 +13596,7 @@
         <v>148</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13528,7 +13604,7 @@
         <v>149</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13536,7 +13612,7 @@
         <v>70</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -13595,7 +13671,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13609,7 +13685,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13617,7 +13693,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13625,7 +13701,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13633,7 +13709,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13641,7 +13717,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13649,7 +13725,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13665,20 +13741,24 @@
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="12"/>
+      <c r="B12" s="12" t="s">
+        <v>631</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="12"/>
+      <c r="B13" s="12" t="s">
+        <v>631</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -13729,27 +13809,27 @@
         <v>46</v>
       </c>
       <c r="O16" s="13" t="s">
-        <v>333</v>
+        <v>632</v>
       </c>
       <c r="P16" s="13" t="s">
-        <v>334</v>
+        <v>633</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>10</v>
@@ -13763,10 +13843,10 @@
       <c r="I17" s="12"/>
       <c r="J17" s="12"/>
       <c r="K17" s="12" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -13781,19 +13861,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>14</v>
@@ -13805,10 +13885,10 @@
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -13823,17 +13903,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>8</v>
@@ -13844,15 +13924,17 @@
       <c r="H19" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="I19" s="12"/>
+      <c r="I19" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="J19" s="12" t="s">
         <v>54</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -13867,17 +13949,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>7</v>
@@ -13888,15 +13970,17 @@
       <c r="H20" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="I20" s="12"/>
+      <c r="I20" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="J20" s="12" t="s">
         <v>54</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -13911,17 +13995,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>19</v>
@@ -13932,15 +14016,17 @@
       <c r="H21" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="I21" s="12"/>
+      <c r="I21" s="12" t="s">
+        <v>117</v>
+      </c>
       <c r="J21" s="12" t="s">
         <v>54</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -13955,19 +14041,19 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>18</v>
@@ -13983,10 +14069,10 @@
         <v>309</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -14001,17 +14087,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
         <v>115</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>17</v>
@@ -14025,10 +14111,10 @@
         <v>54</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -14043,17 +14129,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>4</v>
@@ -14069,10 +14155,10 @@
         <v>54</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -14083,19 +14169,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>12</v>
@@ -14108,13 +14194,13 @@
       </c>
       <c r="I25" s="12"/>
       <c r="J25" s="12" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -14125,17 +14211,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="12" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>20</v>
@@ -14151,10 +14237,10 @@
         <v>54</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -14165,17 +14251,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="12" t="s">
         <v>127</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>5</v>
@@ -14187,10 +14273,10 @@
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
       <c r="K27" s="12" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -14201,17 +14287,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>9</v>
@@ -14223,10 +14309,10 @@
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
       <c r="K28" s="12" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -14237,17 +14323,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>15</v>
@@ -14259,10 +14345,10 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="12" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -14273,17 +14359,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>22</v>
@@ -14295,10 +14381,10 @@
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="12" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -14446,7 +14532,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14460,7 +14546,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14468,60 +14554,72 @@
         <v>15</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="12"/>
+      <c r="B6" s="12" t="s">
+        <v>708</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="12"/>
+      <c r="B7" s="12" t="s">
+        <v>709</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="12"/>
+      <c r="B9" s="12" t="s">
+        <v>711</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="12"/>
+      <c r="B10" s="12" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="12"/>
+      <c r="B12" s="12" t="s">
+        <v>713</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="12"/>
+      <c r="B13" s="12" t="s">
+        <v>713</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -14574,19 +14672,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>11</v>
@@ -14601,13 +14699,13 @@
         <v>53</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>57</v>
@@ -14618,17 +14716,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>18</v>
@@ -14646,10 +14744,10 @@
         <v>54</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>57</v>
@@ -14660,19 +14758,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>7</v>
@@ -14687,13 +14785,13 @@
         <v>53</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>57</v>
@@ -14704,17 +14802,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>10</v>
@@ -14732,10 +14830,10 @@
         <v>54</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>57</v>
@@ -14746,19 +14844,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>13</v>
@@ -14776,10 +14874,10 @@
         <v>309</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>57</v>
@@ -14790,14 +14888,14 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>169</v>
@@ -14818,10 +14916,10 @@
         <v>54</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>57</v>
@@ -14832,17 +14930,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>5</v>
@@ -14860,10 +14958,10 @@
         <v>129</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="M23" s="12" t="s">
         <v>57</v>
@@ -14874,17 +14972,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>8</v>
@@ -14899,13 +14997,13 @@
         <v>117</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="M24" s="12" t="s">
         <v>57</v>
@@ -14916,17 +15014,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>17</v>
@@ -14944,10 +15042,10 @@
         <v>54</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="M25" s="12" t="s">
         <v>57</v>
@@ -14958,17 +15056,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="11" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>20</v>
@@ -14986,10 +15084,10 @@
         <v>54</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="M26" s="12" t="s">
         <v>57</v>
@@ -15000,17 +15098,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="11" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>9</v>
@@ -15028,10 +15126,10 @@
         <v>129</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>57</v>
@@ -15042,17 +15140,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="11" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>1</v>
@@ -15070,10 +15168,10 @@
         <v>54</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="M28" s="12" t="s">
         <v>57</v>
@@ -15084,16 +15182,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>2</v>
@@ -15111,10 +15209,10 @@
         <v>54</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="M29" s="12" t="s">
         <v>57</v>
@@ -15122,16 +15220,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>12</v>
@@ -15146,13 +15244,13 @@
         <v>53</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>57</v>
@@ -15160,13 +15258,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>15</v>
@@ -15184,10 +15282,10 @@
         <v>309</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="M31" s="12" t="s">
         <v>57</v>
@@ -15229,7 +15327,7 @@
         <v>147</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15237,7 +15335,7 @@
         <v>62</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15245,7 +15343,7 @@
         <v>148</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15253,7 +15351,7 @@
         <v>149</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15261,7 +15359,7 @@
         <v>70</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
     </row>
   </sheetData>

--- a/D1_Fiches_Clubs_Joueurs_26_27.xlsx
+++ b/D1_Fiches_Clubs_Joueurs_26_27.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="1128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2527" uniqueCount="1128">
   <si>
     <t xml:space="preserve">FICHES CLUBS · D1 FUTSAL 2026-2027</t>
   </si>
@@ -4168,7 +4168,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4250,10 +4250,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4665,7 +4661,7 @@
       <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="24" t="s">
         <v>793</v>
       </c>
     </row>
@@ -4673,7 +4669,7 @@
       <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>794</v>
       </c>
     </row>
@@ -4872,7 +4868,7 @@
       <c r="I19" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="J19" s="25" t="s">
+      <c r="J19" s="24" t="s">
         <v>815</v>
       </c>
       <c r="K19" s="12" t="s">
@@ -5381,34 +5377,44 @@
       <c r="A36" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B36" s="21"/>
+      <c r="B36" s="12" t="s">
+        <v>822</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="21"/>
+      <c r="B37" s="12" t="s">
+        <v>817</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B38" s="21"/>
+      <c r="B38" s="12" t="s">
+        <v>840</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B39" s="21"/>
+      <c r="B39" s="12" t="s">
+        <v>851</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B40" s="21"/>
+      <c r="B40" s="12" t="s">
+        <v>798</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="4">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G17:G31" type="list">
       <formula1>"Gardien,Fixo,Ailier,Pivot,Universel"</formula1>
       <formula2>0</formula2>
@@ -5423,10 +5429,6 @@
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M17:M31" type="list">
       <formula1>"oui,non"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B36:B40" type="list">
-      <formula1>$A$17:$A$31</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -7225,7 +7227,7 @@
       <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="24" t="s">
         <v>1037</v>
       </c>
     </row>
@@ -8002,34 +8004,44 @@
       <c r="A38" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B38" s="21"/>
+      <c r="B38" s="12" t="s">
+        <v>1082</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B39" s="21"/>
+      <c r="B39" s="12" t="s">
+        <v>1067</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B40" s="21"/>
+      <c r="B40" s="12" t="s">
+        <v>1043</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B41" s="21"/>
+      <c r="B41" s="12" t="s">
+        <v>1057</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B42" s="21"/>
+      <c r="B42" s="12" t="s">
+        <v>1077</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="4">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G17:G32" type="list">
       <formula1>"Gardien,Fixo,Ailier,Pivot,Universel"</formula1>
       <formula2>0</formula2>
@@ -8044,10 +8056,6 @@
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M17:M34" type="list">
       <formula1>"oui,non"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B38:B42" type="list">
-      <formula1>$A$17:$A$31</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -10998,11 +11006,15 @@
       <c r="F18" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G18" s="12"/>
+      <c r="G18" s="12" t="s">
+        <v>62</v>
+      </c>
       <c r="H18" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="I18" s="12"/>
+      <c r="I18" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="J18" s="12"/>
       <c r="K18" s="12" t="s">
         <v>343</v>
@@ -11144,7 +11156,9 @@
       <c r="F22" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="G22" s="12"/>
+      <c r="G22" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H22" s="12" t="s">
         <v>52</v>
       </c>
@@ -11634,7 +11648,9 @@
       <c r="A40" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="21"/>
+      <c r="B40" s="12" t="s">
+        <v>339</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
@@ -11648,7 +11664,9 @@
       <c r="A42" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B42" s="21"/>
+      <c r="B42" s="12" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
@@ -11659,7 +11677,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="4">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G17:G31" type="list">
       <formula1>"Gardien,Fixo,Ailier,Pivot,Universel"</formula1>
       <formula2>0</formula2>
@@ -11674,10 +11692,6 @@
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M17:M35" type="list">
       <formula1>"oui,non"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B40 B42" type="list">
-      <formula1>$A$17:$A$31</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -11763,7 +11777,7 @@
       <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>432</v>
       </c>
     </row>
@@ -12538,7 +12552,7 @@
       <c r="D33" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="E33" s="23" t="s">
+      <c r="E33" s="22" t="s">
         <v>525</v>
       </c>
       <c r="F33" s="1" t="n">
@@ -12735,7 +12749,7 @@
       <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>532</v>
       </c>
     </row>
@@ -12743,7 +12757,7 @@
       <c r="A9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>533</v>
       </c>
     </row>
@@ -13471,7 +13485,7 @@
       <c r="D32" s="0" t="s">
         <v>615</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="23" t="s">
         <v>616</v>
       </c>
       <c r="F32" s="0" t="n">
@@ -13513,7 +13527,7 @@
       <c r="D33" s="0" t="s">
         <v>621</v>
       </c>
-      <c r="E33" s="24" t="s">
+      <c r="E33" s="23" t="s">
         <v>622</v>
       </c>
       <c r="F33" s="0" t="n">
@@ -13708,7 +13722,7 @@
       <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="24" t="s">
         <v>627</v>
       </c>
     </row>
@@ -13835,7 +13849,7 @@
         <v>10</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>52</v>
@@ -14102,7 +14116,9 @@
       <c r="F23" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="G23" s="12"/>
+      <c r="G23" s="12" t="s">
+        <v>70</v>
+      </c>
       <c r="H23" s="12" t="s">
         <v>52</v>
       </c>
@@ -14446,34 +14462,44 @@
       <c r="A36" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B36" s="21"/>
+      <c r="B36" s="12" t="s">
+        <v>676</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="21"/>
+      <c r="B37" s="12" t="s">
+        <v>647</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B38" s="21"/>
+      <c r="B38" s="12" t="s">
+        <v>634</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B39" s="21"/>
+      <c r="B39" s="12" t="s">
+        <v>661</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B40" s="21"/>
+      <c r="B40" s="12" t="s">
+        <v>667</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="4">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G17:G31" type="list">
       <formula1>"Gardien,Fixo,Ailier,Pivot,Universel"</formula1>
       <formula2>0</formula2>
@@ -14488,10 +14514,6 @@
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M17:M31" type="list">
       <formula1>"oui,non"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B36:B40" type="list">
-      <formula1>$A$17:$A$31</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/D1_Fiches_Clubs_Joueurs_26_27.xlsx
+++ b/D1_Fiches_Clubs_Joueurs_26_27.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Mode emploi" sheetId="1" state="visible" r:id="rId3"/>
@@ -6767,7 +6767,7 @@
         <v>91</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I23" s="12" t="s">
         <v>53</v>
@@ -8929,7 +8929,7 @@
         <v>26</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>57</v>
@@ -11601,7 +11601,7 @@
         <v>425</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>91</v>
@@ -12229,7 +12229,7 @@
         <v>91</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I25" s="12" t="s">
         <v>53</v>
